--- a/src/results/(News)Sentiment.xlsx
+++ b/src/results/(News)Sentiment.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="3" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)All" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Bioenergi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Energi Fosil" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Minyak" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Minyak" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Produk Kilang" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Produk Kilang" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -121,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,18 +132,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,31 +1149,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Tanggal awal</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Tanggal akhir</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="7" t="n">
         <v>45950</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="7" t="n">
         <v>45957</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -1185,10 +1183,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="7" t="n">
         <v>45958</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="7" t="n">
         <v>45973</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1201,17 +1199,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>45973</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>45987</v>
+      <c r="A4" s="7" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>45981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Harga minyak kelapa sawit (CPO) mengalami penurunan signifikan antara tanggal 21 hingga 24 November 2025, mencapai level terendah dalam lebih dari empat bulan, disebabkan oleh peningkatan pasokan di Malaysia, perkiraan lesunya permintaan ekspor, apresiasi nilai tukar ringgit, dan penurunan harga minyak nabati pesaing.
-2. Meskipun berada dalam zona bearish, analisis teknikal harian dan mingguan menunjukkan potensi CPO untuk mengalami technical rebound atau kenaikan harga dalam waktu dekat, mengingat komoditas tersebut telah terkoreksi dalam dan berada dalam kondisi jenuh jual (oversold).
-3. Kementerian Kehutanan (Kemenhut) dan Satuan Tugas Penertiban Kawasan Hutan (Satgas PKH) memperketat pengamanan dan melanjutkan operasi penertiban kebun sawit ilegal di Taman Nasional Tesso Nilo, Riau, dengan fokus mengembalikan kawasan sebagai habitat gajah sumatera dan menindak pemilik lahan, pemodal, serta pengendali alat berat, bukan masyarakat kecil, meskipun menghadapi perusakan fasilitas posko.</t>
+          <t>1. Beberapa perusahaan kelapa sawit menunjukkan kinerja keuangan yang membaik, di mana PTPN IV PalmCo melaporkan peningkatan laba bersih 49% menjadi Rp3,76 triliun pada tahun 2024, dan PT Sampoerna Agro Tbk (SGRO) mengalami kenaikan laba bersih 236,06% pada semester I-2025 yang diikuti akuisisi oleh POSCO International. Selain itu, PT Sawit Sumbermas Sarana Tbk (SSMS) memperoleh pembiayaan sindikasi Rp5,2 triliun untuk memperkuat operasional dan ekspansi melalui akuisisi lahan.
+2. Harga minyak sawit mentah (CPO) di Bursa Malaysia sempat naik selama lima hari berturut-turut hingga mencapai MYR 4.226/ton pada 19 November 2025, namun kemudian reli tersebut terhenti akibat permintaan yang melemah dan penurunan harga minyak kedelai. Sejalan dengan perbaikan harga CPO, harga tandan buah segar (TBS) sawit petani mitra di Sumatra Utara sedikit meningkat menjadi Rp3.435,79 per kilogram, meskipun harga kernel mengalami penurunan.
+3. Sektor kelapa sawit Indonesia terus berupaya memenuhi standar keberlanjutan global, ditunjukkan dengan peluncuran ESG Advisory Playbook oleh BNI untuk membantu debitur dalam transisi hijau. Di sisi lain, meskipun Indonesia–European Union Comprehensive Economic Partnership Agreement (IEU-CEPA) diharapkan menghapus tarif ekspor, produk sawit masih menghadapi tantangan ketat dari regulasi keberlanjutan Uni Eropa seperti EUDR dan RED, yang memerlukan perbaikan rantai pasok dan ketelusuran untuk mempertahankan akses pasar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>45986</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1. Harga minyak sawit mentah (CPO) menunjukkan tren penurunan pada periode ini, dengan harga di Bursa Malaysia Derivatives Exchange tercatat turun menjadi MYR 4.068/ton pada 21 November dan MYR 4.055/ton pada 24 November. Penurunan harga ini disebabkan oleh beberapa faktor, termasuk peningkatan inventori pasokan, perkiraan permintaan ekspor yang melemah dari Malaysia, penguatan nilai tukar ringgit yang membuat CPO lebih mahal bagi pembeli asing, serta harga minyak nabati pesaing seperti minyak kedelai yang juga mengalami penurunan.
+2. Indonesia diproyeksikan akan mengalami penurunan porsi ekspor sawitnya di masa mendatang karena peningkatan utilisasi domestik. Kebutuhan dalam negeri akan sawit semakin besar, terutama untuk mendukung program mandatory biodiesel B40. Ekonom menyarankan agar pemerintah melakukan perhitungan yang tepat untuk memastikan pasokan CPO dapat memenuhi kebutuhan B40 tanpa mengorbankan pasokan untuk industri dan rumah tangga. Ada juga peluang untuk meningkatkan produktivitas CPO melalui peremajaan sawit tanpa perlu menambah luas lahan, dengan memanfaatkan dana Badan Pengelola Dana Perkebunan Kelapa Sawit (BPDPKS).
+3. Sektor hilirisasi sawit nasional mengalami perkembangan dengan diresmikannya PT AGPA Refinery Complex (ARC) di Balikpapan, Kalimantan Timur. Fasilitas dengan kapasitas 500.000 ton per tahun ini merupakan hasil kolaborasi Indonesia-Korea Selatan dan bertujuan untuk memperkuat rantai pasok energi bersih berbasis kelapa sawit. ARC diharapkan dapat menciptakan nilai tambah bagi industri sawit nasional dengan mengolah CPO menjadi berbagai produk bernilai jual tinggi seperti minyak nabati dan bahan bakar bio, yang sebagian besar ditujukan untuk ekspor, serta mendukung transisi menuju energi bersih.</t>
         </is>
       </c>
     </row>
@@ -1226,31 +1239,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Tanggal awal</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Tanggal akhir</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="7" t="n">
         <v>45967</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="7" t="n">
         <v>45974</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -1260,10 +1273,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="7" t="n">
         <v>45975</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="7" t="n">
         <v>45980</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1276,18 +1289,292 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="7" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>45981</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.  Persediaan produk olahan seperti bensin dan distilat (termasuk solar) di Amerika Serikat, setelah periode di level rendah dalam lebih dari satu dekade, baru-baru ini mencatat kenaikan untuk pertama kalinya dalam lebih dari sebulan. Meskipun demikian, selisih harga produk olahan (crack spreads) tetap tinggi. Sementara itu, harga gas alam di AS mengalami kenaikan hampir dua kali lipat tahun ini karena permintaan yang tinggi, sedangkan harga gas alam di Eropa cenderung rendah.
+2.  Harga minyak mentah global menunjukkan tren melemah, dengan Brent diperdagangkan di bawah $64 per barel dan WTI di atas $59 per barel, didominasi sentimen pasokan yang cenderung surplus. Meskipun persediaan minyak mentah AS menurun, volume minyak yang diangkut melalui laut meningkat tajam, mencapai rekor tertinggi, sebagian karena rute transit yang lebih panjang untuk minyak Rusia.
+3.  Di Indonesia, Pertamina memperkuat pengawasan pasokan BBM dan LPG untuk menghadapi lonjakan permintaan dan tantangan cuaca ekstrem menjelang periode libur akhir tahun 2025 dan awal 2026. Proyek Refinery Development Master Plan (RDMP) Balikpapan dijadwalkan akan diresmikan pada pertengahan Desember 2025, yang diharapkan mengurangi ketergantungan impor BBM hingga 15% dengan kapasitas produksi 360.000 barel per hari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>45986</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1. Harga minyak global menunjukkan tren penurunan dengan Brent Crude dan WTI masing-masing berada di sekitar $62.59 dan $58.08 per barel, dipicu laporan kesepakatan damai Ukraina-AS dan kekhawatiran pasokan berlebih. Harga gas Eropa juga turun ke level terendah sejak Mei 2024 karena negosiasi damai, cuaca hangat, dan pasokan yang melimpah. Analis memproyeksikan penurunan harga lebih lanjut hingga 2026-2027, meskipun ada kekhawatiran tentang kurangnya investasi dalam jangka panjang.
+2. Pasokan bahan bakar minyak (BBM) di SPBU swasta di Indonesia, seperti Vivo, BP-AKR, dan Shell, berangsur pulih setelah melakukan pembelian base fuel dari Pertamina Patra Niaga. Vivo telah membeli 100.000 barel dan menurunkan harga Revvo 92, sementara BP-AKR menambah pasokan menjadi total 200.000 barel, dan Shell telah menyelesaikan negosiasi untuk pembelian 100.000 barel.
+3. Pemerintah Indonesia melakukan langkah-langkah untuk mendukung Pertamina dan ketahanan energi nasional, termasuk mengubah skema pencairan dana kompensasi BBM bersubsidi menjadi bulanan yang akan mendukung likuiditas Pertamina. Pertamina Patra Niaga juga meningkatkan stok Pertalite sebesar 1,4 juta kiloliter dan menyiapkan satuan tugas untuk memastikan ketersediaan BBM selama periode Natal dan Tahun Baru (Nataru), serta berupaya menjaga keterjangkauan harga BBM campuran bioetanol melalui relaksasi cukai.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>45974</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B3" s="7" t="n">
         <v>45980</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>45987</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  Pasar minyak global saat ini ditandai oleh kelebihan pasokan yang signifikan, dengan IEA dan OPEC memproyeksikan surplus besar pada tahun 2026, diperparah oleh peningkatan stok minyak mentah AS, yang menyebabkan harga minyak bertahan di level rendah meskipun ada gangguan geopolitik jangka pendek.
+2.  Ketegangan geopolitik, khususnya perang Rusia-Ukraina, terus memengaruhi pasokan minyak global, di mana serangan drone Ukraina di pelabuhan dan kilang minyak Rusia menyebabkan gangguan ekspor sementara, sementara sanksi AS yang akan datang terhadap produsen Rusia memperlebar diskon minyak mentah Urals secara signifikan terhadap Brent.
+3.  Di Indonesia, sektor energi fosil menghadapi isu hukum terkait dugaan korupsi impor BBM yang melibatkan mantan pejabat Pertamina Patra Niaga, di mana tim kuasa hukum berargumen bahwa kliennya justru mencetak keuntungan historis bagi perusahaan.
+4.  Pemerintah Indonesia melalui Kementerian ESDM juga mendorong penerapan bensin campuran etanol 10% (E10) pada tahun 2028 meskipun menghadapi berbagai tantangan, sementara Pertamina Patra Niaga berhasil mengendalikan penyaluran BBM bersubsidi dengan memblokir ratusan ribu kendaraan yang terindikasi melakukan kecurangan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>45981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Pasokan bahan bakar minyak (BBM) di SPBU swasta seperti Shell, BP-AKR, dan Vivo diperkirakan akan kembali normal pada akhir November 2025. Hal ini menyusul kesepakatan pembelian *base fuel* (bahan bakar murni) dari PT Pertamina Patra Niaga, dengan Shell dan Vivo masing-masing menyerap 100.000 barel, sementara BP-AKR menambah pasokan hingga total 200.000 barel.
-2. PT Pertamina Patra Niaga meningkatkan stok BBM nasional, termasuk Pertalite sebanyak 1,4 juta kiloliter dan Pertamax Turbo, untuk mengamankan pasokan selama periode Natal dan Tahun Baru (Nataru) 2025/2026. Kementerian Pertahanan juga akan mengerahkan personel TNI mulai Desember 2025 untuk mengamankan kilang minyak dan terminal Pertamina yang merupakan objek vital nasional.
-3. Kementerian Energi dan Sumber Daya Mineral (ESDM) akan memperketat pengawasan kualitas BBM Pertamina, terutama menjelang Nataru, setelah adanya beberapa keluhan masyarakat terkait kualitas BBM yang tercampur air atau isu lainnya. Pengawasan ini akan melibatkan analisis rutin oleh Lemigas.
-4. Di pasar global, harga minyak mentah mengalami penurunan (Brent di $62/barel, WTI di $58.08/barel) karena laporan kemajuan kesepakatan damai Rusia-Ukraina dan kekhawatiran pasokan berlebih. Sementara itu, harga gas di Eropa berada pada level terendah sejak Mei 2024 akibat perundingan damai, cuaca hangat, dan pasokan yang melimpah.</t>
+          <t>1. Menjelang libur Natal 2025 dan Tahun Baru 2026, Pertamina meningkatkan pengawasan pasokan dan distribusi BBM dan LPG untuk mengantisipasi lonjakan permintaan serta potensi gangguan cuaca ekstrem. Proyek Refinery Development Master Plan (RDMP) Balikpapan, yang direncanakan beroperasi penuh pada pertengahan Desember 2025, ditargetkan mampu memangkas ketergantungan impor BBM hingga 15% dengan kapasitas produksi mencapai 360.000 barel per hari, didukung oleh fasilitas penyimpanan minyak berkapasitas 2 juta kiloliter.
+2. Ketersediaan stok BBM nasional berada dalam kondisi aman dengan cadangan dilaporkan cukup untuk 18 hingga 19 hari.
+3. Di pasar global, harga minyak mentah mempertahankan penurunan setelah persediaan bahan bakar di Amerika Serikat meningkat, meskipun data menunjukkan persediaan minyak mentah AS turun sebesar 3,4 juta barel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>45986</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.  Beberapa operator SPBU swasta, yaitu BP-AKR dan Vivo, telah memperoleh tambahan pasokan base fuel dari Pertamina Patra Niaga masing-masing 100.000 barel, sehingga total pembelian BP-AKR mencapai 200.000 barel. Shell Indonesia juga dalam tahap final negosiasi untuk membeli 100.000 barel base fuel dari Pertamina Patra Niaga untuk mengisi kembali stok BBM mereka.
+2.  Pertamina Patra Niaga meningkatkan stok Pertalite sebesar 1,4 juta kiloliter (KL) melalui kombinasi produksi kilang dan impor, dengan tujuan memperkuat ketahanan stok BBM menjadi 21-23 hari menjelang periode Natal dan Tahun Baru. Penambahan stok juga dilakukan untuk Pertamax Turbo.
+3.  Dalam upaya efisiensi dan regulasi, Daihatsu meluncurkan Rocky e-Smart Hybrid yang diklaim sangat efisien dengan konsumsi BBM 34,8 km per liter. Di sisi kebijakan, BPH Migas akan menyelesaikan revisi Perpres No. 191 Tahun 2014 untuk tata kelola penyaluran Pertalite agar lebih tepat sasaran, sementara usulan penghapusan cukai bioetanol sebesar Rp20.000 per liter juga diajukan karena saat ini menambah harga Pertamax Green 95 sekitar Rp1.000 per liter.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>45957</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>45973</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>45981</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Kilang Pertamina Internasional (KPI) telah meningkatkan kapasitas produksi unit platformer di Kilang Dumai menjadi 14 ribu barel per hari, yang menghasilkan gasoline RON 95.
+2. KPI memproduksi biofuel melalui metode co-processing, menghasilkan bioavtur Pertamina Sustainable Aviation Fuel (SAF) dengan bahan baku minyak inti sawit, serta memproduksi biodiesel 100% (HVO) atau Pertamina Renewable Diesel dari bahan baku nabati.
+3. Pengembangan green refinery oleh KPI mencakup produksi Pertamina SAF dari minyak jelantah di Kilang Cilacap, yang telah digunakan dalam penerbangan komersial perdana pada pertengahan Agustus 2025, dan berencana dikembangkan lebih lanjut di Kilang Dumai dan Balongan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>45986</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.  Menteri Pertahanan menginstruksikan pengerahan personel Tentara Nasional Indonesia (TNI) untuk mengamankan kilang minyak dan terminal milik PT Pertamina (Persero).
+2.  Pengerahan pasukan akan dimulai pada Desember 2025, dengan menugaskan personel dari TNI Angkatan Darat dan dipantau oleh Badan Intelijen Strategis (BAIS).
+3.  Kementerian Energi dan Sumber Daya Mineral (ESDM) menyatakan dukungan terhadap rencana ini, menganggapnya sebagai langkah wajar karena kilang Pertamina termasuk dalam kategori objek vital nasional.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>45957</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>45973</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>45981</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tidak ada berita</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>45986</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tidak ada berita</t>
         </is>
       </c>
     </row>

--- a/src/results/(News)Sentiment.xlsx
+++ b/src/results/(News)Sentiment.xlsx
@@ -3,15 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="13" activeTab="14" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)All" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Bioenergi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Minyak" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Minyak" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Produk Kilang" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Produk Kilang" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Idx Risiko Geopolitik" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Idx Volatilitas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Nilai Tukar Rupiah" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)IHSG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Inflasi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)BI-Rate" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)JIBOR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Idx Penjualan Retail" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Idx Keyakinan Konsumen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Idx PMI" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Neraca Perdagangan" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)PDB" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Biodiesel" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Bioetanol" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Minyak" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Minyak" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Produk Kilang" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Produk Kilang" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -25,13 +38,18 @@
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -55,12 +73,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -103,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,6 +146,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1120,43 +1156,1258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  BNI Sekuritas memproyeksikan ekonomi Indonesia tetap prospektif, ditopang konsumsi domestik, stabilitas kebijakan, investasi, dan program sosial. Indeks Harga Saham Gabungan (IHSG) ditargetkan pada 9.100 dalam skenario dasar, dengan potensi kenaikan 24%. Hingga Oktober 2025, portofolio saham kelolaan BNI Wealth Management tumbuh 34% dan jumlah nasabah BNI Emerald meningkat 7% secara tahunan.
+2.  Pasar smartphone Indonesia mengalami pertumbuhan solid sebesar 12% secara tahunan pada kuartal III 2025, didorong oleh minat pada perangkat entry-level, adopsi fitur AI, dan peningkatan indeks kepercayaan konsumen. Samsung kembali mendominasi pasar dengan peningkatan pengiriman 30% secara tahunan, mencapai pangsa pasar 20%, sementara Infinix mencatat pertumbuhan pengiriman 45% secara tahunan, meraih pangsa pasar 12%.
+3.  Kementerian Perindustrian menyayangkan penolakan insentif otomotif untuk tahun 2026 oleh Menteri Koordinator Bidang Perekonomian, yang dikhawatirkan dapat menghambat pemulihan sektor manufaktur dan menurunkan optimisme pelaku usaha. Insentif ini dianggap krusial untuk mendorong pertumbuhan industri otomotif secara menyeluruh, termasuk sektor pendukung dan konsumsi, yang memiliki efek pengganda signifikan terhadap perekonomian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Indeks Keyakinan Konsumen (IKK) Indonesia menguat menjadi 124,0 pada November 2025, naik dari 121,2 pada bulan sebelumnya, mencerminkan optimisme terhadap kondisi ekonomi saat ini dan prospek enam bulan ke depan. Peningkatan ini didukung oleh stabilnya pendapatan, inflasi yang mereda, suku bunga akomodatif, dan berlanjutnya program stimulus fiskal pemerintah. Kenaikan kepercayaan ini juga terkait dengan keyakinan masyarakat terhadap pemerintah dan peningkatan pendapatan serta konsumsi di kelas menengah-bawah, yang akan menjadi penopang utama pertumbuhan ekonomi domestik menuju 2026.
+2. Pasar smartphone Indonesia mencatatkan pertumbuhan pengiriman 12% secara tahunan pada kuartal III-2025, dengan Samsung meraih pangsa pasar 20% setelah pengiriman meningkat 30%. Pertumbuhan ini didorong oleh minat tinggi pada perangkat entry-level, adopsi fitur AI, dan ketersediaan perangkat 5G yang lebih terjangkau. Sementara itu, pasar unitlink di Indonesia mengalami penurunan premi sebesar 17,57% secara tahunan hingga kuartal III-2025 menjadi Rp30,67 triliun, sebagian besar karena pengetatan regulasi pemasaran. Namun, pasar unitlink global diproyeksikan tumbuh pesat dengan CAGR 10,5% hingga 2034.
+3. Harga emas global berada di sekitar US$4.199,65 per troy ons dan perak di US$58,47 per troy ons pada 8 Desember 2025, didukung oleh ekspektasi pemangkasan suku bunga The Federal Reserve AS. Di sisi lain, ekonomi China menghadapi tantangan struktural, termasuk memburuknya sektor properti dengan penurunan penjualan rumah baru 20-30% pada November 2025 dan kesulitan keuangan pengembang seperti Vanke. Konsumsi domestik China juga lesu dan rasio kredit macet rumah tangga meningkat menjadi 1,33% pada paruh pertama 2025, yang akan menjadi fokus utama dalam Konferensi Kerja Ekonomi Pusat China mendatang.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  Indeks Kinerja Manufaktur Indonesia mencapai 53.3 pada November 2025, meningkat dari 51.2 pada Oktober 2025, menandai level tertinggi sejak Februari 2025 dan empat bulan ekspansi berturut-turut. Peningkatan ini didorong oleh lonjakan pesanan baru domestik tercepat dalam 27 bulan, meskipun pesanan ekspor mencatat penurunan terdalam dalam 14 bulan.
+2.  Ekonomi Indonesia menunjukkan kinerja solid dengan inflasi November 2025 terkendali pada 2.72% (yoy) dan surplus neraca perdagangan US$ 2.39 miliar pada Oktober 2025, melanjutkan surplus selama 66 bulan berturut-turut. Kebijakan pemerintah menempatkan dana sebesar Rp 200-276 triliun ke perbankan diklaim berhasil membalikkan optimisme masyarakat dan mendorong perbaikan ekonomi.
+3.  Di tingkat regional, aktivitas manufaktur ASEAN secara keseluruhan menguat dengan PMI naik menjadi 53 pada November 2025 dari 52.7 pada bulan sebelumnya. Pasar saham Indonesia menunjukkan decoupling signifikan, dengan Indeks Harga Saham Gabungan (IHSG) menguat 4.29% pada 28 November 2025, menjadi indeks dengan kinerja terbaik di Asia, didorong oleh arus dana asing dan ekspektasi pemangkasan suku bunga The Federal Reserve pada Desember.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Asian Development Bank (ADB) pada Desember 2025 merevisi proyeksi pertumbuhan ekonomi Indonesia naik menjadi 5.0% untuk tahun 2025 dari 4.9%, dan 5.1% untuk tahun 2026 dari 5.0%. Peningkatan ini didasari kinerja ekspor yang kuat, perbaikan belanja pemerintah, konsumsi dalam negeri, serta indeks kinerja manufaktur (PMI) yang berada di atas level 50 dari Agustus hingga Oktober 2025.
+2. Proyeksi pertumbuhan ekonomi Indonesia untuk 2025 sebesar 5.0% masih berada di bawah laju pertumbuhan beberapa negara Asia lainnya seperti Vietnam (7.5%) dan India (7.2%), namun sebanding dengan Filipina (5.0%). Indonesia diproyeksikan tumbuh lebih cepat dibandingkan China (4.8%), Malaysia (4.5%), Singapura (4.1%), dan Thailand (2.0%) pada tahun yang sama.
+3. ADB juga menaikkan prakiraan pertumbuhan ekonomi kawasan Asia yang sedang berkembang dan Pasifik menjadi 5.1% pada 2025 dan 4.6% pada 2026, didorong oleh ekspor yang lebih kuat dari perkiraan dan stabilnya kondisi keuangan. Namun, proyeksi ini masih menghadapi risiko dari ketegangan perdagangan yang berpotensi memanas kembali, gejolak pasar keuangan, dan tekanan geopolitik.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  Indonesia mencatat surplus neraca perdagangan kumulatif sebesar US$35,88 miliar pada Januari-Oktober 2025, didukung oleh surplus komoditas non-migas sebesar US$51,51 miliar. Namun, sektor migas mengalami defisit US$15,63 miliar pada periode yang sama. Pada Oktober 2025, surplus bulanan tercatat sebesar US$2,39 miliar, melanjutkan tren surplus selama 66 bulan berturut-turut meskipun nilainya menyusut dari bulan sebelumnya.
+2.  Amerika Serikat mengukuhkan posisi sebagai negara penyumbang surplus terbesar bagi Indonesia dengan total US$14,93 miliar pada Januari-Oktober 2025. Sebaliknya, China menjadi penyumbang defisit terdalam bagi Indonesia dengan minus US$16,32 miliar pada periode yang sama.
+3.  Penyusutan surplus perdagangan pada Oktober 2025 diindikasikan oleh Menteri Keuangan sebagai tanda pemulihan permintaan domestik. Kebijakan hilirisasi juga mulai menunjukkan dampak, dengan operasional pabrik petrokimia raksasa di Banten sejak Oktober 2025 yang diharapkan dapat memangkas impor bahan baku hingga 70%, berkontribusi pada substitusi impor US$1,4 miliar per tahun dan peningkatan ekspor US$600 juta per tahun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Indonesia's trade balance registered a surplus for the 66th consecutive month, reaching US$2.4 billion in October 2025, with total exports at US$24.24 billion. The fisheries sector contributed positively with exports of US$5.07 billion from January to October 2025, a 5.1% increase year on year, leading to a US$4.53 billion surplus. Conversely, the Textile and Textile Products industry recorded a trade deficit and a low PDB growth of 0.93% year on year in Q3 2025, attributed to economic weaknesses and import dumping practices.
+2. The Indonesian government is advancing policies to enhance its trade balance, including a plan to implement a 10% ethanol blend (E10) in gasoline by 2027 to reduce an annual gasoline import volume of 27 million tons. In bilateral relations, Indonesia and Pakistan agreed on December 9 2025 to balance their US$4.5 billion trade by increasing Pakistan's agricultural and IT exports to Indonesia. Concurrently, the US trade deficit declined 10.9% to US$52.8 billion in September 2025 due to a 3% export increase, while the IMF on December 11 2025 urged China to reorient its economy from export reliance towards domestic consumption, given China's trade surplus exceeding US$1 trillion through November.
+3. APINDO projects Indonesia's economic growth for 2026 at 5% to 5.4%, anticipating 7-16% year on year export growth, partially supported by potential IEU-CEPA and Indonesia-Canada CEPA agreements. However, this outlook is tempered by significant external challenges including the potential failure of Indonesia-US reciprocal tariff negotiations, which could revert tariffs on Indonesian exports to the US from 19% to 32%. This risk poses a substantial threat to export-oriented sectors such as furniture and frozen shrimp, which have high exposure to the US market. The Ministry of Energy and Mineral Resources is also evaluating 2026 BBM import quotas, considering a 10% increase in line with demand growth, to ensure supply security and maintain the energy sector's trade balance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  Pemerintah Indonesia dan Bank Indonesia menunjukkan optimisme terhadap pertumbuhan ekonomi nasional, menargetkan 5.4%-5.6% pada kuartal IV 2025 dan 5.4% di 2026, dengan proyeksi mencapai 8% pada 2029. Kebijakan moneter akan diarahkan untuk mendukung pertumbuhan ekonomi dan penciptaan lapangan kerja, dengan BI mempertimbangkan penurunan suku bunga acuan dan memberikan insentif likuiditas kepada bank yang mempercepat penyaluran kredit ke sektor prioritas, efektif 1 Desember 2025. Menteri Keuangan Purbaya Yudhi Sadewa telah menggelontorkan Rp276 triliun dana pemerintah ke perbankan untuk meningkatkan likuiditas, meskipun target penerimaan pajak 2025 diperkirakan tidak tercapai dan defisit APBN akan dijaga di bawah 3% dari PDB.
+2.  Sektor ekonomi utama di Indonesia diharapkan menjadi pendorong pertumbuhan. Ekonomi kreatif yang didominasi generasi muda ditargetkan terus meningkat kontribusinya, didukung Sensus Ekonomi 2026 oleh BPS. Sektor properti diharapkan menyumbang 0.5% PDB untuk setiap injeksi US$2.5-5 miliar, dengan rata-rata investasi Rp115 triliun (US$6.9 miliar) per tahun dalam 5 tahun terakhir. Usaha Mikro Kecil dan Menengah (UMKM), yang menyumbang lebih dari 60% PDB, terus didukung melalui berbagai program dan digitalisasi. Hilirisasi sumber daya alam, seperti nikel, diproyeksikan meningkatkan ekspor mencapai US$36-38 miliar pada 2025, dan secara keseluruhan, Indonesia menargetkan investasi Rp13.032 triliun (US$869 miliar) untuk periode 2025-2029. Aktivitas ekonomi digital juga menunjukkan pertumbuhan signifikan, dengan penerimaan pajak mencapai Rp43.75 triliun per Oktober 2025.
+3.  Lanskap ekonomi global menunjukkan perlambatan moderat, dengan Organisasi untuk Kerja Sama dan Pembangunan Ekonomi (OECD) memproyeksikan pertumbuhan global 3.2% pada 2025 dan 2.9% pada 2026, serta PDB Australia tumbuh 2.1% secara tahunan pada kuartal III 2025. Pasar keuangan global menunjukkan minat tinggi terhadap aset safe-haven seperti emas, yang diproyeksikan mencapai US$5.000 per troy ounce pada akhir 2026 oleh investor institusional. Harga minyak mentah Brent stabil di US$63.38 per barel dan WTI di US$59.04 per barel menjelang akhir November 2025, dengan sentimen dipengaruhi negosiasi geopolitik dan keputusan OPEC+. Meskipun demikian, pasar modal Indonesia menunjukkan kinerja kuat dengan arus modal asing masuk Rp12.70 triliun pada akhir November 2025, mendorong IHSG menuju target 10.500 pada 2026, sementara nilai tukar rupiah ditutup pada Rp16,663 per US dolar pada 1 Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Indonesia mencatat pertumbuhan ekonomi kuartal III 2025 sebesar 5.04% secara tahunan dan memproyeksikan pertumbuhan stabil di kisaran 5.0% hingga 5.4% pada 2026, sejalan dengan target ambisius pemerintah mencapai 8% dalam lima tahun ke depan. Upaya pemerintah berfokus pada hilirisasi sumber daya alam dan pengembangan Kawasan Ekonomi Khusus yang telah menarik investasi kumulatif sebesar Rp314 triliun hingga kuartal III 2025.
+2. Bank sentral Amerika Serikat memangkas suku bunga acuannya sebesar 25 basis poin menjadi 3.50% hingga 3.75% pada 11 Desember 2025, yang diharapkan memberi sentimen positif bagi pasar keuangan global dan domestik. Secara global, Dana Moneter Internasional memproyeksikan pertumbuhan ekonomi dunia sebesar 3% pada 2025, sementara muncul kekhawatiran terkait stablecoin dan investasi besar di sektor kecerdasan buatan di negara-negara seperti India.
+3. Kondisi fiskal Indonesia menunjukkan tantangan dengan penerimaan pajak yang mencapai Rp1.459 triliun atau 70.2% dari outlook APBN 2025 per Oktober 2025, berpotensi melebar defisit anggaran. Sektor perbankan mencatat pertumbuhan kredit melambat menjadi 7.36% secara tahunan per Oktober 2025, dengan kredit UMKM bahkan kontraksi minus 0.1%, menunjukkan perlunya dorongan lebih lanjut untuk sektor swasta.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Berikut ringkasan umum berita bioenergi antara tanggal 01 November 2025 dan 07 November 2025:
+1.  Ekspor CPO dan produk turunannya menunjukkan pertumbuhan yang positif. Badan Pusat Statistik (BPS) mencatat nilai ekspor CPO dan turunannya pada Januari-September 2025 naik 32,40% menjadi US$18,14 miliar, dengan volume meningkat 11,62% menjadi 17,58 juta ton. Wilayah Sumatera Utara juga melaporkan kenaikan ekspor keseluruhan sebesar 18,90% hingga September 2025, dengan CPO menjadi penyumbang utama. Meskipun demikian, harga CPO di Bursa Malaysia mengalami fluktuasi, sempat menurun ke level terendah dalam hampir empat bulan di awal November, namun menunjukkan sedikit pemulihan menjelang akhir pekan, dipengaruhi oleh pasokan yang melimpah dan pergerakan harga minyak nabati pesaing.
+2.  Pemerintah terus mendorong pengembangan bioenergi dengan rencana mandatori biodiesel B50 pada 2026. Kementerian ESDM memproyeksikan kebijakan ini dapat menghasilkan surplus pasokan solar domestik dan mengeliminasi impor solar, didukung oleh penyelesaian proyek kilang RDMP Balikpapan pada November 2025. Namun, asosiasi pertambangan seperti APBI dan Perhapi menyatakan kekhawatiran tentang potensi peningkatan biaya operasional dan isu teknis pada peralatan berat akibat implementasi B50. Di sisi lain, PT Perusahaan Gas Negara Tbk. (PGAS) telah memulai pembangunan titik injeksi biomethane dari limbah kelapa sawit (POME) di Sumatera Selatan, dengan target pengurangan emisi gas rumah kaca yang berarti.
+3.  Kinerja perusahaan sawit menunjukkan pertumbuhan yang kuat. PT Astra Agro Lestari Tbk. (AALI) mencatatkan kenaikan pendapatan 35,8% dan laba bersih 33% pada kuartal III-2025, didorong oleh peningkatan produksi dan harga CPO. Emiten CPO Grup Salim, PT Salim Ivomas Pratama Tbk. (SIMP) dan PT PP London Sumatra Indonesia Tbk. (LSIP), juga melaporkan pertumbuhan pendapatan dan laba bersih yang didukung oleh harga jual rata-rata yang lebih tinggi. Perusahaan juga menunjukkan komitmen pada keberlanjutan, seperti investasi AALI pada fasilitas penangkap metana dan program Sawit Terampil Sinar Mas Agribusiness and Food yang mendukung petani swadaya untuk memperoleh sertifikasi RSPO. Akademisi dan industri otomotif juga menyepakati percepatan mandatori bioetanol E10 dan biodiesel untuk transisi energi.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pada periode 2025-11-01–2025-11-07, rata-rata CPO 13853.67 dan rata-rata Biodiesel 14036.00.Periode ini mengalami penurunan 5.02% nilai CPO dan kenaikan 0.63% biodiesel dibanding week sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Pemerintah Indonesia mendorong implementasi program biodiesel B50 pada semester II/2026, yang instruksi percepatannya datang dari Presiden. Program ini dihadapkan pada tantangan ketersediaan bahan baku CPO yang belum memadai, kebutuhan metanol yang tinggi yang masih mengandalkan impor, serta hasil uji coba awal yang menunjukkan potensi dampak teknis pada kendaraan seperti umur filter yang lebih singkat dan daya mesin yang sedikit lebih rendah. Kementerian ESDM berencana memulai uji jalan B50 secara menyeluruh pada awal Desember 2025, dan Badan Pengelola Dana Perkebunan (BPDP) sedang mengkaji skema subsidi fleksibel untuk mengantisipasi gejolak harga.
+2. Harga minyak sawit mentah (CPO) di pasar global menunjukkan fluktuasi, dengan kecenderungan penurunan pada beberapa waktu terakhir yang dipengaruhi oleh tingginya pasokan di Malaysia. Namun, kalangan analis memproyeksikan harga CPO akan menguat pada 2026, didorong oleh pertumbuhan produksi yang mulai melambat dan antisipasi peningkatan permintaan dari program biodiesel. Kebijakan B50 ini juga menimbulkan kekhawatiran bagi negara pengimpor utama seperti India, yang sedang mencari strategi untuk mengamankan pasokan CPO mereka.
+3. Di sektor bioenergi dan turunan sawit, terdapat beberapa perkembangan positif dalam upaya hilirisasi dan keberlanjutan. PGN memulai pembangunan titik injeksi biomethane dari limbah kelapa sawit di Sumatra Selatan. PTPN IV PalmCo melaporkan peningkatan laba bersih dan pendapatan yang signifikan berkat peningkatan produktivitas dan efisiensi operasional. Selain itu, Kawasan Ekonomi Khusus (KEK) Maloy Batuta Trans Kalimantan menarik investasi besar untuk industri oleofood, dan program co-firing biomassa pada pembangkit listrik tenaga uap (PLTU) telah diterapkan di 47 lokasi, menunjukkan peningkatan pemanfaatan biomassa.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pada periode 2025-11-08 sampai 2025-11-14, rata-rata CPO 13768.75 dan rata-rata Biodiesel 14036.00.Periode ini mengalami penurunan 0.61% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.  Pemerintah Indonesia memastikan akan melanjutkan program mandatori biodiesel langsung ke B50 pada semester II-2026, tanpa transisi B45. Uji jalan B50 dijadwalkan dimulai awal Desember 2025 untuk berbagai sektor. Hasil uji laboratorium awal B50 menunjukkan potensi penurunan kinerja mesin dan mempercepat penggantian filter. Kebutuhan FAME untuk B50 diprediksi meningkat sekitar 4 juta kiloliter, memicu diskusi mengenai opsi pasokan CPO seperti pembatasan ekspor. Analis pasar dan asosiasi petani menyuarakan kekhawatiran terkait potensi lonjakan harga CPO dan dampaknya terhadap harga tandan buah segar (TBS) petani jika produksi tidak mencukupi.
+2.  Emiten kelapa sawit di Indonesia menunjukkan perbaikan kinerja keuangan hingga kuartal III-2025 dan diproyeksikan akan memberikan dividen yang lebih tinggi. Beberapa perusahaan melakukan aksi korporasi, seperti PT Sawit Sumbermas Sarana Tbk. (SSMS) yang memperoleh fasilitas kredit sindikasi Rp5,2 triliun untuk akuisisi dan ekspansi. Sementara itu, POSCO International Corporation mengakuisisi 65,721% saham PT Sampoerna Agro Tbk. (SGRO), yang kemudian mendivestasi bisnis sagunya untuk fokus pada kelapa sawit. PTPN IV PalmCo juga membukukan kenaikan laba bersih 49% pada 2024 dan menyetor dividen Rp1,5 triliun.
+3.  Harga minyak sawit mentah (CPO) di Bursa Malaysia menunjukkan pergerakan yang berfluktuasi, sempat menguat selama lima hari berturut-turut sebelum terkoreksi, dipengaruhi oleh data stok CPO Malaysia yang meningkat dan ekspektasi permintaan yang melemah. Di sisi lain, harga TBS petani di Sumatra Utara mulai menunjukkan perbaikan setelah beberapa minggu mengalami penurunan. Inisiatif keberlanjutan juga dilakukan, seperti peluncuran benih sawit toleran kekeringan oleh Sinar Mas Agribusiness and Food dan panduan ESG oleh BNI untuk sektor perkebunan sawit.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pada periode 2025-11-15 sampai 2025-11-21, rata-rata CPO 14020.60 dan rata-rata Biodiesel 14036.00.Periode ini mengalami kenaikan 1.83% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.  Pengembangan hilirisasi dan investasi di sektor kelapa sawit terus berlanjut di Indonesia, ditandai dengan peresmian PT AGPA Refinery Complex (ARC) di Balikpapan yang berkapasitas 500.000 ton per tahun sebagai kolaborasi Indonesia-Korea Selatan untuk energi terbarukan berbasis sawit. Selain itu, POSCO International mengakuisisi saham mayoritas PT Sampoerna Agro Tbk (SGRO), menambah lahan sawitnya menjadi total 150.000 hektare untuk memperkuat rantai pasok bahan baku biofuel, sementara PT Sawit Sumbermas Sarana Tbk (SSMS) juga mengakuisisi PT Sawit Mandiri Lestari senilai Rp1,6 triliun guna memperbesar skala usaha.
+2.  Data produksi dan perdagangan menunjukkan pergerakan turun pada September 2025, dengan produksi minyak kelapa sawit mentah (CPO) dan minyak inti sawit (PKO) menurun masing-masing sebesar 22,32% dan 24% dibandingkan bulan sebelumnya. Konsumsi domestik, khususnya biodiesel, juga mengalami penurunan sebesar 3,69%, dan total ekspor produk sawit merosot 36,65%. Meskipun demikian, produksi CPO dan PKO secara tahun berjalan (Year-on-Year) hingga September 2025 menunjukkan kenaikan 11,30%, dan nilai ekspor secara kumulatif juga lebih tinggi dibandingkan periode yang sama tahun sebelumnya karena peningkatan harga rata-rata CPO.
+3.  Harga CPO di pasar global mengalami fluktuasi selama periode ini; harga menunjukkan penurunan berturut-turut di awal pekan, mencapai level terendah sejak Juli, yang dipengaruhi oleh ekspektasi penurunan permintaan, penguatan mata uang ringgit, dan koreksi harga minyak nabati pesaing. Namun, harga CPO kemudian berbalik arah dan naik pada pertengahan hingga akhir periode, didukung oleh potensi technical rebound dan kekhawatiran akan gangguan pasokan akibat cuaca buruk di negara-negara produsen. Bersamaan dengan itu, Menteri Koordinator Bidang Pangan menyatakan bahwa menanam kelapa kini dapat lebih menguntungkan dibandingkan kelapa sawit karena peningkatan permintaan ekspor dan potensi hilirisasi kelapa di dalam negeri.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pada periode 2025-11-22 sampai 2025-11-28, rata-rata CPO 14061.25 dan rata-rata Biodiesel 14036.00.Periode ini mengalami kenaikan 0.29% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  Kementerian Energi dan Sumber Daya Mineral (ESDM) menetapkan Harga Indeks Pasar (HIP) bioetanol Desember 2025 sebesar Rp8.428 per liter, menurun dari Rp9.013 per liter pada November. HIP biodiesel Desember 2025 juga mengalami penurunan menjadi Rp13.381 per liter dari Rp14.036 per liter pada November. Harga rata-rata tetes tebu, sebagai komponen perhitungan bioetanol, tercatat Rp1.034 per kg untuk periode 15 Agustus hingga 14 November 2025.
+2.  PT Sinergi Gula Nusantara (Sugar Co) berencana mengakuisisi tiga pabrik gula yaitu PT Pabrik Gula Rajawali I, PT Pabrik Gula Rajawali II, dan PT Pabrik Gula Candi Baru dari ID Food. Pabrik-pabrik ini bergerak di sektor pengolahan tebu, yang merupakan bahan baku bioetanol. Secara terpisah, Nilai Tukar Petani (NTP) di Jawa Tengah pada November 2025 turun menjadi 116,11 poin dari 116,41 poin bulan sebelumnya, dengan penurunan yang terjadi pada subsektor tanaman perkebunan rakyat, termasuk tebu.
+3.  Kinerja ekspor nonmigas Indonesia pada Januari hingga Oktober 2025 mencapai US$223,1 miliar, menunjukkan kenaikan dari periode yang sama tahun sebelumnya. Total ekspor secara keseluruhan untuk periode tersebut juga meningkat menjadi US$234,04 miliar. Sektor industri pengolahan dan pertanian menjadi pendorong utama ekspor. Komoditas minyak kelapa sawit (CPO), yang merupakan bahan baku biodiesel, mencatat kenaikan nilai ekspor sebesar 25,73% secara tahunan.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pada bulan December 2025, rata-rata Bioetanol 8428.00 dan rata-rata Tetes Tebu 1034.00. Periode ini mengalami penurunan 6.49% nilai Bioetanol dan penurunan 12.37% Tetes Tebu dibanding bulan sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Program mandatori bioetanol campuran bensin sebanyak 5% (E5) di Indonesia berjalan lambat dan belum mencapai target. Produksi bioetanol oleh PT Pertamina (Persero) tercatat baru 150.000 kiloliter. Salah satu kendala utama adalah regulasi cukai yang memberlakukan etanol untuk bahan bakar sama dengan etanol untuk minuman beralkohol, serta ketersediaan bahan baku di sisi hulu.
+2. Pemerintah tengah berupaya mengatasi tantangan tersebut. Revisi Peraturan Presiden No. 40/2023 sedang dipersiapkan untuk mengecualikan pungutan cukai pada etanol yang digunakan sebagai bahan bakar. Di sisi hulu, pemerintah fokus pada ekspansi lahan tebu, dengan target perluasan lahan PT Perkebunan Nusantara (PTPN) menjadi 500.000–700.000 hektare dan program bongkar ratoon seluas 100.000 hektare pada 2025 dan 2026 untuk PT Sinergi Gula Nusantara (SGN), yang bertujuan menjamin pasokan molase.
+3. Kementerian Energi dan Sumber Daya Mineral (ESDM) menargetkan penerapan wajib E5 pada 2026, dimulai secara regional di Pulau Jawa, mengingat pasokan bioetanol yang masih terbatas dari tiga produsen. Selain itu, pemerintah juga berencana mengimplementasikan mandatori bensin campuran 10% etanol (E10) pada 2027, dengan perkiraan kebutuhan etanol mencapai 1,4 juta ton, dan tengah mempersiapkan pasokan bahan baku serta menjajaki kerja sama investasi dengan Brasil.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pada bulan December 2025, rata-rata Bioetanol 8428.00 dan rata-rata Tetes Tebu 1034.00. Periode ini mengalami penurunan 6.49% nilai Bioetanol dan penurunan 12.37% Tetes Tebu dibanding bulan sebelumnya.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Harga minyak mentah global mengalami tekanan penurunan sepanjang minggu pertama November 2025 akibat kekhawatiran kelebihan pasokan dan lemahnya permintaan, khususnya dari Amerika Serikat. Harga Brent diperdagangkan di sekitar US$63-US$64 per barel, dan West Texas Intermediate (WTI) mendekati US$60 per barel, dengan WTI anjlok sekitar 16-17% secara tahun berjalan. Stok minyak mentah AS menunjukkan kenaikan signifikan, dengan laporan API sebesar 6.5 juta barel dan EIA sebesar 5.2 juta barel pada pekan lalu.
+2. OPEC+ memutuskan untuk menghentikan sementara rencana kenaikan produksi pada kuartal I 2026, setelah peningkatan moderat pada Desember, sebagai upaya menyeimbangkan pasar dan meredam volatilitas. Morgan Stanley menaikkan proyeksi harga Brent menjadi US$60 per barel untuk semester I 2026 dari US$57.50. Namun, proyeksi tekanan harga tetap ada, dengan Capital Economics memperkirakan Brent mencapai US$60 per barel pada akhir 2025 dan US$50 per barel pada akhir 2026.
+3. Sanksi AS terhadap produsen minyak utama Rusia (Rosneft PJSC dan Lukoil PJSC) mengakibatkan kilang-kilang di China menghentikan pembelian minyak mentah Rusia, mempengaruhi sekitar 400.000 barel per hari atau 45% dari total impor Rusia ke China. Kondisi pasar yang cukup pasokan ini mendorong Arab Saudi untuk memangkas harga jual minyak mentah utamanya untuk pembeli Asia pada Desember, termasuk Arab Light yang dipangkas US$1.20 per barel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Harga minyak global menunjukkan kenaikan, dengan Brent di atas USD64 per barel dan West Texas Intermediate di sekitar USD60 per barel, didukung oleh perkembangan positif di Amerika Serikat. Kenaikan ini terjadi setelah harga minyak mentah turun dalam lima dari enam pekan terakhir karena kekhawatiran kelebihan pasokan. Pasar sedang menantikan rilis data pasokan dan permintaan dari OPEC, IEA, dan EIA pekan ini, sementara OPEC dan sekutunya berencana menunda kenaikan produksi pada kuartal pertama tahun depan untuk mengelola pasokan.
+2. Produksi minyak mentah Rusia sedikit meningkat pada Oktober menjadi rata-rata 9.411 mb/d, 43.000 b/d lebih tinggi dari September, namun masih 70.000 b/d di bawah kuota OPEC+ yang mencakup pemotongan kompensasi. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena beberapa kilang di India, China, dan Turki enggan menerima pasokan yang terkena sanksi.
+3. India, sebagai importir minyak mentah terbesar ketiga di dunia, mengurangi pembelian minyak dari Rusia untuk pengiriman Desember sebagai dampak sanksi Barat dan negosiasi dagang dengan Amerika Serikat. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia India tahun ini, tidak mengajukan pesanan untuk bulan tersebut. Pergeseran ini mendorong India untuk mencari pasokan alternatif dari kawasan Amerika dan Timur Tengah, mengingat sekitar 36% dari total impor minyak mentah India tahun ini berasal dari Rusia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1. Indonesia sedang menyiapkan Peraturan Presiden yang memperbolehkan PT Pertamina (Persero) untuk mengimpor energi langsung dari perusahaan Amerika Serikat tanpa proses lelang. Kebijakan ini merupakan tindak lanjut dari kesepakatan tarif timbal balik antara AS dan Indonesia pada Juli 2025, dengan tujuan mengurangi defisit perdagangan AS dengan Indonesia yang sekitar US$18 miliar, dan mengakselerasi komitmen impor minyak Indonesia dari AS senilai US$15 miliar. PT Kilang Pertamina Internasional (KPI) mencari cara agar impor minyak mentah dari AS dapat lebih ekonomis, dan pemerintah berencana meningkatkan impor minyak mentah dari AS mulai Desember 2025.
+2. Harga minyak global terkoreksi di pekan ini, dengan harga berjangka Brent turun US$1,63 (2,5%) menjadi US$63,26 per barel dan West Texas Intermediate (WTI) melemah US$1,56 (2,6%) menjadi US$59,18 per barel pada 20 November 2025. Penurunan ini dipengaruhi oleh laporan upaya AS untuk mengakhiri perang Rusia-Ukraina, yang berpotensi meningkatkan pasokan minyak Rusia ke pasar. Bersamaan dengan itu, sanksi AS terhadap Rosneft dan Lukoil mulai berlaku pada 21 November 2025, berpotensi membuat hampir 48 juta barel minyak mentah Rusia terlantar di laut dan mendorong pembeli di Asia mencari pasokan alternatif.
+3. Harga minyak mentah Indonesia (ICP) untuk Oktober 2025 ditetapkan sebesar US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya. Penurunan ini disebabkan oleh beberapa faktor seperti peningkatan suplai minyak oleh OPEC+ sebesar 137.000 barel per hari untuk November 2025, berkurangnya ketegangan geopolitik di Timur Tengah, pengolahan minyak mentah global yang diperkirakan mencapai titik terendah musiman 81,6 juta barel per hari pada Oktober, penguatan nilai tukar dolar AS, serta pemotongan harga jual resmi minyak mentah Arab Saudi untuk pembeli di Asia di tengah melemahnya permintaan dan perlambatan ekonomi Tiongkok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.  Harga minyak menunjukkan tekanan turun selama minggu ini, dengan Brent diperdagangkan di kisaran USD 62-63 per barel dan WTI Crude di kisaran USD 58-59 per barel. Prediksi dari bank investasi seperti Goldman Sachs memperkirakan WTI Crude akan rata-rata USD 53 per barel pada 2026, sementara JP Morgan memproyeksikan Brent dapat turun ke kisaran USD 30-an per barel pada 2027 karena kekhawatiran pasokan berlebih sebesar 2 juta barel per hari. Harga bensin eceran di Amerika Serikat turun di bawah USD 3 per galon di banyak negara bagian, dengan beberapa lokasi mencapai USD 1.99 per galon.
+2.  Pasokan minyak global tetap kuat, didorong oleh produksi yang tangguh dari produsen non-OPEC seperti Amerika Serikat, Brasil, dan Guyana. Meskipun eksekutif shale AS melaporkan tantangan profitabilitas di bawah USD 60 per barel dan kenaikan biaya pengeboran sebesar 5 hingga 10 persen dari tahun lalu, produksi shale AS terus meningkat. OPEC+ diperkirakan akan mempertahankan tingkat produksi saat ini pada pertemuan tanggal 30 November, menunda peningkatan produksi yang direncanakan untuk kuartal I 2026 akibat kekhawatiran peningkatan persediaan global.
+3.  Pembicaraan damai yang diperbarui antara Rusia dan Ukraina memberikan tekanan signifikan pada harga minyak karena potensi pelonggaran sanksi yang dapat meningkatkan pasokan Rusia. Di sisi lain, konferensi energi di Timur Tengah menampilkan pandangan yang berbeda, dengan ADIPEC menyoroti permintaan energi jangka panjang yang kuat dan kebutuhan investasi besar USD 18.2 triliun untuk mencapai 123 juta barel per hari pada 2050, sementara Dii Desert Energy Summit berfokus pada percepatan pertumbuhan energi rendah karbon dan investasi yang melampaui bahan bakar fosil dengan rasio 2 berbanding 1. Cina terus mempercepat pembelian minyak mentah strategisnya, mengimpor sekitar 2.15 juta barel per hari dari Rusia dan menimbun lebih dari 1 juta barel per hari pada beberapa bulan di tahun 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. OPEC+ menegaskan kembali rencana untuk menahan kenaikan produksi minyak mentah sepanjang kuartal I 2026 di tengah ekspektasi pelemahan pasar musiman dan potensi surplus pasokan global. Badan Energi Internasional (IEA) memproyeksikan rekor kelebihan pasokan pada 2026, sementara harga Brent diperdagangkan mendekati USD63/bbl dan West Texas Intermediate (WTI) mendekati USD59/bbl pada awal Desember 2025.
+2. Ketegangan geopolitik, seperti retorika dan pengerahan pasukan Amerika Serikat di bawah Presiden Donald Trump terkait Venezuela, serta upaya perundingan damai antara Amerika Serikat dan Rusia mengenai konflik Ukraina, terus menopang harga minyak dengan menambah premi risiko. Potensi gencatan senjata di Ukraina dapat membuka peluang pelonggaran sanksi terhadap Rusia dan peningkatan ekspor minyak, yang berpotensi menekan harga lebih lanjut.
+3. Indikasi kelebihan pasokan global tetap menjadi perhatian, didorong oleh lonjakan pasokan dari Amerika dan kenaikan persediaan minyak mentah AS sekitar 574.000 barel pada pekan lalu. Di sisi domestik, PT Pertamina International Shipping (PIS) menyiagakan 332 armada kapal tanker ditambah 12 kapal cadangan untuk memastikan kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia di Indonesia selama periode Natal 2025 dan Tahun Baru 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1. Harga minyak global menunjukkan volatilitas dan tren bearish menjelang akhir pekan, berfluktuasi antara sekitar US$57–US$64 per barel. Penurunan suku bunga acuan Federal Reserve sebesar 25 basis poin sesuai ekspektasi pasar, namun kekhawatiran kelebihan pasokan global dan perkembangan negosiasi Rusia-Ukraina yang mengarah ke jalur perdamaian menekan harga minyak.
+2. Kekhawatiran kelebihan pasokan global menjadi sentimen dominan, dengan laporan International Energy Agency (IEA) mencatat pasokan minyak dunia mencapai 109 juta barel per hari pada November. IEA merevisi perkiraan surplus global untuk tahun 2026 menjadi 3.84 juta barel per hari, sedikit lebih rendah dari proyeksi sebelumnya, didorong oleh peningkatan proyeksi pertumbuhan permintaan.
+3. Tiongkok terus melakukan penimbunan minyak mentah strategis dan komersial dengan rata-rata sekitar 1 juta barel per hari pada tahun 2025, dan diproyeksikan sekitar 900.000 barel per hari pada tahun 2026, yang membantu meredam kelebihan pasokan di pasar global. Sementara itu, Kementerian Energi dan Sumber Daya Mineral Indonesia melaporkan kerugian devisa negara sebesar Rp523 triliun per tahun karena impor minyak yang mencapai 313 juta barel pada 2024.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.  OPEC+ mengumumkan penghentian sementara kenaikan produksi pada kuartal I-2026 setelah kenaikan moderat pada Desember, sebagai upaya menyeimbangkan pasar di tengah tanda-tanda kelebihan pasokan. Morgan Stanley menaikkan proyeksi harga Brent menjadi USD60/bbl untuk semester I-2026, namun mencatat peningkatan produksi OPEC+ sebesar 500.000 bph dari Maret hingga Oktober jauh di bawah kenaikan kuota 2,6 mb/d.
+2.  Harga minyak mentah global melemah dan mencatat penurunan mingguan kedua, tertekan oleh peningkatan pasokan dari OPEC+ serta produsen non-anggota seperti Amerika Serikat dan Brasil. Brent turun menjadi sekitar USD63/bbl dan WTI di bawah USD60/bbl, dengan WTI anjlok sekitar 16% hingga 17% sepanjang tahun ini. Data American Petroleum Institute (API) menunjukkan stok minyak mentah Amerika Serikat naik 6,5 juta barel pada pekan lalu.
+3.  Kilang-kilang minyak di China, termasuk milik negara dan swasta, menghentikan pembelian minyak mentah asal Rusia setelah Amerika Serikat menjatuhkan sanksi terhadap produsen utama Moskow, memengaruhi sekitar 400.000 bpd atau hampir 45% dari total impor minyak Rusia ke China. Menanggapi pasar yang cukup mendapat pasokan dan lemahnya permintaan di Asia, Saudi Aramco memangkas harga minyak mentah unggulannya, Arab Light, untuk pasar Asia pada Desember sebesar USD1.20/bbl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Produksi minyak mentah Rusia pada Oktober mencapai rata-rata 9.411 juta barel per hari, meningkat 43.000 barel per hari dari September. Angka ini 70.000 barel per hari di bawah kuota OPEC+ yang mencakup pemotongan kompensasi, dengan target yang dibutuhkan sebesar 9.481 juta barel per hari. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena keengganan beberapa kilang di India, China, dan Turki untuk menerima minyak yang terkena sanksi.
+2. Harga minyak global menunjukkan kenaikan, dengan Brent melewati US$64 per barel dan West Texas Intermediate (WTI) bergerak di kisaran US$60 per barel, didorong oleh upaya mengakhiri penutupan pemerintahan Amerika Serikat. Kekhawatiran akan kelebihan pasokan masih membebani pasar, menyebabkan harga minyak mentah turun dalam lima dari enam pekan terakhir. Organisasi Negara-Negara Pengekspor Minyak (OPEC) dan sekutunya mulai melonggarkan pembatasan produksi, namun berencana menunda kenaikan output pada kuartal pertama tahun depan, sementara produsen non-OPEC termasuk Amerika Serikat terus menambah pasokan.
+3. India, importir minyak terbesar ketiga di dunia, mengurangi pembelian minyak mentah dari Rusia untuk pengiriman Desember. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia tahun ini, belum mengajukan pesanan. Perubahan pola pembelian ini sebagian besar didorong oleh sanksi Barat terhadap produsen minyak Rusia dan negosiasi dagang dengan Amerika Serikat, di mana India berkomitmen membeli lebih banyak minyak mentah dari Amerika Serikat. Akibatnya, kilang-kilang di India mulai mencari alternatif pasokan dari kawasan Amerika dan Timur Tengah, dengan Indian Oil Corp. berupaya membeli hingga 24 juta barel dari Amerika untuk pengiriman Januari hingga Maret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1. Indonesia berkomitmen untuk meningkatkan impor minyak mentah dari Amerika Serikat hingga US$15 miliar mulai Desember 2025, sebagai bagian dari kesepakatan tarif timbal balik. PT Pertamina (Persero) melalui anak usahanya PT Kilang Pertamina Internasional (KPI) berupaya mencari skema ekonomis untuk impor ini, dengan regulasi baru yang memungkinkan pembelian langsung tanpa lelang dari perusahaan AS.
+2. Harga minyak mentah global mengalami koreksi, dengan Brent turun 2,5% ke US$63,26 per barel dan WTI melemah 2,6% menjadi US$59,18 per barel pada 20 November 2025, dipicu laporan potensi berakhirnya perang Rusia-Ukraina dan peningkatan pasokan OPEC+ sebesar 137.000 barel per hari mulai November 2025. Harga Minyak Mentah Indonesia (ICP) Oktober 2025 ditetapkan US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya.
+3. Sanksi Amerika Serikat terhadap produsen minyak Rusia Rosneft PJSC dan Lukoil PJSC yang berlaku pada 21 November 2025 berpotensi menyebabkan hampir 48 juta barel minyak mentah Rusia terlantar di laut, memaksa pembeli di Asia mencari pasokan alternatif dan kapal tanker mencari tujuan baru di tengah tekanan untuk mematuhi sanksi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.  Pada 27 November 2025, harga minyak Brent naik 0.2% menjadi USD 63.34 per barel dan West Texas Intermediate (WTI) menguat 0.8% menjadi USD 59.10 per barel. Kenaikan ini dipicu oleh harapan terobosan pembicaraan perdamaian antara Rusia dan Ukraina, yang menetralkan kekhawatiran pasokan akibat sanksi baru AS terhadap produsen Rusia.
+2.  Organisasi Negara-Negara Pengekspor Minyak dan sekutunya (OPEC+) diperkirakan akan mempertahankan tingkat produksi pada pertemuan mendatang. Selain itu, delapan negara anggota OPEC+ yang secara bertahap meningkatkan produksi pada tahun 2025 diproyeksikan untuk mempertahankan kebijakan jeda kenaikan produksi pada kuartal I 2026.
+3.  Ekspektasi pemangkasan suku bunga acuan oleh The Federal Reserve pada Desember 2025 turut mendorong harga minyak, mengingat penurunan suku bunga dapat mendukung pertumbuhan ekonomi global dan memperkuat permintaan minyak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina International Shipping (PIS) mengaktifkan Satuan Tugas Nataru 2025/2026 dan menyiagakan 332 kapal tanker utama ditambah 12 kapal cadangan serta 338 kapal pendukung pelabuhan mulai 1 Desember 2025 untuk menjamin kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia nasional.
+2. Harga minyak dunia menguat pada 1 Desember 2025, dengan Brent diperdagangkan pada US$63 per barel dan West Texas Intermediate (WTI) pada US$59.13 per barel, setelah OPEC+ menegaskan rencana menahan kenaikan produksi sepanjang kuartal I/2026 akibat pelemahan kondisi pasar musiman.
+3. Keputusan OPEC+ untuk mempertahankan jeda pasokan selama tiga bulan diambil di tengah proyeksi surplus pasokan global, dengan Badan Energi Internasional (IEA) memperkirakan rekor kelebihan pasokan pada tahun 2026 dan harga minyak telah merosot 15% sepanjang tahun hingga akhir November 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.  Harga minyak global melemah sepanjang minggu dengan Brent diperdagangkan di bawah US$64/bbl dan kemudian turun menjadi US$61,94/bbl, sementara WTI mendekati US$60/bbl dan kemudian merosot ke US$58,25/bbl. Penurunan ini dipicu oleh pemulihan produksi 460.000 barel per hari di ladang minyak West Qurna 2 Irak dan kekhawatiran pasokan global berlebih dari OPEC+, Amerika Serikat, Brasil, dan Guyana. Stok minyak kargo di laut meningkat sekitar 2,5 juta barel per hari sejak pertengahan Agustus.
+2.  Medco Energi menargetkan produksi minyak dan gas bumi mencapai 160.000 barel setara minyak per hari (boepd) pada akhir 2025, meningkat dari 150.000 boepd pada kuartal III/2025, didukung oleh akuisisi 24% Participating Interest di Corridor PSC dan 45% PI di Sakakemang PSC. Perusahaan juga menandatangani perjanjian penjaminan untuk uang muka jual beli transaksi minyak mentah senilai maksimum US$80 juta. Pada semester I/2025, Medco mencatatkan laba bersih US$37,36 juta dari penjualan US$1,13 miliar.
+3.  Perkembangan geopolitik dan makroekonomi memengaruhi pasar minyak, termasuk negosiasi damai Rusia-Ukraina dan serangan terhadap infrastruktur energi Rusia. Negara-negara G7 dan Uni Eropa sedang mempertimbangkan larangan penuh layanan maritim untuk minyak Rusia. China melanjutkan penimbunan minyak mentah dengan perkiraan 800.000 hingga 900.000 barel per hari pada tahun 2026, meskipun pertumbuhan permintaan domestiknya diproyeksikan melambat menjadi 150.000 hingga 320.000 barel per hari pada tahun yang sama. Keputusan suku bunga Federal Reserve AS sebesar 25 basis poin juga dinantikan pasar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Pada 1 November 2025, beberapa operator SPBU di Indonesia melakukan penyesuaian harga Bahan Bakar Minyak (BBM). PT Pertamina (Persero) menaikkan harga Dexlite dan Pertamina Dex masing-masing sebesar Rp200 per liter menjadi Rp13.900/liter dan Rp14.200/liter, sementara harga Pertamax, Pertamax Turbo, dan Pertamax Green tetap tidak berubah. SPBU Shell dan BP-AKR mayoritas menurunkan harga produk bensin mereka seperti Shell Super (turun Rp210 menjadi Rp12.680/liter) dan BP 92 (turun Rp210 menjadi Rp12.680/liter), namun menaikkan harga produk diesel mereka.
+2. PT Pertamina Patra Niaga telah menyalurkan 100.000 barel base fuel RON 92 kepada BP-AKR (PT Aneka Petroindo Raya) melalui mekanisme bisnis-ke-bisnis, yang memungkinkan ketersediaan kembali BBM BP 92 di jaringan SPBU BP-AKR. BP-AKR diperkirakan akan membeli tambahan 100.000 barel base fuel lagi yang dijadwalkan tiba pada pekan ketiga November 2025. Kementerian ESDM melaporkan PT Vivo Energy Indonesia juga hampir mencapai kesepakatan untuk pembelian sekitar 100.000 barel base fuel, sedangkan negosiasi dengan Shell Indonesia masih berlangsung.
+3. Menanggapi dugaan masalah kualitas BBM Pertalite yang menyebabkan keluhan kendaraan "brebet" di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM telah memeriksa hampir 300 SPBU dan hasil sementara menunjukkan tidak ada kontaminasi air atau etanol. Pertamina juga membuka posko pengaduan dan menyediakan 32 bengkel rekanan untuk perbaikan gratis bagi konsumen yang terdampak. Sementara itu, Kilang Pertamina Internasional (KPI) di Cilacap melanjutkan inisiatif energi hijau, meningkatkan produksi gasoline RON 92 menjadi 53.000 barel per hari dan memproduksi bahan bakar nabati (HVO serta PertaminaSAF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Pada 10 November 2025, PT Kilang Pertamina Internasional (KPI) memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) Complex hasil Proyek Refinery Development Master Plan (RDMP) Balikpapan. Proyek ini akan meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari, serta memproduksi bahan bakar standar Euro V, tambahan LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun. Di samping itu, PT Pertamina (Persero) menargetkan keputusan investasi akhir (FID) proyek Kilang Tuban senilai US$24 miliar, dengan kapasitas 300.000 barel per hari, dapat rampung pada awal Desember 2025.
+2. Sepanjang 9-12 November 2025, Kementerian ESDM mendorong pemerataan distribusi BBM dan mengatasi isu pasokan SPBU swasta yang kuota impornya telah habis. BP-AKR telah membeli 100.000 barel base fuel dari Pertamina Patra Niaga dan berencana menambah pembelian 200.000 barel, melalui skema business to business. Sementara itu, Shell dan Vivo masih dalam tahap negosiasi pembelian base fuel dari Pertamina.
+3. Pada 13 November 2025, Kementerian ESDM menyatakan akan mendorong penerapan bensin campuran 10% etanol (E10) pada tahun 2028, dengan kebutuhan etanol diperkirakan mencapai 1,4 juta kiloliter pada 2027. Implementasi E10 menghadapi tantangan seperti ketersediaan bahan baku dan infrastruktur produksi, serta usulan pembebasan etanol bahan bakar dari cukai sebesar Rp20.000 per liter oleh Asosiasi Produsen Spiritus dan Etanol Indonesia (Apsendo) untuk mencegah kenaikan harga produk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1. Proyek Refinery Development Master Plan Balikpapan menunjukkan kemajuan signifikan dengan pengoperasian awal unit Residual Fluid Catalytic Cracking pada 10 November 2025, menargetkan peresmian pada pertengahan Desember 2025. Investasi sebesar US$7.4 miliar (Rp126 triliun) ini akan meningkatkan kapasitas produksi menjadi 360.000 barel per hari, memenuhi 22-25% kebutuhan energi nasional, dan memangkas ketergantungan impor bahan bakar minyak (BBM) sebesar 10-15% serta avtur mulai tahun 2026. Kilang ini juga akan menghasilkan produk berstandar Euro V dan petrokimia bernilai tinggi.
+2. Pertamina Patra Niaga mencatat peningkatan signifikan pada penjualan produk non-subsidi hingga Oktober 2025, dengan Pertamax Turbo naik 76% secara tahunan dan Pertamax Green 95 naik 80% dibandingkan 2024, yang menyebabkan Pertamina harus menambah pasokan Pertamax Turbo melalui produksi kilang dan impor. Sementara itu, penyaluran BBM bersubsidi seperti Pertalite dan Solar terkendali di bawah kuota masing-masing 10% dan 1.5% dari target 2025, menunjukkan pergeseran konsumen ke BBM beroktan lebih tinggi dan potensi penghematan kompensasi sebesar Rp12.61 triliun.
+3. Harga minyak mentah global mengalami penurunan dengan West Texas Intermediate (WTI) diperdagangkan di atas US$59 per barel dan Brent di bawah US$64 per barel, didorong oleh kenaikan persediaan bensin dan distillate di Amerika Serikat. Di sisi lain, sanksi Amerika Serikat terhadap produsen minyak Rusia dan Iran menghambat aliran minyak mentah ke China dan India, meskipun ketersediaan BBM nasional dipastikan aman dengan cadangan 18-19 hari. Untuk memenuhi permintaan domestik, operator SPBU BP-AKR juga mengandalkan pasokan base fuel dari Pertamina Patra Niaga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina (Persero) dan anak usahanya, PT Pertamina Patra Niaga (PPN), memperkuat pasokan dan distribusi bahan bakar minyak (BBM) serta LPG menjelang libur Natal 2025 dan Tahun Baru 2026 (Nataru), dengan proyeksi kenaikan konsumsi gasoline 2.3% dan LPG 3.3%. PPN menambah 1.4 juta kiloliter (kl) Pertalite dan memastikan ketahanan stok nasional BBM rata-rata 20.2 hari. Selain itu, stok BBM di SPBU swasta seperti Vivo, BP-AKR, dan Shell secara bertahap kembali tersedia mulai 23 November 2025, setelah membeli base fuel dari PPN. Vivo dan BP-AKR menyerap total 100.000 barel dan 230.000 barel base fuel, sementara Shell telah menyepakati pembelian 100.000 barel base fuel dari PPN.
+2. Pemerintah RI mulai menerapkan skema pembayaran dana kompensasi BBM bersubsidi secara bulanan (70% per bulan) kepada Pertamina efektif 19 November 2025, menggantikan pola kuartalan, yang diperkirakan akan memperkuat likuiditas Pertamina. BPH Migas merencanakan revisi Perpres Nomor 191 Tahun 2014 untuk mengatur tata kelola penjualan Pertalite agar lebih tepat sasaran. Pertamina Patra Niaga juga mempertimbangkan peluang impor Pertalite dari Amerika Serikat sebagai bagian dari strategi pengadaan, menunggu arahan pemerintah.
+3. PT Kilang Pertamina Internasional (KPI) Unit Balikpapan memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari pada 10 November 2025, bertujuan meningkatkan produksi produk bernilai tinggi dan mengurangi impor BBM. Selain itu, PT AGPA Refinery Complex (ARC) berkapasitas 500.000 ton per tahun di Balikpapan diresmikan pada 21 November 2025 sebagai fasilitas hilir sawit nasional baru, mendukung transformasi energi terbarukan berbasis kelapa sawit. Upaya menjaga operasional kilang Pertamina sebagai objek vital nasional diperkuat dengan pengerahan personel TNI dan BAIS mulai Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.  Pertamina Patra Niaga dan operator SPBU swasta seperti Shell, BP, serta Vivo menyesuaikan harga produk kilang nonsubsidi mereka per 1 Desember 2025, yang secara kompak mengalami kenaikan mengacu pada formula harga pemerintah dan tren harga minyak dunia. Namun, khusus tiga wilayah terdampak bencana di Aceh, Sumatra Utara, dan Sumatra Barat, harga BBM nonsubsidi relatif tidak mengalami penyesuaian signifikan. Terkait kinerja ekspor, Badan Pusat Statistik mencatat nilai ekspor Indonesia pada Oktober 2025 mencapai US$24,24 miliar, turun 2,31% dibanding tahun sebelumnya, terutama disebabkan oleh penurunan ekspor bahan bakar mineral sebesar 19,04% nilai dan 7,26% volume.
+2.  Pemerintah dan Pertamina Group mengintensifkan upaya penyaluran dan distribusi energi untuk wilayah Sumatra yang terdampak bencana banjir dan longsor di Aceh, Sumatra Utara, dan Sumatra Barat, serta dalam rangka persiapan periode Natal 2025 dan Tahun Baru 2026 (Nataru). Langkah-langkah yang diambil meliputi pengerahan armada tanker oleh PTPertamina International Shipping, penggunaan moda transportasi beragam seperti pesawat Hercules dan perintis untuk pengiriman BBM ke daerah terisolasi, serta peniadaan sementara sistem barcode MyPertamina untuk pembelian BBM subsidi di daerah bencana. Pertamina Patra Niaga juga berhasil menyuplai total 430.000 barel base fuel kepada SPBU swasta (Shell, BP-AKR, Vivo) untuk menormalisasi kembali ketersediaan BBM mereka.
+3.  Dalam pengembangan industri kilang, PT Kilang Pertamina Internasional (KPI) berkomitmen meningkatkan produksi petrokimia, dengan proyek Refinery Development Master Plan Balikpapan yang akan menghasilkan propilena sekitar 225.000 ton per tahun untuk mengurangi ketergantungan impor. Selain itu, pemerintah berencana merombak skema subsidi energi (BBM dan listrik) dalam dua tahun ke depan untuk meningkatkan efisiensi dan ketepatan sasaran. Pertamina Patra Niaga juga mempertimbangkan opsi impor Pertalite dari Amerika Serikat yang direncanakan mencapai 40% dari total pengadaan, sebagai bagian dari strategi ketahanan energi nasional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1. Kementerian Energi dan Sumber Daya Mineral (ESDM) melaporkan devisa negara hilang Rp523 triliun per tahun akibat impor minyak dan Bahan Bakar Minyak (BBM), dengan produksi minyak Indonesia 221 juta barel pada 2024 berbanding impor 313 juta barel. Sebagai upaya penahanan laju impor, Pertamina Patra Niaga telah menyalurkan 430.000 barel base fuel kepada SPBU swasta, mengakhiri kekosongan stok sejak akhir Agustus 2025. Kementerian ESDM juga akan memutuskan kuota impor BBM untuk SPBU swasta pada tahun 2026.
+2. Pertamina Patra Niaga menaikkan harga BBM nonsubsidi per 1 Desember 2025, seperti Pertamax (RON 92) menjadi Rp12.750 per liter dari sebelumnya Rp12.200 per liter, sejalan dengan tren harga minyak global dan nilai tukar rupiah terhadap dolar Amerika Serikat. SPBU swasta juga melakukan penyesuaian harga serupa. Untuk periode Natal 2025 dan Tahun Baru 2026 (Nataru), Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan gasolin 5% dan avtur 1,6%, serta memberikan diskon avtur rata-rata 10% di 37 bandara strategis mulai 22 Desember 2025.
+3. Kilang Pertamina Internasional (KPI) mempercepat proyek Refinery Development Master Plan (RDMP) Balikpapan untuk meningkatkan kapasitas pengolahan minyak mentah dari 260.000 barel menjadi 360.000 barel per hari, dengan target operasi komersial pada 17 Desember 2025. Proyek ini bernilai US$7,4 miliar. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban, yang bernilai US$20,7 miliar hingga US$24 miliar, diharapkan diputuskan antara Pertamina dan Rosneft Singapore Pte Ltd pada pertengahan Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina Patra Niaga (PPN) menyalurkan 100.000 barel bahan bakar dasar impor kepada BP-AKR untuk menormalisasi pasokan BBM di SPBU swasta, dengan 100.000 barel tambahan diperkirakan tiba pada pekan ketiga November 2025. Badan usaha swasta lainnya, termasuk Vivo dan Shell, masih dalam tahap negosiasi untuk pembelian bahan bakar dasar dari Pertamina.
+2. Per 01 November 2025, Pertamina menaikkan harga Dexlite dan Pertamina Dex sebesar Rp200 per liter, menjadi Rp13.900 per liter dan Rp14.200 per liter. Pada periode yang sama, Shell dan BP-AKR juga menyesuaikan harga BBM, dengan mayoritas jenis bensin turun dan jenis diesel naik.
+3. Terkait dugaan masalah kualitas Pertalite di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM melakukan pengecekan di sekitar 300 SPBU. Hasil sementara menunjukkan bahwa Pertalite yang disalurkan "on specification" tanpa kontaminasi air atau etanol, dan Pertamina telah membuka 32 posko pengaduan serta bengkel rekanan untuk memberikan solusi dan kompensasi kepada masyarakat yang terdampak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.  Pemerintah daerah Sumatra Barat dan Pertamina Patra Niaga telah mengambil langkah cepat untuk memulihkan kelangkaan bahan bakar minyak di wilayah tersebut pada November 2025, dengan Pertamina mempercepat pasokan melalui jalur darat dan mengoperasikan Integrated Terminal Teluk Kabung 24 jam sehari sejak 7 November 2025, yang meningkatkan kecepatan penyaluran sekitar 16%. Di sisi lain, Kementerian Energi dan Sumber Daya Mineral mendorong SPBU swasta untuk membeli base fuel dari Pertamina Patra Niaga untuk mengatasi ketimpangan pasokan, di mana BP-AKR telah sepakat membeli dua kargo atau 200.000 barel base fuel, dengan indikasi akan menambah pesanan hingga 300.000 barel, sementara Shell dan Vivo masih dalam tahap negosiasi.
+2.  Kementerian Keuangan mengawal penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan yang ditargetkan meningkatkan kapasitas produksi bahan bakar minyak hingga 142.000 barel per hari, LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun, dengan nilai investasi mencapai US$7,4 miliar. PT Kilang Pertamina Internasional telah melakukan pengoperasian awal Unit Residual Fluid Catalytic Cracking Complex di RDMP Balikpapan pada 10 November 2025, yang berhasil meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari dan produksi LPG menjadi 43.000 ton per tahun. Sementara itu, keputusan investasi akhir atau Final Investment Decision (FID) proyek Kilang Tuban berkapasitas 300.000 barel per hari dengan Rosneft ditargetkan rampung pada awal Desember 2025.
+3.  Kementerian Energi dan Sumber Daya Mineral mendorong penerapan bensin campuran 10% etanol (E10) pada 2028, atau berpotensi dipercepat menjadi 2027, dengan kebutuhan etanol mencapai 1,4 juta hingga 4 juta kiloliter. Proyek ini menghadapi tantangan seperti ketersediaan bahan baku, keterbatasan insentif, dan infrastruktur distribusi yang belum memadai, serta usulan dari Asosiasi Produsen Spiritus dan Etanol Indonesia untuk membebaskan etanol dari kategori barang kena cukai sebesar Rp20.000 per liter agar tidak membebani harga bensin hijau bagi konsumen. Pemerintah juga mencari keterlibatan sektor swasta, dengan Toyota Indonesia menunjukkan minat untuk mengembangkan pabrik bioetanol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.  Penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan senilai 7.4 miliar USD ditargetkan pada pertengahan Desember 2025. Proyek ini akan meningkatkan kapasitas kilang dari 260.000 barel per hari (bph) menjadi 360.000 bph, berpotensi mengurangi ketergantungan impor Bahan Bakar Minyak (BBM) hingga 15% dan memenuhi 22%-25% kebutuhan energi domestik. Unit Residual Fluid Catalytic Cracking (RFCC) Complex dengan kapasitas 90.000 bph telah mulai beroperasi pada 10 November 2025.
+2.  PT Pertamina Patra Niaga mencatat volume penjualan bensin dan solar sebesar 87 juta kiloliter (KL) per Oktober 2025, dengan 41% berasal dari produk non-subsidi. Penyaluran Solar bersubsidi terkendali 1.5% di bawah kuota 18.8 juta KL dan Pertalite 10% di bawah kuota 31.2 juta KL hingga Oktober 2025. Permintaan Pertamax Turbo (RON 98) melonjak 76%, sehingga Pertamina menambah pasokan melalui impor dan memastikan kesiapan distribusi untuk periode Natal dan Tahun Baru 2025-2026.
+3.  Dalam pengembangan biofuel, penjualan Pertamax Green 95 (E5) di 168 SPBU Pertamina mencatat pertumbuhan 80% dari 2024, dengan proyeksi kebutuhan bioetanol 4,800-5,000 KL per tahun untuk Pulau Jawa. Asosiasi Produsen Spiritus dan Etanol Indonesia (Aspendo) mengusulkan penghapusan cukai bioetanol fuel grade sebesar Rp20.000 per liter untuk menjaga harga kompetitif. Sementara itu, BP-AKR membeli 100.000 barel base fuel dari Pertamina Patra Niaga untuk mengatasi kekurangan stok, sedangkan Shell dan Vivo masih dalam negosiasi business-to-business untuk pengadaan base fuel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina Patra Niaga memperkuat pasokan BBM untuk periode Natal 2025 dan Tahun Baru 2026. Ini mencakup penambahan 1,4 juta kiloliter Pertalite dari produksi kilang domestik dan impor baru, dengan target ketahanan stok 21-23 hari per 25 November 2025. Kilang Pertamina Internasional juga memulai operasi awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari di Kilang Balikpapan sejak 10 November 2025, yang akan meningkatkan produksi gasoline dan LPG serta mengurangi impor.
+2. Pasokan BBM di SPBU swasta mulai normal kembali setelah mencapai kesepakatan pembelian base fuel dari Pertamina Patra Niaga. Vivo Energy Indonesia telah menerima 100.000 barel Revvo 92 (RON 92) yang mulai tersedia bertahap sejak 23 November 2025. BP-AKR menambah pembelian base fuel menjadi total 230.000 barel dari Pertamina Patra Niaga per 27 November 2025. Shell Indonesia juga menyelesaikan kesepakatan pada 25 November 2025 untuk membeli 100.000 barel base fuel, dengan harapan stok pulih akhir November 2025.
+3. Distribusi energi menghadapi tantangan cuaca ekstrem dan diperkuat dengan langkah keamanan. Dua kapal pengangkut Pertalite dan Biosolar tidak dapat bersandar di Belawan, Sumatra Utara sejak 23 November 2025 karena cuaca ekstrem, menyebabkan penyesuaian pola suplai dari terminal alternatif. Untuk mengamankan infrastruktur energi nasional, pemerintah akan mengerahkan personel TNI untuk menjaga kilang minyak dan terminal BBM Pertamina yang memiliki kapasitas pengolahan 1 juta barel per hari dan 231 terminal migas, dimulai pada Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Kilang Pertamina Internasional (KPI) menargetkan produksi untuk November 2025 sebesar 8 juta barel gasoline, 10,7 juta barel gasoil, dan 2,2 juta barel avtur. Untuk Desember 2025, produksi gasoil seri ditingkatkan menjadi sekitar 11,5 juta barel, sementara volume gasoline dan avtur dipertahankan sesuai rencana November 2025 guna mendukung kelancaran pasokan BBM menjelang periode Natal dan Tahun Baru 2026.
+2. Badan Pusat Statistik (BPS) mencatat volume ekspor bahan bakar mineral (BBM) Indonesia turun sebesar 7,26% pada Oktober 2025 dibandingkan periode yang sama tahun lalu. Penurunan ini merupakan bagian dari total ekspor migas yang turun 33,60% secara tahunan menjadi US$0,89 miliar.
+3. PT Pertamina Patra Niaga (PPN) memasok total 430.000 barel base fuel kepada badan usaha SPBU swasta seperti Shell, Vivo, dan BP-AKR untuk memastikan ketersediaan BBM. PPN juga memproyeksikan peningkatan konsumsi gasoline sebesar 8,4% dan avtur sebesar 2,4% selama periode Nataru 2025/2026 di wilayah Jawa Timur, Bali, dan Nusa Tenggara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.  Kementerian Energi dan Sumber Daya Mineral melaporkan Indonesia kehilangan devisa sebesar Rp523 triliun per tahun akibat impor minyak. Pada 2024, produksi minyak Indonesia mencapai 221 juta barel, sementara impor minyak nasional sebesar 313 juta barel yang mencakup 112 juta barel minyak mentah dan 201 juta barel Bahan Bakar Minyak (BBM), dengan konsumsi BBM nasional sebesar 532 juta barel. Pemerintah berupaya mengurangi ketergantungan impor melalui kebijakan seperti implementasi B50 pada 2026 dan campuran etanol 10% pada 2027, serta menolak permintaan tambahan kuota impor BBM dari SPBU swasta pada 2025 dengan mengarahkan pembelian base fuel dari PT Pertamina Patra Niaga.
+2.  Proyek Refinery Development Master Plan (RDMP) Balikpapan dijadwalkan beroperasi komersial pada 17 Desember 2025, dengan peningkatan kapasitas unit distilasi minyak mentah (CDU) dari 260.000 barel per hari (bph) menjadi 360.000 bph, yang akan meningkatkan total kapasitas CDU nasional dari 1.17 juta bph menjadi 1.26 juta bph pada akhir 2025. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban yang bernilai sekitar US$20.7 miliar hingga US$24 miliar, dengan PJSC Rosneft Oil Company sebagai mitra utama, ditargetkan rampung pada akhir Desember 2025. PT Pertamina Patra Niaga juga telah menyalurkan total 430.000 barel base fuel kepada SPBU swasta per Desember 2025 untuk mengatasi kekosongan stok sebelumnya.
+3.  Distribusi BBM dan LPG di Aceh, Sumatra Utara, dan Sumatra Barat menghadapi tantangan akibat bencana alam, mendorong PT Pertamina Patra Niaga untuk mengoptimalkan berbagai moda transportasi termasuk jalur udara menggunakan pesawat Air Tractor guna memastikan pasokan energi mencapai wilayah terisolir. Kementerian Energi dan Sumber Daya Mineral memperpanjang relaksasi pembelian BBM subsidi tanpa penggunaan QR code di wilayah terdampak bencana hingga akhir Desember 2025. Selain itu, harga BBM nonsubsidi dari Pertamina, Shell, BP-AKR, dan Vivo mengalami penyesuaian kenaikan per 1 Desember 2025. Menjelang Natal dan Tahun Baru 2026, Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan BBM jenis gasolin sebesar 5% dan avtur 1.6%, serta penurunan gasoil sebesar 4% di wilayah Jawa Tengah-DI Yogyakarta.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="11.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Tanggal awal</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Tanggal akhir</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Summary Data</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>45961</v>
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1169,89 +2420,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>45968</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Berikut ringkasan umum berita bioenergi antara tanggal 01 November 2025 dan 07 November 2025:
-1.  Ekspor CPO dan produk turunannya menunjukkan pertumbuhan yang positif. Badan Pusat Statistik (BPS) mencatat nilai ekspor CPO dan turunannya pada Januari-September 2025 naik 32,40% menjadi US$18,14 miliar, dengan volume meningkat 11,62% menjadi 17,58 juta ton. Wilayah Sumatera Utara juga melaporkan kenaikan ekspor keseluruhan sebesar 18,90% hingga September 2025, dengan CPO menjadi penyumbang utama. Meskipun demikian, harga CPO di Bursa Malaysia mengalami fluktuasi, sempat menurun ke level terendah dalam hampir empat bulan di awal November, namun menunjukkan sedikit pemulihan menjelang akhir pekan, dipengaruhi oleh pasokan yang melimpah dan pergerakan harga minyak nabati pesaing.
-2.  Pemerintah terus mendorong pengembangan bioenergi dengan rencana mandatori biodiesel B50 pada 2026. Kementerian ESDM memproyeksikan kebijakan ini dapat menghasilkan surplus pasokan solar domestik dan mengeliminasi impor solar, didukung oleh penyelesaian proyek kilang RDMP Balikpapan pada November 2025. Namun, asosiasi pertambangan seperti APBI dan Perhapi menyatakan kekhawatiran tentang potensi peningkatan biaya operasional dan isu teknis pada peralatan berat akibat implementasi B50. Di sisi lain, PT Perusahaan Gas Negara Tbk. (PGAS) telah memulai pembangunan titik injeksi biomethane dari limbah kelapa sawit (POME) di Sumatera Selatan, dengan target pengurangan emisi gas rumah kaca yang berarti.
-3.  Kinerja perusahaan sawit menunjukkan pertumbuhan yang kuat. PT Astra Agro Lestari Tbk. (AALI) mencatatkan kenaikan pendapatan 35,8% dan laba bersih 33% pada kuartal III-2025, didorong oleh peningkatan produksi dan harga CPO. Emiten CPO Grup Salim, PT Salim Ivomas Pratama Tbk. (SIMP) dan PT PP London Sumatra Indonesia Tbk. (LSIP), juga melaporkan pertumbuhan pendapatan dan laba bersih yang didukung oleh harga jual rata-rata yang lebih tinggi. Perusahaan juga menunjukkan komitmen pada keberlanjutan, seperti investasi AALI pada fasilitas penangkap metana dan program Sawit Terampil Sinar Mas Agribusiness and Food yang mendukung petani swadaya untuk memperoleh sertifikasi RSPO. Akademisi dan industri otomotif juga menyepakati percepatan mandatori bioetanol E10 dan biodiesel untuk transisi energi.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pada periode 2025-11-01–2025-11-07, rata-rata CPO 13853.67 dan rata-rata Biodiesel 14036.00.Periode ini mengalami penurunan 5.02% nilai CPO dan kenaikan 0.63% biodiesel dibanding week sebelumnya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1. Pemerintah Indonesia mendorong implementasi program biodiesel B50 pada semester II/2026, yang instruksi percepatannya datang dari Presiden. Program ini dihadapkan pada tantangan ketersediaan bahan baku CPO yang belum memadai, kebutuhan metanol yang tinggi yang masih mengandalkan impor, serta hasil uji coba awal yang menunjukkan potensi dampak teknis pada kendaraan seperti umur filter yang lebih singkat dan daya mesin yang sedikit lebih rendah. Kementerian ESDM berencana memulai uji jalan B50 secara menyeluruh pada awal Desember 2025, dan Badan Pengelola Dana Perkebunan (BPDP) sedang mengkaji skema subsidi fleksibel untuk mengantisipasi gejolak harga.
-2. Harga minyak sawit mentah (CPO) di pasar global menunjukkan fluktuasi, dengan kecenderungan penurunan pada beberapa waktu terakhir yang dipengaruhi oleh tingginya pasokan di Malaysia. Namun, kalangan analis memproyeksikan harga CPO akan menguat pada 2026, didorong oleh pertumbuhan produksi yang mulai melambat dan antisipasi peningkatan permintaan dari program biodiesel. Kebijakan B50 ini juga menimbulkan kekhawatiran bagi negara pengimpor utama seperti India, yang sedang mencari strategi untuk mengamankan pasokan CPO mereka.
-3. Di sektor bioenergi dan turunan sawit, terdapat beberapa perkembangan positif dalam upaya hilirisasi dan keberlanjutan. PGN memulai pembangunan titik injeksi biomethane dari limbah kelapa sawit di Sumatra Selatan. PTPN IV PalmCo melaporkan peningkatan laba bersih dan pendapatan yang signifikan berkat peningkatan produktivitas dan efisiensi operasional. Selain itu, Kawasan Ekonomi Khusus (KEK) Maloy Batuta Trans Kalimantan menarik investasi besar untuk industri oleofood, dan program co-firing biomassa pada pembangkit listrik tenaga uap (PLTU) telah diterapkan di 47 lokasi, menunjukkan peningkatan pemanfaatan biomassa.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pada periode 2025-11-08 sampai 2025-11-14, rata-rata CPO 13768.75 dan rata-rata Biodiesel 14036.00.Periode ini mengalami penurunan 0.61% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>45982</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1.  Pemerintah Indonesia memastikan akan melanjutkan program mandatori biodiesel langsung ke B50 pada semester II-2026, tanpa transisi B45. Uji jalan B50 dijadwalkan dimulai awal Desember 2025 untuk berbagai sektor. Hasil uji laboratorium awal B50 menunjukkan potensi penurunan kinerja mesin dan mempercepat penggantian filter. Kebutuhan FAME untuk B50 diprediksi meningkat sekitar 4 juta kiloliter, memicu diskusi mengenai opsi pasokan CPO seperti pembatasan ekspor. Analis pasar dan asosiasi petani menyuarakan kekhawatiran terkait potensi lonjakan harga CPO dan dampaknya terhadap harga tandan buah segar (TBS) petani jika produksi tidak mencukupi.
-2.  Emiten kelapa sawit di Indonesia menunjukkan perbaikan kinerja keuangan hingga kuartal III-2025 dan diproyeksikan akan memberikan dividen yang lebih tinggi. Beberapa perusahaan melakukan aksi korporasi, seperti PT Sawit Sumbermas Sarana Tbk. (SSMS) yang memperoleh fasilitas kredit sindikasi Rp5,2 triliun untuk akuisisi dan ekspansi. Sementara itu, POSCO International Corporation mengakuisisi 65,721% saham PT Sampoerna Agro Tbk. (SGRO), yang kemudian mendivestasi bisnis sagunya untuk fokus pada kelapa sawit. PTPN IV PalmCo juga membukukan kenaikan laba bersih 49% pada 2024 dan menyetor dividen Rp1,5 triliun.
-3.  Harga minyak sawit mentah (CPO) di Bursa Malaysia menunjukkan pergerakan yang berfluktuasi, sempat menguat selama lima hari berturut-turut sebelum terkoreksi, dipengaruhi oleh data stok CPO Malaysia yang meningkat dan ekspektasi permintaan yang melemah. Di sisi lain, harga TBS petani di Sumatra Utara mulai menunjukkan perbaikan setelah beberapa minggu mengalami penurunan. Inisiatif keberlanjutan juga dilakukan, seperti peluncuran benih sawit toleran kekeringan oleh Sinar Mas Agribusiness and Food dan panduan ESG oleh BNI untuk sektor perkebunan sawit.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pada periode 2025-11-15 sampai 2025-11-21, rata-rata CPO 14020.60 dan rata-rata Biodiesel 14036.00.Periode ini mengalami kenaikan 1.83% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>45989</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.  Pengembangan hilirisasi dan investasi di sektor kelapa sawit terus berlanjut di Indonesia, ditandai dengan peresmian PT AGPA Refinery Complex (ARC) di Balikpapan yang berkapasitas 500.000 ton per tahun sebagai kolaborasi Indonesia-Korea Selatan untuk energi terbarukan berbasis sawit. Selain itu, POSCO International mengakuisisi saham mayoritas PT Sampoerna Agro Tbk (SGRO), menambah lahan sawitnya menjadi total 150.000 hektare untuk memperkuat rantai pasok bahan baku biofuel, sementara PT Sawit Sumbermas Sarana Tbk (SSMS) juga mengakuisisi PT Sawit Mandiri Lestari senilai Rp1,6 triliun guna memperbesar skala usaha.
-2.  Data produksi dan perdagangan menunjukkan pergerakan turun pada September 2025, dengan produksi minyak kelapa sawit mentah (CPO) dan minyak inti sawit (PKO) menurun masing-masing sebesar 22,32% dan 24% dibandingkan bulan sebelumnya. Konsumsi domestik, khususnya biodiesel, juga mengalami penurunan sebesar 3,69%, dan total ekspor produk sawit merosot 36,65%. Meskipun demikian, produksi CPO dan PKO secara tahun berjalan (Year-on-Year) hingga September 2025 menunjukkan kenaikan 11,30%, dan nilai ekspor secara kumulatif juga lebih tinggi dibandingkan periode yang sama tahun sebelumnya karena peningkatan harga rata-rata CPO.
-3.  Harga CPO di pasar global mengalami fluktuasi selama periode ini; harga menunjukkan penurunan berturut-turut di awal pekan, mencapai level terendah sejak Juli, yang dipengaruhi oleh ekspektasi penurunan permintaan, penguatan mata uang ringgit, dan koreksi harga minyak nabati pesaing. Namun, harga CPO kemudian berbalik arah dan naik pada pertengahan hingga akhir periode, didukung oleh potensi technical rebound dan kekhawatiran akan gangguan pasokan akibat cuaca buruk di negara-negara produsen. Bersamaan dengan itu, Menteri Koordinator Bidang Pangan menyatakan bahwa menanam kelapa kini dapat lebih menguntungkan dibandingkan kelapa sawit karena peningkatan permintaan ekspor dan potensi hilirisasi kelapa di dalam negeri.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pada periode 2025-11-22 sampai 2025-11-28, rata-rata CPO 14061.25 dan rata-rata Biodiesel 14036.00.Periode ini mengalami kenaikan 0.29% nilai CPO dan kenaikan 0.00% biodiesel dibanding week sebelumnya.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1261,106 +2431,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Tanggal awal</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Tanggal akhir</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Summary Data</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>45961</v>
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>45968</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1. Harga minyak mentah global mengalami tekanan penurunan sepanjang minggu pertama November 2025 akibat kekhawatiran kelebihan pasokan dan lemahnya permintaan, khususnya dari Amerika Serikat. Harga Brent diperdagangkan di sekitar US$63-US$64 per barel, dan West Texas Intermediate (WTI) mendekati US$60 per barel, dengan WTI anjlok sekitar 16-17% secara tahun berjalan. Stok minyak mentah AS menunjukkan kenaikan signifikan, dengan laporan API sebesar 6.5 juta barel dan EIA sebesar 5.2 juta barel pada pekan lalu.
-2. OPEC+ memutuskan untuk menghentikan sementara rencana kenaikan produksi pada kuartal I 2026, setelah peningkatan moderat pada Desember, sebagai upaya menyeimbangkan pasar dan meredam volatilitas. Morgan Stanley menaikkan proyeksi harga Brent menjadi US$60 per barel untuk semester I 2026 dari US$57.50. Namun, proyeksi tekanan harga tetap ada, dengan Capital Economics memperkirakan Brent mencapai US$60 per barel pada akhir 2025 dan US$50 per barel pada akhir 2026.
-3. Sanksi AS terhadap produsen minyak utama Rusia (Rosneft PJSC dan Lukoil PJSC) mengakibatkan kilang-kilang di China menghentikan pembelian minyak mentah Rusia, mempengaruhi sekitar 400.000 barel per hari atau 45% dari total impor Rusia ke China. Kondisi pasar yang cukup pasokan ini mendorong Arab Saudi untuk memangkas harga jual minyak mentah utamanya untuk pembeli Asia pada Desember, termasuk Arab Light yang dipangkas US$1.20 per barel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1. Harga minyak global menunjukkan kenaikan, dengan Brent di atas USD64 per barel dan West Texas Intermediate di sekitar USD60 per barel, didukung oleh perkembangan positif di Amerika Serikat. Kenaikan ini terjadi setelah harga minyak mentah turun dalam lima dari enam pekan terakhir karena kekhawatiran kelebihan pasokan. Pasar sedang menantikan rilis data pasokan dan permintaan dari OPEC, IEA, dan EIA pekan ini, sementara OPEC dan sekutunya berencana menunda kenaikan produksi pada kuartal pertama tahun depan untuk mengelola pasokan.
-2. Produksi minyak mentah Rusia sedikit meningkat pada Oktober menjadi rata-rata 9.411 mb/d, 43.000 b/d lebih tinggi dari September, namun masih 70.000 b/d di bawah kuota OPEC+ yang mencakup pemotongan kompensasi. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena beberapa kilang di India, China, dan Turki enggan menerima pasokan yang terkena sanksi.
-3. India, sebagai importir minyak mentah terbesar ketiga di dunia, mengurangi pembelian minyak dari Rusia untuk pengiriman Desember sebagai dampak sanksi Barat dan negosiasi dagang dengan Amerika Serikat. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia India tahun ini, tidak mengajukan pesanan untuk bulan tersebut. Pergeseran ini mendorong India untuk mencari pasokan alternatif dari kawasan Amerika dan Timur Tengah, mengingat sekitar 36% dari total impor minyak mentah India tahun ini berasal dari Rusia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>45982</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1. Indonesia sedang menyiapkan Peraturan Presiden yang memperbolehkan PT Pertamina (Persero) untuk mengimpor energi langsung dari perusahaan Amerika Serikat tanpa proses lelang. Kebijakan ini merupakan tindak lanjut dari kesepakatan tarif timbal balik antara AS dan Indonesia pada Juli 2025, dengan tujuan mengurangi defisit perdagangan AS dengan Indonesia yang sekitar US$18 miliar, dan mengakselerasi komitmen impor minyak Indonesia dari AS senilai US$15 miliar. PT Kilang Pertamina Internasional (KPI) mencari cara agar impor minyak mentah dari AS dapat lebih ekonomis, dan pemerintah berencana meningkatkan impor minyak mentah dari AS mulai Desember 2025.
-2. Harga minyak global terkoreksi di pekan ini, dengan harga berjangka Brent turun US$1,63 (2,5%) menjadi US$63,26 per barel dan West Texas Intermediate (WTI) melemah US$1,56 (2,6%) menjadi US$59,18 per barel pada 20 November 2025. Penurunan ini dipengaruhi oleh laporan upaya AS untuk mengakhiri perang Rusia-Ukraina, yang berpotensi meningkatkan pasokan minyak Rusia ke pasar. Bersamaan dengan itu, sanksi AS terhadap Rosneft dan Lukoil mulai berlaku pada 21 November 2025, berpotensi membuat hampir 48 juta barel minyak mentah Rusia terlantar di laut dan mendorong pembeli di Asia mencari pasokan alternatif.
-3. Harga minyak mentah Indonesia (ICP) untuk Oktober 2025 ditetapkan sebesar US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya. Penurunan ini disebabkan oleh beberapa faktor seperti peningkatan suplai minyak oleh OPEC+ sebesar 137.000 barel per hari untuk November 2025, berkurangnya ketegangan geopolitik di Timur Tengah, pengolahan minyak mentah global yang diperkirakan mencapai titik terendah musiman 81,6 juta barel per hari pada Oktober, penguatan nilai tukar dolar AS, serta pemotongan harga jual resmi minyak mentah Arab Saudi untuk pembeli di Asia di tengah melemahnya permintaan dan perlambatan ekonomi Tiongkok.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>45989</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.  Harga minyak menunjukkan tekanan turun selama minggu ini, dengan Brent diperdagangkan di kisaran USD 62-63 per barel dan WTI Crude di kisaran USD 58-59 per barel. Prediksi dari bank investasi seperti Goldman Sachs memperkirakan WTI Crude akan rata-rata USD 53 per barel pada 2026, sementara JP Morgan memproyeksikan Brent dapat turun ke kisaran USD 30-an per barel pada 2027 karena kekhawatiran pasokan berlebih sebesar 2 juta barel per hari. Harga bensin eceran di Amerika Serikat turun di bawah USD 3 per galon di banyak negara bagian, dengan beberapa lokasi mencapai USD 1.99 per galon.
-2.  Pasokan minyak global tetap kuat, didorong oleh produksi yang tangguh dari produsen non-OPEC seperti Amerika Serikat, Brasil, dan Guyana. Meskipun eksekutif shale AS melaporkan tantangan profitabilitas di bawah USD 60 per barel dan kenaikan biaya pengeboran sebesar 5 hingga 10 persen dari tahun lalu, produksi shale AS terus meningkat. OPEC+ diperkirakan akan mempertahankan tingkat produksi saat ini pada pertemuan tanggal 30 November, menunda peningkatan produksi yang direncanakan untuk kuartal I 2026 akibat kekhawatiran peningkatan persediaan global.
-3.  Pembicaraan damai yang diperbarui antara Rusia dan Ukraina memberikan tekanan signifikan pada harga minyak karena potensi pelonggaran sanksi yang dapat meningkatkan pasokan Rusia. Di sisi lain, konferensi energi di Timur Tengah menampilkan pandangan yang berbeda, dengan ADIPEC menyoroti permintaan energi jangka panjang yang kuat dan kebutuhan investasi besar USD 18.2 triliun untuk mencapai 123 juta barel per hari pada 2050, sementara Dii Desert Energy Summit berfokus pada percepatan pertumbuhan energi rendah karbon dan investasi yang melampaui bahan bakar fosil dengan rasio 2 berbanding 1. Cina terus mempercepat pembelian minyak mentah strategisnya, mengimpor sekitar 2.15 juta barel per hari dari Rusia dan menimbun lebih dari 1 juta barel per hari pada beberapa bulan di tahun 2025.</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1370,8 +2485,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1396,75 +2511,245 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>45961</v>
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>45968</v>
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45992</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.  OPEC+ mengumumkan penghentian sementara kenaikan produksi pada kuartal I-2026 setelah kenaikan moderat pada Desember, sebagai upaya menyeimbangkan pasar di tengah tanda-tanda kelebihan pasokan. Morgan Stanley menaikkan proyeksi harga Brent menjadi USD60/bbl untuk semester I-2026, namun mencatat peningkatan produksi OPEC+ sebesar 500.000 bph dari Maret hingga Oktober jauh di bawah kenaikan kuota 2,6 mb/d.
-2.  Harga minyak mentah global melemah dan mencatat penurunan mingguan kedua, tertekan oleh peningkatan pasokan dari OPEC+ serta produsen non-anggota seperti Amerika Serikat dan Brasil. Brent turun menjadi sekitar USD63/bbl dan WTI di bawah USD60/bbl, dengan WTI anjlok sekitar 16% hingga 17% sepanjang tahun ini. Data American Petroleum Institute (API) menunjukkan stok minyak mentah Amerika Serikat naik 6,5 juta barel pada pekan lalu.
-3.  Kilang-kilang minyak di China, termasuk milik negara dan swasta, menghentikan pembelian minyak mentah asal Rusia setelah Amerika Serikat menjatuhkan sanksi terhadap produsen utama Moskow, memengaruhi sekitar 400.000 bpd atau hampir 45% dari total impor minyak Rusia ke China. Menanggapi pasar yang cukup mendapat pasokan dan lemahnya permintaan di Asia, Saudi Aramco memangkas harga minyak mentah unggulannya, Arab Light, untuk pasar Asia pada Desember sebesar USD1.20/bbl.</t>
+          <t>1. Pada 1 Desember 2025, nilai tukar rupiah di pasar spot menguat 0.07% menjadi Rp 16.663 per dolar AS pada penutupan perdagangan, setelah dibuka menguat 0.10% pada level Rp 16.658 per dolar AS. Sebaliknya, kurs rupiah Jisdor melemah 0.04% menjadi Rp 16.668 per dolar AS.
+2. Sentimen yang mempengaruhi pergerakan rupiah meliputi berlanjutnya surplus neraca perdagangan Indonesia pada Oktober 2025 meskipun menyempit, penurunan ekspor batu bara untuk pertama kalinya sejak tahun lalu, serta arus keluar dana asing dari pasar saham dan obligasi negara hingga November 2025. Dari sisi eksternal, pasar mencermati data ekonomi AS yang beragam dan ekspektasi pelonggaran kebijakan moneter The Fed pada Desember 2025, dengan probabilitas pemotongan suku bunga 25 basis poin mencapai sekitar 85%.
+3. Gubernur Bank Indonesia pada akhir pekan lalu menyatakan fokus pada stabilitas nilai tukar dan dukungan pemulihan ekonomi, serta mempertimbangkan penurunan suku bunga acuan jika inflasi terkendali. Meskipun demikian, rupiah telah melemah lebih dari 3% sepanjang tahun ini, menjadikannya mata uang dengan kinerja terburuk di Asia Tenggara.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45975</v>
+      <c r="A4" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Produksi minyak mentah Rusia pada Oktober mencapai rata-rata 9.411 juta barel per hari, meningkat 43.000 barel per hari dari September. Angka ini 70.000 barel per hari di bawah kuota OPEC+ yang mencakup pemotongan kompensasi, dengan target yang dibutuhkan sebesar 9.481 juta barel per hari. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena keengganan beberapa kilang di India, China, dan Turki untuk menerima minyak yang terkena sanksi.
-2. Harga minyak global menunjukkan kenaikan, dengan Brent melewati US$64 per barel dan West Texas Intermediate (WTI) bergerak di kisaran US$60 per barel, didorong oleh upaya mengakhiri penutupan pemerintahan Amerika Serikat. Kekhawatiran akan kelebihan pasokan masih membebani pasar, menyebabkan harga minyak mentah turun dalam lima dari enam pekan terakhir. Organisasi Negara-Negara Pengekspor Minyak (OPEC) dan sekutunya mulai melonggarkan pembatasan produksi, namun berencana menunda kenaikan output pada kuartal pertama tahun depan, sementara produsen non-OPEC termasuk Amerika Serikat terus menambah pasokan.
-3. India, importir minyak terbesar ketiga di dunia, mengurangi pembelian minyak mentah dari Rusia untuk pengiriman Desember. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia tahun ini, belum mengajukan pesanan. Perubahan pola pembelian ini sebagian besar didorong oleh sanksi Barat terhadap produsen minyak Rusia dan negosiasi dagang dengan Amerika Serikat, di mana India berkomitmen membeli lebih banyak minyak mentah dari Amerika Serikat. Akibatnya, kilang-kilang di India mulai mencari alternatif pasokan dari kawasan Amerika dan Timur Tengah, dengan Indian Oil Corp. berupaya membeli hingga 24 juta barel dari Amerika untuk pengiriman Januari hingga Maret.</t>
+          <t>1. Pada 2 Desember 2025, nilai tukar rupiah menguat Rp 38 atau 0,23% di pasar spot menjadi Rp 16.625 per dolar AS, menjadikannya mata uang Asia dengan penguatan terbesar hari itu. Sementara itu, indeks dolar AS menguat tipis 0,01% menjadi 99,42 setelah enam hari pelemahan beruntun.
+2. Pasar memperkirakan probabilitas 87% The Federal Reserve akan memangkas suku bunga sebesar 25 basis poin pada pertemuan kebijakan moneter yang dijadwalkan pada 9-10 Desember 2025, berkontribusi pada pelemahan dolar AS di awal Desember.
+3. Indonesia mencatat surplus perdagangan sebesar US$2,39 miliar pada Oktober 2025, melanjutkan tren surplus selama 66 bulan berturut-turut. Indeks PMI manufaktur Indonesia juga meningkat menjadi 53,3 pada November 2025, menandakan ekspansi selama empat bulan beruntun, sementara Kementerian Keuangan menggelar lelang surat berharga negara (SBN) dengan target indikatif Rp 23 triliun.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>45982</v>
+      <c r="A5" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Indonesia berkomitmen untuk meningkatkan impor minyak mentah dari Amerika Serikat hingga US$15 miliar mulai Desember 2025, sebagai bagian dari kesepakatan tarif timbal balik. PT Pertamina (Persero) melalui anak usahanya PT Kilang Pertamina Internasional (KPI) berupaya mencari skema ekonomis untuk impor ini, dengan regulasi baru yang memungkinkan pembelian langsung tanpa lelang dari perusahaan AS.
-2. Harga minyak mentah global mengalami koreksi, dengan Brent turun 2,5% ke US$63,26 per barel dan WTI melemah 2,6% menjadi US$59,18 per barel pada 20 November 2025, dipicu laporan potensi berakhirnya perang Rusia-Ukraina dan peningkatan pasokan OPEC+ sebesar 137.000 barel per hari mulai November 2025. Harga Minyak Mentah Indonesia (ICP) Oktober 2025 ditetapkan US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya.
-3. Sanksi Amerika Serikat terhadap produsen minyak Rusia Rosneft PJSC dan Lukoil PJSC yang berlaku pada 21 November 2025 berpotensi menyebabkan hampir 48 juta barel minyak mentah Rusia terlantar di laut, memaksa pembeli di Asia mencari pasokan alternatif dan kapal tanker mencari tujuan baru di tengah tekanan untuk mematuhi sanksi.</t>
+          <t>1. Pada tanggal 3 Desember 2025, nilai tukar rupiah melemah terhadap dolar Amerika Serikat di pasar spot dan pembukaan perdagangan. Rupiah ditutup pada Rp 16.628 per dolar AS, melemah 0.02%, setelah sempat dibuka melemah 0.04% ke posisi Rp 16.632 per dolar AS.
+2. Pelemahan rupiah didorong oleh ekspektasi global terhadap pelonggaran suku bunga The Fed sebesar 25 basis poin pada Desember 2025 dengan probabilitas 87.4%. Dari dalam negeri, laju inflasi nasional pada November 2025 menunjukkan pelemahan menjadi 0.17% secara bulanan dan 2.72% secara tahunan.
+3. Lelang Surat Berharga Negara sebelumnya mencatat permintaan tinggi sebesar Rp 69.64 triliun. Namun, pemerintah hanya memenangkan Rp 23 triliun sesuai target awal, karena imbal hasil yang diminta investor terus meningkat. Imbal hasil rata-rata SBN tenor 10 tahun seri FR108 mencapai 6.24%, naik dari 6.06% pada lelang sebelumnya di 18 November.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>45989</v>
+      <c r="A6" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.  Pada 27 November 2025, harga minyak Brent naik 0.2% menjadi USD 63.34 per barel dan West Texas Intermediate (WTI) menguat 0.8% menjadi USD 59.10 per barel. Kenaikan ini dipicu oleh harapan terobosan pembicaraan perdamaian antara Rusia dan Ukraina, yang menetralkan kekhawatiran pasokan akibat sanksi baru AS terhadap produsen Rusia.
-2.  Organisasi Negara-Negara Pengekspor Minyak dan sekutunya (OPEC+) diperkirakan akan mempertahankan tingkat produksi pada pertemuan mendatang. Selain itu, delapan negara anggota OPEC+ yang secara bertahap meningkatkan produksi pada tahun 2025 diproyeksikan untuk mempertahankan kebijakan jeda kenaikan produksi pada kuartal I 2026.
-3.  Ekspektasi pemangkasan suku bunga acuan oleh The Federal Reserve pada Desember 2025 turut mendorong harga minyak, mengingat penurunan suku bunga dapat mendukung pertumbuhan ekonomi global dan memperkuat permintaan minyak.</t>
+          <t>1.  Nilai tukar rupiah melemah terhadap dolar Amerika Serikat pada 04 Desember 2025. Kurs rupiah di pasar spot melemah Rp25 atau 0,15% menjadi Rp16.653 per dolar AS, dan kurs Jisdor melemah Rp14 atau 0,08% menjadi Rp16.646 per dolar AS. Rupiah juga dibuka melemah 0,06% di level Rp16.638 per dolar AS menurut Bloomberg, dan ditutup melemah 0,15% di level yang sama.
+2.  Indeks dolar AS (DXY) terpantau menguat tipis 0,08%-0,10% di level 98,93-98,95. Sentimen global didominasi ekspektasi pemangkasan suku bunga Federal Reserve (The Fed) sebesar 25 basis poin pada pertemuan 09-10 Desember dengan probabilitas sekitar 89%-90%, didukung data ekonomi AS yang melemah. Mayoritas mata uang Asia lainnya juga melemah terhadap dolar AS.
+3.  Bank Indonesia (BI) menegaskan komitmennya untuk menjaga stabilitas nilai tukar rupiah melalui intervensi terukur di pasar domestik dan luar negeri, seperti diungkapkan oleh Deputi Gubernur Senior BI Destry Damayanti. BI mempertahankan suku bunga kebijakan untuk menjaga daya tarik rupiah di tengah mandat untuk mendorong pertumbuhan ekonomi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1. Pada 5 Desember 2025, nilai tukar rupiah di pasar spot menguat tipis 0,03% atau Rp 5 menjadi Rp 16.648 per dolar Amerika Serikat (AS), sementara kurs rupiah Jisdor melemah 0,05% atau Rp 9 menjadi Rp 16.655 per dolar AS. Bank Indonesia melaporkan cadangan devisa pada November 2025 naik menjadi US$ 150,06 miliar, meningkat dari US$ 149,93 miliar pada Oktober 2025.
+2. Pergerakan nilai tukar rupiah dipengaruhi oleh sentimen eksternal berupa spekulasi pelonggaran moneter oleh Federal Reserve AS, dengan probabilitas pemangkasan suku bunga mendekati 90% berdasarkan CME FedWatch setelah data ketenagakerjaan swasta AS menyusut 32.000 pada November. Indeks dolar AS terpantau melemah 0,09% ke posisi 98,89 pada akhir perdagangan.
+3. Dari sisi domestik, proyeksi pertumbuhan ekonomi Indonesia pada 2025 diperkirakan mencapai 5%–5,1%, yang lebih rendah dari target Asumsi Ekonomi Makro APBN 2025 sebesar 5,2%. Meskipun demikian, indikator ekonomi seperti Purchasing Managers’ Index manufaktur naik menjadi 53,3 dan indeks keyakinan konsumen mencatat posisi tertinggi dalam lima bulan terakhir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Pada Senin, 8 Desember 2025, nilai tukar rupiah terhadap dolar AS dibuka melemah 0,20% ke Rp16.682 dan terdepresiasi hingga 0,28% ke Rp16.695, setelah pada Jumat, 5 Desember 2025, ditutup menguat 5 poin ke Rp16.648 per dolar AS.
+2. Pasar berekspektasi Federal Reserve akan memangkas suku bunga sebesar 25 basis poin pada Desember 2025 didorong data pasar tenaga kerja AS yang melemah, meskipun pejabat masih terpecah pandangannya. Selain itu, kegagalan perundingan AS-Rusia terkait gencatan senjata Ukraina turut menjadi sentimen global.
+3. Bank Indonesia mencatat posisi cadangan devisa Indonesia pada akhir November 2025 meningkat menjadi US$150.1 miliar, setara dengan pembiayaan 6.2 bulan impor. Transaksi berjalan tahun 2025 diproyeksikan berada dalam kisaran surplus 0.1% hingga defisit 0.7% terhadap produk domestik bruto, menunjukkan ketahanan eksternal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1. Nilai tukar rupiah pada 9 Desember 2025 bergerak fluktuatif, dibuka melemah 0,01% ke Rp16.697 per dolar AS namun kemudian ditutup menguat 0,12% ke Rp16.675,5 per dolar AS, dengan indeks dolar AS juga terapresiasi 0,02% ke 99,10.
+2. Pasar global didorong oleh ekspektasi pemangkasan suku bunga Federal Reserve sebesar 25 basis poin dengan probabilitas sekitar 87% pada 10 Desember 2025, meskipun ada sinyal kehati-hatian dari pejabat The Fed dan fokus pasar pada laporan ketenagakerjaan AS yang tertunda.
+3. Bank Indonesia memproyeksikan transaksi berjalan Indonesia 2025 dalam kisaran surplus 0,1% hingga defisit 0,7% terhadap PDB, sementara Kementerian Keuangan menyiapkan aturan baru untuk memperketat pengelolaan pendapatan ekspor komoditas, dengan catatan lonjakan utang luar negeri jangka pendek Indonesia pada 2024 sebesar 29,1% menjadi US$65,12 miliar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1. Pada 10 Desember 2025, nilai tukar rupiah terhadap dolar AS dibuka melemah 0,10% ke level Rp16.692 per dolar AS dan ditutup melemah 0,07% ke Rp16.688 per dolar AS. Indeks dolar AS pada waktu yang sama menunjukkan pergerakan menguat 0,02% saat pembukaan dan kemudian turun 0,12% saat penutupan.
+2. Sentimen pasar hari itu dipengaruhi oleh ekspektasi pasar berjangka sebesar 87% untuk pemangkasan suku bunga The Fed sebesar 25 basis poin pada 10 Desember 2025 serta fokus pada laporan ketenagakerjaan AS. Dari dalam negeri, lonjakan utang luar negeri jangka pendek Indonesia pada 2024 sebesar 29,1% menjadi US$65,12 miliar, yang sebagian dipicu oleh agresivitas penerbitan Sekuritas Rupiah Bank Indonesia (SRBI), juga menjadi perhatian.
+3. Secara historis, rupiah sempat mencatat level terlemah sepanjang sejarah pada April 2025 di Rp17.217 per dolar AS, melampaui rekor terendah krisis 1998 di kisaran Rp16.800 per dolar AS. Pelemahan signifikan pada April 2025 tersebut dipicu oleh kebijakan tarif impor resiprokal sebesar 32% oleh pemerintah AS terhadap barang-barang Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1. Nilai tukar rupiah menunjukkan pergerakan beragam pada 11 Desember 2025, dibuka menguat ke Rp16.667 per dolar AS setelah Bank Sentral Amerika Serikat (The Fed) memangkas suku bunga acuan sebesar 25 basis poin menjadi 3.50%-3.75%. Namun, rupiah diperkirakan akan ditutup melemah di rentang Rp16.680-Rp16.720, sementara Bank Indonesia diproyeksikan mempertahankan BI-Rate di 4.75% untuk menjaga stabilitas.
+2. Pemerintah Indonesia merevisi kebijakan Devisa Hasil Ekspor Sumber Daya Alam (DHE SDA) yang berlaku mulai 1 Januari 2026, mewajibkan penempatan 100% dana di bank Himbara selama minimal 12 bulan dan membatasi konversi ke Rupiah maksimal 50%. Asosiasi Pengusaha Indonesia (APINDO) memproyeksikan pertumbuhan ekonomi Indonesia pada 2026 sebesar 5%-5.4% dan nilai tukar rupiah akan bergerak melemah moderat di kisaran Rp16.500-Rp16.900 per dolar AS.
+3. Rencana pensiun dini Pembangkit Listrik Tenaga Uap (PLTU) Cirebon-1 dibatalkan karena pertimbangan teknis, meskipun komitmen pendanaan Just Energy Transition Partnership (JETP) untuk Indonesia meningkat menjadi US$21.4 miliar. Kementerian Energi dan Sumber Daya Mineral (ESDM) memperkirakan kebutuhan investasi sebesar US$618 miliar hingga tahun 2040 untuk proyek hilirisasi, yang diproyeksikan menciptakan 3 juta lapangan kerja baru dan meningkatkan nilai ekspor nikel menjadi US$33.9 miliar pada 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1. Pada 12 Desember 2025, nilai tukar rupiah dibuka menguat 0,04% ke Rp16.669 per dolar AS dan ditutup menguat 0,18% ke Rp16.635 per dolar AS, didukung oleh pemangkasan suku bunga The Fed sebesar 25 basis poin menjadi 3,50%-3,75% serta rencana injeksi likuiditas The Fed sebesar US$55 miliar. Namun, Bank Pembangunan Asia (ADB) memangkas proyeksi pertumbuhan ekonomi Indonesia 2025 menjadi 4,9% dari 5% dan 2026 menjadi 5% dari 5,1%.
+2. Goldman Sachs Group Inc. menilai yuan China (CNY) undervalued sebesar 25% dari nilai wajarnya, dengan proyeksi nilai wajar sekitar CNY 5/US$ dibandingkan level pasar saat ini CNY 7,064/US$. Yuan telah menguat 3,23% year-to-date sepanjang 2025, dari CNY 7,30/US$ menjadi CNY 7,064/US$ pada 10 Desember 2025.
+3. Perundingan tarif resiprokal antara Indonesia dan Amerika Serikat berisiko gagal, berpotensi mengembalikan tarif impor Indonesia ke AS menjadi sekitar 32% dan membebani daya saing ekspor. Emiten yang sangat terdampak termasuk PT Integra Indocabinet Tbk (WOOD) dengan 90,27% penjualan ekspor ke AS pada akhir 2024 dan PT Panca Mitra Multiperdana Tbk (PMMP) dengan 66,80% penjualan ekspor ke AS hingga September 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.  Rupiah menguat 0,18% ke Rp 16.635 per dolar AS pada penutupan perdagangan 12 Desember 2025, stabil sepanjang pekan tersebut. Penguatan ini terjadi di tengah pelemahan indeks dolar AS (DXY) sebesar 0,6% dalam sepekan, menyusul keputusan Federal Reserve memangkas suku bunga acuan sebesar 25 basis poin pada 10 Desember 2025. Federal Reserve juga mengumumkan rencana pembelian surat utang pemerintah jangka pendek senilai sekitar 55 miliar dolar AS mulai 12 Desember 2025 untuk injeksi likuiditas.
+2.  Nilai tukar rupiah melemah 0,49% menjadi Rp 208,6 per rubel pada penutupan perdagangan 12 Desember 2025. Secara year-to-date, rupiah mengalami depresiasi sekitar 47,2% terhadap rubel, didorong oleh penguatan signifikan rubel sebesar 30% terhadap dolar AS sepanjang tahun ini. Penguatan rubel didukung kebijakan Bank Sentral Rusia mempertahankan suku bunga tinggi di 20% dan pengetatan capital controls. Defisit dagang Indonesia dengan Rusia mencapai 882 juta dolar AS dari Januari hingga Oktober 2025.
+3.  Rupiah diproyeksikan akan bergerak fluktuatif namun melemah di rentang Rp 16.640 hingga Rp 16.700 per dolar AS pada 15 Desember 2025. Prediksi ini mempertimbangkan data klaim pengangguran awal AS yang meningkat menjadi 236.000 pada pekan yang berakhir 6 Desember 2025. Dari dalam negeri, pemerintah Indonesia tengah menyiapkan paket kebijakan ekonomi untuk pemulihan pascabencana dan restrukturisasi kredit usaha rakyat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1. Asia-Pasifik meningkatkan penerbitan obligasi dalam denominasi euro hingga mencapai rekor 23% dari total penerbitan mata uang gabungan pada tahun 2025, naik enam poin persentase dari tahun 2024, sebagai upaya diversifikasi dari konsentrasi dolar AS dan memanfaatkan biaya pendanaan yang lebih rendah. Total penjualan obligasi euro oleh perusahaan dan pemerintah meningkat 75% menjadi 86.4 miliar euro pada tahun 2025, sementara dolar AS merosot 11% terhadap euro.
+2. Pasar tenaga kerja dan konsumsi Amerika Serikat menunjukkan pelemahan pada September dan Oktober 2025, dengan penjualan ritel AS hanya naik 0.2% bulan ke bulan pada September dan tingkat pengangguran AS naik ke 4.4% pada Oktober, tertinggi sejak Oktober 2021. Data inflasi inti AS pada November tercatat melambat menjadi 3% tahun ke tahun, di bawah ekspektasi pasar, yang berpotensi memperkuat ekspektasi akhir siklus pengetatan moneter Federal Reserve.
+3. Bank Indonesia akan mengadakan Rapat Dewan Gubernur (RDG) pada 16-17 Desember 2025 untuk menjaga stabilitas nilai tukar, inflasi, dan arus modal asing di tengah rilis Statistik Utang Luar Negeri Indonesia (SULNI) Oktober 2025. Pada saat yang sama, data ekonomi dari Tiongkok, termasuk produksi industri dan penjualan ritel Oktober 2025, serta inflasi Jepang pada November yang mencapai 3.0% tahun ke tahun, menunjukkan adanya dinamika ekonomi regional yang perlu dicermati pasar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1. Pada 15 Desember 2025, nilai tukar rupiah terhadap dolar AS berfluktuasi dan ditutup melemah di kisaran Rp16.660 hingga Rp16.667 per dolar AS, terdepresiasi sekitar 0,12% hingga 0,15%. Indeks dolar AS menunjukkan pergerakan tipis di sekitar level 98,36 hingga 98,40, sementara mayoritas mata uang Asia menunjukkan penguatan.
+2. The Federal Reserve telah memangkas suku bunga acuannya sebesar 25 basis poin menjadi 3,50% hingga 3,75% dan mengumumkan rencana pembelian obligasi pemerintah jangka pendek sekitar US$40 miliar per bulan. Bank Indonesia merilis Statistik Utang Luar Negeri Indonesia periode Oktober 2025 sebesar US$423,9 miliar, serta akan mengadakan Rapat Dewan Gubernur pada 16-17 Desember 2025.
+3. Sentimen pasar dipengaruhi oleh peningkatan klaim pengangguran awal di AS menjadi 236.000 untuk pekan yang berakhir 6 Desember, serta peringatan Bank Indonesia tentang risiko krisis global yang didorong oleh akumulasi utang publik global mencapai US$110,9 triliun atau 94,6% dari PDB dunia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1. Pada 16 Desember 2025, nilai tukar rupiah dibuka melemah 0,06% ke level Rp16.677 per dolar AS dan ditutup terdepresiasi 0,15% ke level Rp16.685 per dolar AS, di tengah pelemahan tipis indeks dolar AS (DXY) di sekitar 98,28. Mayoritas mata uang Asia menunjukkan pergerakan yang beragam terhadap dolar AS sepanjang hari.
+2. Bank Indonesia memulai Rapat Dewan Gubernur (RDG) pada 16 Desember 2025, dengan konsensus pasar terbagi antara menahan atau memangkas suku bunga acuan BI-Rate, menyusul pemangkasan suku bunga The Federal Reserve sebesar 25 basis poin menjadi 3,50-3,75% pada pekan sebelumnya. Bank Indonesia juga melakukan penyesuaian operasional sistem pembayaran dengan memperpanjang jam layanan untuk penutupan buku akhir tahun 2025.
+3. Pelemahan nilai tukar rupiah sepanjang tahun 2025, dengan depresiasi berkisar 4,33% terhadap yen Jepang hingga 13,50% terhadap baht Thailand, menyebabkan peningkatan biaya perjalanan ke luar negeri bagi wisatawan Indonesia. Sementara itu, inflasi domestik November 2025 tercatat 0,17% secara bulanan dan 2,72% secara tahunan, masih dalam rentang target Bank Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1. Bank Indonesia (BI) mempertahankan BI Rate pada level 4,75% pada 17 Desember 2025, dengan deposit facility 3,75% dan lending facility 5,5%. Keputusan ini bertujuan untuk menjaga stabilitas nilai tukar rupiah di tengah ketidakpastian global serta mendukung pertumbuhan ekonomi, meskipun BI telah memangkas suku bunga acuan sebanyak 125 basis poin sepanjang tahun 2025.
+2. Nilai tukar rupiah menunjukkan pergerakan yang fluktuatif namun relatif stabil pada 17 Desember 2025, bergerak di rentang Rp16.660 hingga Rp16.705 per dolar AS, dengan penutupan di sekitar Rp16.680 per dolar AS. Stabilitas ini didukung oleh intervensi BI di pasar valuta asing dan pembelian Surat Berharga Negara (SBN), serta masuknya dana asing ke pasar domestik, meskipun indeks dolar AS (DXY) menguat karena kenaikan imbal hasil US Treasury.
+3. Transaksi tanpa dolar AS melalui skema Local Currency Settlement (LCS) Indonesia mencapai US$22,13 miliar atau setara Rp369,56 triliun (kurs Rp16.699/US$) per November 2025, meningkat signifikan dari US$12,5 miliar pada periode yang sama tahun sebelumnya. Korea Selatan dan Uni Emirat Arab (UEA) bergabung sebagai negara mitra LCS pada 2025, sementara India, Singapura, dan Hong Kong sedang dalam proses penjajakan kerja sama, dengan Tiongkok (64%) dan Jepang (17,8%) mendominasi total transaksi.</t>
         </is>
       </c>
     </row>
@@ -1479,8 +2764,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1505,75 +2790,230 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>45961</v>
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>45968</v>
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45992</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Pada 1 November 2025, beberapa operator SPBU di Indonesia melakukan penyesuaian harga Bahan Bakar Minyak (BBM). PT Pertamina (Persero) menaikkan harga Dexlite dan Pertamina Dex masing-masing sebesar Rp200 per liter menjadi Rp13.900/liter dan Rp14.200/liter, sementara harga Pertamax, Pertamax Turbo, dan Pertamax Green tetap tidak berubah. SPBU Shell dan BP-AKR mayoritas menurunkan harga produk bensin mereka seperti Shell Super (turun Rp210 menjadi Rp12.680/liter) dan BP 92 (turun Rp210 menjadi Rp12.680/liter), namun menaikkan harga produk diesel mereka.
-2. PT Pertamina Patra Niaga telah menyalurkan 100.000 barel base fuel RON 92 kepada BP-AKR (PT Aneka Petroindo Raya) melalui mekanisme bisnis-ke-bisnis, yang memungkinkan ketersediaan kembali BBM BP 92 di jaringan SPBU BP-AKR. BP-AKR diperkirakan akan membeli tambahan 100.000 barel base fuel lagi yang dijadwalkan tiba pada pekan ketiga November 2025. Kementerian ESDM melaporkan PT Vivo Energy Indonesia juga hampir mencapai kesepakatan untuk pembelian sekitar 100.000 barel base fuel, sedangkan negosiasi dengan Shell Indonesia masih berlangsung.
-3. Menanggapi dugaan masalah kualitas BBM Pertalite yang menyebabkan keluhan kendaraan "brebet" di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM telah memeriksa hampir 300 SPBU dan hasil sementara menunjukkan tidak ada kontaminasi air atau etanol. Pertamina juga membuka posko pengaduan dan menyediakan 32 bengkel rekanan untuk perbaikan gratis bagi konsumen yang terdampak. Sementara itu, Kilang Pertamina Internasional (KPI) di Cilacap melanjutkan inisiatif energi hijau, meningkatkan produksi gasoline RON 92 menjadi 53.000 barel per hari dan memproduksi bahan bakar nabati (HVO serta PertaminaSAF).</t>
+          <t>1. Pada 1 Desember 2025, Indeks Harga Saham Gabungan (IHSG) menguat 0,47% menjadi 8.548,79, melanjutkan kinerja positif setelah kenaikan 4,22% sepanjang November 2025 yang mencetak rekor All Time High (ATH) penutupan 8.602,13 dan ATH intraday 8.622,27. Pada hari tersebut, investor asing mencatatkan jual bersih senilai Rp120,38 miliar, sementara arus dana asing secara bulanan pada November 2025 mencapai beli bersih sebesar Rp17,9 triliun.
+2. Penguatan IHSG didorong oleh saham-saham berkapitalisasi besar seperti TLKM, DSSA, SRAJ, BBCA, BBNI, dan BMRI. Sentimen positif dari ekspektasi penurunan suku bunga Federal Reserve sebesar 25 basis poin pada Desember 2025, serta potensi window dressing dan stimulus Nataru domestik menjadi faktor pendorong pasar. Namun, risiko bencana banjir di Sumatra dapat memicu inflasi volatile food dan komoditas, yang berpotensi membatasi ruang gerak Bank Indonesia.
+3. Untuk pekan ini, analis memprediksi IHSG akan bergerak pada kisaran 8.470-8.600 dengan target penguatan hingga 8.660. Investor akan memantau rilis data ekonomi domestik seperti PMI manufaktur, neraca perdagangan, inflasi, dan cadangan devisa, serta data ekonomi global termasuk indeks PCE prices AS dan PMI China. Emiten seperti BBCA dan TOWR juga mengumumkan pembagian dividen interim masing-masing sebesar Rp55 dan Rp6,87 per saham.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45975</v>
+      <c r="A4" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Pada 10 November 2025, PT Kilang Pertamina Internasional (KPI) memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) Complex hasil Proyek Refinery Development Master Plan (RDMP) Balikpapan. Proyek ini akan meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari, serta memproduksi bahan bakar standar Euro V, tambahan LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun. Di samping itu, PT Pertamina (Persero) menargetkan keputusan investasi akhir (FID) proyek Kilang Tuban senilai US$24 miliar, dengan kapasitas 300.000 barel per hari, dapat rampung pada awal Desember 2025.
-2. Sepanjang 9-12 November 2025, Kementerian ESDM mendorong pemerataan distribusi BBM dan mengatasi isu pasokan SPBU swasta yang kuota impornya telah habis. BP-AKR telah membeli 100.000 barel base fuel dari Pertamina Patra Niaga dan berencana menambah pembelian 200.000 barel, melalui skema business to business. Sementara itu, Shell dan Vivo masih dalam tahap negosiasi pembelian base fuel dari Pertamina.
-3. Pada 13 November 2025, Kementerian ESDM menyatakan akan mendorong penerapan bensin campuran 10% etanol (E10) pada tahun 2028, dengan kebutuhan etanol diperkirakan mencapai 1,4 juta kiloliter pada 2027. Implementasi E10 menghadapi tantangan seperti ketersediaan bahan baku dan infrastruktur produksi, serta usulan pembebasan etanol bahan bakar dari cukai sebesar Rp20.000 per liter oleh Asosiasi Produsen Spiritus dan Etanol Indonesia (Apsendo) untuk mencegah kenaikan harga produk.</t>
+          <t>1. Indeks Harga Saham Gabungan (IHSG) ditutup menguat 0.80% atau 68.25 poin mencapai rekor tertinggi baru 8,617.04 pada perdagangan 2 Desember 2025, dengan kapitalisasi pasar mencapai Rp15.842 triliun. Investor asing mencatat beli bersih Rp454.01 miliar di seluruh pasar.
+2. Analis memproyeksikan IHSG akan mencapai 8,700 hingga 8,900 jelang penutupan tahun 2025, didukung sentimen musiman window dressing, kebijakan likuiditas Bank Indonesia, serta ekspektasi sinyal dovish dari Federal Reserve. Data ekonomi domestik menunjukkan Manufacturing PMI November naik menjadi 53.3 dan inflasi November melambat menjadi 2.72% secara tahunan.
+3. Untuk tahun 2026, JP Morgan menargetkan IHSG pada skenario dasar 9.100 dan skenario optimistis 10.000, didorong oleh belanja fiskal yang lebih tinggi, pelonggaran moneter lanjutan, dan perbaikan kondisi makro global. Sektor-sektor yang diunggulkan adalah Industrials, Materials, Consumer Staples, Consumer Discretionary, dan Property.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>45982</v>
+      <c r="A5" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Proyek Refinery Development Master Plan Balikpapan menunjukkan kemajuan signifikan dengan pengoperasian awal unit Residual Fluid Catalytic Cracking pada 10 November 2025, menargetkan peresmian pada pertengahan Desember 2025. Investasi sebesar US$7.4 miliar (Rp126 triliun) ini akan meningkatkan kapasitas produksi menjadi 360.000 barel per hari, memenuhi 22-25% kebutuhan energi nasional, dan memangkas ketergantungan impor bahan bakar minyak (BBM) sebesar 10-15% serta avtur mulai tahun 2026. Kilang ini juga akan menghasilkan produk berstandar Euro V dan petrokimia bernilai tinggi.
-2. Pertamina Patra Niaga mencatat peningkatan signifikan pada penjualan produk non-subsidi hingga Oktober 2025, dengan Pertamax Turbo naik 76% secara tahunan dan Pertamax Green 95 naik 80% dibandingkan 2024, yang menyebabkan Pertamina harus menambah pasokan Pertamax Turbo melalui produksi kilang dan impor. Sementara itu, penyaluran BBM bersubsidi seperti Pertalite dan Solar terkendali di bawah kuota masing-masing 10% dan 1.5% dari target 2025, menunjukkan pergeseran konsumen ke BBM beroktan lebih tinggi dan potensi penghematan kompensasi sebesar Rp12.61 triliun.
-3. Harga minyak mentah global mengalami penurunan dengan West Texas Intermediate (WTI) diperdagangkan di atas US$59 per barel dan Brent di bawah US$64 per barel, didorong oleh kenaikan persediaan bensin dan distillate di Amerika Serikat. Di sisi lain, sanksi Amerika Serikat terhadap produsen minyak Rusia dan Iran menghambat aliran minyak mentah ke China dan India, meskipun ketersediaan BBM nasional dipastikan aman dengan cadangan 18-19 hari. Untuk memenuhi permintaan domestik, operator SPBU BP-AKR juga mengandalkan pasokan base fuel dari Pertamina Patra Niaga.</t>
+          <t>1. Pada 3 Desember 2025, Indeks Harga Saham Gabungan (IHSG) melemah tipis 0,06% menjadi 8.611,79 setelah sempat menguat di sesi pagi. Investor asing mencatat beli bersih Rp70,25 miliar di seluruh pasar, meskipun di pasar reguler terjadi jual bersih Rp229,60 miliar. Sehari sebelumnya pada 2 Desember 2025, IHSG mencapai rekor tertinggi sepanjang masa baru di 8.617,04, naik 0,80% dengan kapitalisasi pasar Rp15.842 triliun.
+2. Analis memproyeksikan IHSG berpotensi menguat pada Desember 2025 hingga Januari 2026 didukung fenomena santa claus rally dan janury effect, dengan target 8.940 untuk 2025-2026 dan 9.050 hingga 9.350 untuk 2026. Pertumbuhan ekonomi domestik kuartal IV 2025 diperkirakan mencapai 5,4%-5,6% dengan inflasi terkendali 1,5%-3,5%, serta adanya stimulus fiskal pemerintah senilai total Rp60 triliun. Investor domestik menopang pasar saham dan obligasi sepanjang tahun, meskipun investor asing mencatat jual bersih Rp29,24 triliun year to date.
+3. Otoritas Jasa Keuangan (OJK) mengusulkan perubahan kebijakan free float saham untuk meningkatkan likuiditas pasar modal, mengingat rata-rata free float di Bursa Efek Indonesia sebesar 23,9%, terendah dibanding negara kawasan. Usulan baru meliputi perhitungan free float awal hanya untuk saham yang ditawarkan kepada publik, penyesuaian kriteria minimum free float saat IPO berdasarkan kapitalisasi pasar (20% untuk &lt;Rp5 triliun, 15% untuk Rp5-50 triliun, 10% untuk &gt;Rp50 triliun), serta kewajiban mempertahankan free float minimal 1 tahun pasca-IPO. OJK juga berencana meningkatkan free float dari 7,5% menjadi kisaran 10%-15% secara bertahap dengan masa transisi 3-4 tahun.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>45989</v>
+      <c r="A6" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. PT Pertamina (Persero) dan anak usahanya, PT Pertamina Patra Niaga (PPN), memperkuat pasokan dan distribusi bahan bakar minyak (BBM) serta LPG menjelang libur Natal 2025 dan Tahun Baru 2026 (Nataru), dengan proyeksi kenaikan konsumsi gasoline 2.3% dan LPG 3.3%. PPN menambah 1.4 juta kiloliter (kl) Pertalite dan memastikan ketahanan stok nasional BBM rata-rata 20.2 hari. Selain itu, stok BBM di SPBU swasta seperti Vivo, BP-AKR, dan Shell secara bertahap kembali tersedia mulai 23 November 2025, setelah membeli base fuel dari PPN. Vivo dan BP-AKR menyerap total 100.000 barel dan 230.000 barel base fuel, sementara Shell telah menyepakati pembelian 100.000 barel base fuel dari PPN.
-2. Pemerintah RI mulai menerapkan skema pembayaran dana kompensasi BBM bersubsidi secara bulanan (70% per bulan) kepada Pertamina efektif 19 November 2025, menggantikan pola kuartalan, yang diperkirakan akan memperkuat likuiditas Pertamina. BPH Migas merencanakan revisi Perpres Nomor 191 Tahun 2014 untuk mengatur tata kelola penjualan Pertalite agar lebih tepat sasaran. Pertamina Patra Niaga juga mempertimbangkan peluang impor Pertalite dari Amerika Serikat sebagai bagian dari strategi pengadaan, menunggu arahan pemerintah.
-3. PT Kilang Pertamina Internasional (KPI) Unit Balikpapan memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari pada 10 November 2025, bertujuan meningkatkan produksi produk bernilai tinggi dan mengurangi impor BBM. Selain itu, PT AGPA Refinery Complex (ARC) berkapasitas 500.000 ton per tahun di Balikpapan diresmikan pada 21 November 2025 sebagai fasilitas hilir sawit nasional baru, mendukung transformasi energi terbarukan berbasis kelapa sawit. Upaya menjaga operasional kilang Pertamina sebagai objek vital nasional diperkuat dengan pengerahan personel TNI dan BAIS mulai Desember 2025.</t>
+          <t>1. Indeks Harga Saham Gabungan (IHSG) mencapai rekor tertinggi baru pada 4 Desember 2025, ditutup pada level 8.640,19, meningkat 0,33% hari itu dan 22,04% sepanjang tahun berjalan. Investor asing mencatatkan beli bersih signifikan sebesar Rp 1,70 triliun pada hari tersebut, menunjukkan minat yang kuat terhadap pasar modal Indonesia. Berbagai sekuritas memproyeksikan penguatan IHSG berlanjut pada tahun 2026, dengan target antara 9.050 hingga 10.700, didorong oleh stabilitas ekonomi makro dan perbaikan kinerja emiten.
+2. Kebijakan moneter global diproyeksikan melonggar, dengan Federal Reserve diperkirakan akan memangkas suku bunga acuan sebesar 25 basis poin pada Desember 2025, yang dapat membuka ruang bagi Bank Indonesia untuk menurunkan suku bunga acuannya pada tahun 2026. Otoritas Jasa Keuangan (OJK) dan Bursa Efek Indonesia (BEI) sedang aktif mereformasi regulasi pasar modal, termasuk kebijakan free float saham baru dan mekanisme penjatahan IPO yang membatasi pesanan investor ritel maksimal 10% dari total saham yang ditawarkan. Menteri Keuangan juga mendesak tindakan tegas terhadap praktik manipulasi saham, menjanjikan insentif fiskal setelah pasar dibersihkan.
+3. Sektor energi dan pertambangan menunjukkan aktivitas korporasi yang tinggi, dengan PT United Tractors Tbk (UNTR) mendiversifikasi ke industri nikel, PT Energi Mega Persada Tbk (ENRG) menemukan cadangan gas baru, dan PT Bumi Resources Tbk (BUMI) melakukan beberapa akuisisi di sektor emas, tembaga, dan bauksit. Di sektor perbankan, bank-bank besar aktif dalam program pembelian kembali saham, dan ada potensi peningkatan rasio pembayaran dividen dari bank-bank BUMN pada tahun 2026. Beberapa saham emiten lain juga mengalami suspensi perdagangan oleh BEI akibat peningkatan harga kumulatif yang signifikan, sementara pasar reksa dana saham menunjukkan kinerja unggul sepanjang tahun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1. Pada 5 Desember 2025, Indeks Harga Saham Gabungan (IHSG) ditutup melemah 0,09% atau 7,44 poin ke level 8.632,76 setelah sempat mencapai rekor tertinggi baru di 8.689,1. Investor asing mencatat beli bersih Rp 380,86 miliar di seluruh pasar. Sektor industri melonjak 4,01% sementara sektor energi terkoreksi 0,69%.
+2. Pasar menantikan dua penawaran umum perdana (IPO) dari PT Abadi Lestari Indonesia Tbk. (RLCO) yang distribusinya dilakukan pada 5 Desember 2025, dan PT Super Bank Indonesia Tbk. (SUPA) yang dijadwalkan IPO pada 10-15 Desember 2025. PT Sumber Alfaria Trijaya Tbk. (AMRT) juga mengumumkan rencana pembelian kembali saham (buyback) senilai maksimal Rp1,5 triliun mulai 8 Desember 2025 hingga 6 Maret 2026.
+3. Beberapa lembaga keuangan memproyeksikan IHSG dapat menembus level 9.000 hingga 10.500 pada tahun 2026, didukung oleh stabilitas ekonomi Indonesia dengan perkiraan pertumbuhan 5,3% dan potensi pelonggaran kebijakan moneter global serta domestik. Sementara itu, Otoritas Jasa Keuangan (OJK) dan Bursa Efek Indonesia (BEI) sedang mengkaji perubahan ketentuan free float saham, dengan perkiraan kebutuhan penyerapan pasar sekitar Rp21 triliun jika dinaikkan menjadi 10% dan sekitar Rp203 triliun untuk 15%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Indeks Harga Saham Gabungan IHSG mencapai rekor tertinggi baru di 8.710,69 pada penutupan perdagangan 8 Desember 2025, menguat 0,90% dengan kapitalisasi pasar Rp16.034 triliun. Sepanjang pekan sebelumnya 1-5 Desember 2025, IHSG juga menguat 1,46% ke level 8.632,76. Para analis memprediksi IHSG berpotensi mencapai 8.900 hingga 9.000 pada akhir tahun 2025.
+2. Katalis utama penguatan pasar saham Indonesia adalah ekspektasi kuat pemangkasan suku bunga acuan oleh Federal Reserve Amerika Serikat sebesar 25 basis poin pada pertemuan 9-10 Desember 2025. Pemangkasan ini didorong oleh data tenaga kerja yang melemah dan inflasi yang terkendali, diharapkan memicu sentimen risk-on global dan pelemahan dolar AS, sehingga meningkatkan daya tarik pasar negara berkembang seperti Indonesia.
+3. Aliran modal asing ke pasar saham Indonesia tercatat net buy sebesar Rp2,48 triliun pada pekan pertama Desember 2025, meningkat dari Rp992,41 miliar pada pekan terakhir November 2025. Arus masuk modal ini didukung oleh data ekonomi makro domestik yang positif, termasuk PMI Manufaktur November 2025 yang ekspansif di 53,3 dan inflasi yang terjaga di level 2,72%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1. Pada tanggal 9 Desember 2025, Indeks Harga Saham Gabungan (IHSG) ditutup melemah 0,61% pada level 8.657,17-8.657,18, meskipun sempat menyentuh rekor tertinggi intraday 8.749. Indeks Bisnis-27 juga melemah 0,8% ke level 546,9. Kapitalisasi pasar tercatat sekitar Rp15.909 triliun hingga Rp15.939 triliun. Saham-saham seperti ADRO, ADMR, BBCA, BMRI, MEDC, PTRO, dan TLKM menunjukkan pelemahan, sementara BUMI, BBRI, BBNI, dan UNTR menguat.
+2. Pergerakan pasar saham dipengaruhi ekspektasi pertemuan The Fed yang diperkirakan akan menurunkan suku bunga sebesar 25 basis poin menjadi 3,75% pada Desember 2025. Mandiri Sekuritas memproyeksikan IHSG dapat mencapai 9.000 dalam waktu dekat dan berpotensi mencapai 9.050 hingga 9.350 pada tahun 2026, didorong oleh aktivitas investor ritel dan sektor-sektor kunci seperti konsumer, perbankan, telekomunikasi, ritel, serta pertambangan emas dan tembaga. Data ekonomi domestik seperti penjualan sepeda motor yang tumbuh dan proyeksi peningkatan Indeks Keyakinan Konsumen serta penjualan ritel menjadi katalis positif.
+3. Prospek ekonomi yang solid dan likuiditas pasar modal yang bergairah pada tahun 2026, didukung oleh potensi pemangkasan suku bunga acuan The Fed dan BI Rate, menciptakan momentum yang ideal untuk penawaran umum perdana atau IPO. UOB Sekuritas mencatat kondisi ini didukung peredaran uang yang stabil, perbaikan indeks manufaktur, dan aliran modal ekuitas, sementara regulasi free float diharapkan meningkatkan kualitas pasar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1. Indeks Harga Saham Gabungan (IHSG) menguat 22,90% secara year to date hingga 10 Desember 2025, dengan penutupan hari tersebut menguat 0,51% ke level 8.700,92. Penguatan ini didorong oleh saham-saham afiliasi konglomerat seperti DSSA yang naik 195,95% dan BRPT yang menguat 304,35% secara year to date, serta didukung oleh kenaikan sektor energi dan infrastruktur pada perdagangan harian.
+2. Pasar menantikan hasil pertemuan Federal Reserve Amerika Serikat yang diperkirakan akan memangkas suku bunga acuan sebesar 25 basis poin pada pekan ini. Pemangkasan suku bunga ini diantisipasi menjadi katalis kuat yang memicu sentimen risk-on dan arus modal masuk ke pasar berkembang, dengan proyeksi IHSG dapat mencapai level 8.750–8.900.
+3. Meskipun pasar menguat, beberapa emiten big caps seperti BBCA dan AMMN tercatat sebagai top laggards secara year to date 2025, dengan koreksi masing-masing 16,28% dan 26,84%. Pada 10 Desember 2025, Bursa Efek Indonesia membuka kembali perdagangan beberapa saham yang sebelumnya disuspensi dan melakukan suspensi terhadap tiga saham lainnya akibat lonjakan harga di luar kewajaran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1. Indeks Harga Saham Gabungan (IHSG) menunjukkan penguatan signifikan sebesar 21,76% sepanjang tahun berjalan hingga 11 Desember 2025, mencapai level 8.620,48. Namun, pada hari tersebut IHSG ditutup melemah 0,92% akibat tekanan jual pada saham-saham berkapitalisasi besar seperti perbankan dan beberapa emiten sawit.
+2. The Federal Reserve memangkas suku bunga acuan sebesar 25 basis poin menjadi 3,50%–3,75% pada 11 Desember 2025, menandai pemangkasan ketiga tahun ini. Kebijakan ini diharapkan memperkuat sentimen risk-on di pasar keuangan global dan mendorong aliran dana asing ke pasar negara berkembang termasuk Indonesia.
+3. Para analis memprediksi potensi penguatan pasar saham Indonesia berlanjut hingga akhir tahun 2025 didukung oleh fenomena Santa Claus Rally, stabilitas ekonomi domestik, dan potensi penurunan suku bunga BI pada paruh pertama 2026, meskipun diwarnai kewaspadaan terhadap aksi ambil untung dan valuasi pasar yang meningkat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.  IHSG ditutup menguat 0,46% ke 8.660,50 pada 12 Desember 2025 dan mencatatkan kenaikan 20,88% secara year-to-date. Prospek penguatan IHSG akhir 2025 masih ditopang valuasi pasar yang menarik, fundamental emiten besar yang solid, serta potensi aliran dana asing, meskipun kebijakan moneter The Fed 2026 menjadi tantangan.
+2.  Federal Reserve memangkas suku bunga acuan sebesar 25 basis poin menjadi 3,5%-3,75% pada 11 Desember 2025. Meskipun sinyal The Fed tentang kemungkinan hanya satu pemangkasan suku bunga pada 2026 menimbulkan sentimen kehati-hatian, pasar Asia-Pasifik dan Wall Street sebagian besar menguat pasca-keputusan tersebut, berpotensi mendorong masuknya modal asing ke pasar negara berkembang seperti Indonesia.
+3.  Penghimpunan dana melalui rights issue pada 2025 tercatat Rp17,5 triliun dari 12 emiten, lebih rendah dari tahun sebelumnya, namun diproyeksikan meningkat pada 2026. Sebanyak 24 perusahaan melakukan IPO pada 2025 dengan total dana Rp15,2 triliun. Otoritas Jasa Keuangan (OJK) menerapkan regulasi baru (SEOJK 25/2025) mulai 17 November 2025, menetapkan rasio penjatahan saham IPO 1:1 untuk investor ritel dan institusi serta membatasi maksimal 10% untuk satu investor ritel, demi pemerataan distribusi saham.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1. Indeks Harga Saham Gabungan menguat 0,32% sepanjang pekan 8–12 Desember 2025, ditutup pada level 8.660,499. Kapitalisasi pasar Bursa Efek Indonesia meningkat 0,24% menjadi Rp15.882 triliun, dan rata-rata nilai transaksi harian melonjak 41,95% mencapai Rp30,29 triliun.
+2. Bursa Efek Indonesia akan menerapkan periode non-cancellation pada sesi pre-opening dan pre-closing untuk meningkatkan validitas harga dan mencegah spoofing. Otoritas Jasa Keuangan menargetkan Exchange Traded Fund Emas dapat diperdagangkan pada tahun 2026, dan pengawasan aset kripto telah beralih dari Bappebti ke OJK sejak 10 Januari 2025.
+3. PT Telkom Indonesia Tbk memperoleh persetujuan pemegang saham untuk spin-off sebagian bisnis Wholesale Fiber Connectivity ke PT Telkom Infrastruktur Indonesia (InfraNexia) dengan total nilai aset diproyeksikan mencapai Rp90 triliun pada tahun 2026. Selain itu, program Wakaf Saham Masjid Istiqlal resmi diluncurkan untuk filantropi berbasis pasar modal syariah, dan Sei Development Foundation berencana menyematkan aplikasi dompet kripto pada HP Xiaomi mulai 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.  Indeks Harga Saham Gabungan (IHSG) menguat 0,46% menjadi 8.660,50 pada penutupan perdagangan Jumat (12/12/2025). Meskipun beberapa analis memproyeksikan koreksi, IHSG dibuka menguat pada Senin (15/12/2025) ke 8.705,24 sebelum ditutup melemah 0,13% menjadi 8.649,66. Secara tahun berjalan 2025, IHSG telah menguat 22,33%, dan aliran dana asing ke pasar saham Indonesia pada November 2025 mencapai Rp12,20 triliun, meskipun terjadi net sell asing sebesar Rp130 miliar pada pekan kedua Desember 2025.
+2.  Bank sentral global dan domestik menjadi fokus utama pasar, dengan The Federal Reserve (The Fed) memangkas suku bunga acuan (FFR) sebesar 25 basis poin menjadi 3.50-3.75% pada Desember 2025. Keputusan ini berpotensi menarik modal asing ke pasar negara berkembang. Di Indonesia, pasar menantikan hasil Rapat Dewan Gubernur Bank Indonesia pada 16-17 Desember 2025, dengan ekspektasi pemangkasan BI Rate sebesar 25 basis poin menjadi 4.5%.
+3.  Prospek pasar modal Indonesia dan Asia menunjukkan aktivitas tinggi, dengan Hong Kong menjadi pusat penggalangan dana terbesar di Asia pada 2025 mencapai lebih dari US$73 miliar. Di Indonesia, penerbitan obligasi korporasi diproyeksikan solid pada 2026, mencapai sekitar Rp170 triliun, didorong kebutuhan refinancing obligasi jatuh tempo senilai Rp156,35 triliun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1. The Indeks Harga Saham Gabungan (IHSG) closed up 0.43% to 8,686.46 on December 16, 2025, driven by gains in big-cap stocks such as DSSA, UNVR, BREN, and AMMN. This occurred despite analysts' earlier projections of a potential correction and a generally weaker sentiment from global markets where major US and Asian indices declined, alongside a fall in global oil prices.
+2. Indonesia's government reaffirmed its focus on national resilience and disciplined fiscal management following a cabinet meeting on December 15, 2025. The nation's macroeconomic condition was reported as solid by year-end, with a record-high IHSG, surplus in trade and current accounts, and foreign exchange reserves around US$150 billion, leading into Bank Indonesia's final monetary policy meeting of 2025 on December 17.
+3. New government policy mandates an export duty on coal from 2026, which is anticipated to impact the cash flow and profit margins of coal mining companies, particularly those focused on exports. Meanwhile, corporate bond issuance in Indonesia reached a record high of Rp284.3 trillion in 2025, though 2026 is projected for a moderation in new issuances due to geopolitical risks and shifting investor preference towards equity markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1. Indeks Harga Saham Gabungan (IHSG) ditutup melemah 0,11% atau 9,13 poin ke 8.677,34 pada 17 Desember 2025. Pelemahan ini terjadi setelah Bank Indonesia mempertahankan suku bunga acuan BI Rate pada level 4,75% di tengah pelemahan Rupiah dan meningkatnya ketidakpastian ekonomi global.
+2. Pemerintah Indonesia mengumumkan penerapan tarif bea keluar untuk komoditas batu bara sebesar 1% hingga 5% dan emas sebesar 7,5% hingga 15% mulai 1 Januari 2026. Kebijakan ini diperkirakan akan memengaruhi margin laba emiten berorientasi ekspor dan meningkatkan penerimaan negara.
+3. Pasar global mencermati data penjualan ritel China yang hanya tumbuh 1,3% pada November, di bawah ekspektasi pasar, serta harga minyak mentah Brent yang turun ke $58,92 per barel dan WTI ke $55,27 per barel, level terendah sejak awal 2021. Kondisi ini berpotensi menekan permintaan komoditas ekspor Indonesia dan profitabilitas sektor energi.</t>
         </is>
       </c>
     </row>
@@ -1588,8 +3028,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1614,75 +3054,287 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>45961</v>
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>45968</v>
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. PT Pertamina Patra Niaga (PPN) menyalurkan 100.000 barel bahan bakar dasar impor kepada BP-AKR untuk menormalisasi pasokan BBM di SPBU swasta, dengan 100.000 barel tambahan diperkirakan tiba pada pekan ketiga November 2025. Badan usaha swasta lainnya, termasuk Vivo dan Shell, masih dalam tahap negosiasi untuk pembelian bahan bakar dasar dari Pertamina.
-2. Per 01 November 2025, Pertamina menaikkan harga Dexlite dan Pertamina Dex sebesar Rp200 per liter, menjadi Rp13.900 per liter dan Rp14.200 per liter. Pada periode yang sama, Shell dan BP-AKR juga menyesuaikan harga BBM, dengan mayoritas jenis bensin turun dan jenis diesel naik.
-3. Terkait dugaan masalah kualitas Pertalite di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM melakukan pengecekan di sekitar 300 SPBU. Hasil sementara menunjukkan bahwa Pertalite yang disalurkan "on specification" tanpa kontaminasi air atau etanol, dan Pertamina telah membuka 32 posko pengaduan serta bengkel rekanan untuk memberikan solusi dan kompensasi kepada masyarakat yang terdampak.</t>
+          <t>1. Badan Pusat Statistik (BPS) mencatat laju inflasi Indonesia pada November 2025 melambat menjadi 0,17% secara bulanan (month to month/MtM) dari 0,28% MtM pada bulan sebelumnya, serta 2,72% secara tahunan (year on year/YoY) dari 2,86% YoY pada Oktober 2025. Perlambatan ini berbanding terbalik dengan pola historis akhir tahun dan sebagian besar didorong oleh deflasi pada komoditas pangan pokok seperti daging ayam ras dan beras, meskipun kenaikan harga emas perhiasan dan tarif angkutan udara menjadi pendorong utama inflasi.
+2. Bank Indonesia (BI) mempertahankan BI Rate sebesar 4,75% pada November 2025, sejalan dengan proyeksi inflasi 2,5%±1% untuk 2025 dan 2026, serta berencana mencari ruang penurunan suku bunga lebih lanjut untuk mendorong pertumbuhan ekonomi. Kementerian Keuangan dan PLN juga berkomitmen menjaga daya beli masyarakat dengan mempertahankan tarif listrik non-subsidi tidak naik untuk Kuartal IV 2025. Sementara itu, ekspektasi pemangkasan suku bunga Federal Reserve Amerika Serikat sebesar 25 basis poin pada Desember 2025 meningkat dengan probabilitas mencapai 87-89% di tengah pelemahan data ekonomi AS.
+3. Secara regional, beberapa provinsi seperti Aceh, Sumatra Utara, dan Sumatra Barat mencatat deflasi pada November 2025, namun BPS memproyeksikan dampak gangguan distribusi akibat bencana alam di wilayah tersebut baru akan terlihat pada data inflasi Desember 2025. Di provinsi lain seperti Jawa Timur, Jawa Barat, dan Kepulauan Riau, cuaca ekstrem telah menyebabkan kenaikan harga pada komoditas hortikultura tertentu, menambah tekanan inflasi di tengah persiapan Hari Besar Keagamaan Nasional (Nataru) 2025/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45975</v>
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.  Pemerintah daerah Sumatra Barat dan Pertamina Patra Niaga telah mengambil langkah cepat untuk memulihkan kelangkaan bahan bakar minyak di wilayah tersebut pada November 2025, dengan Pertamina mempercepat pasokan melalui jalur darat dan mengoperasikan Integrated Terminal Teluk Kabung 24 jam sehari sejak 7 November 2025, yang meningkatkan kecepatan penyaluran sekitar 16%. Di sisi lain, Kementerian Energi dan Sumber Daya Mineral mendorong SPBU swasta untuk membeli base fuel dari Pertamina Patra Niaga untuk mengatasi ketimpangan pasokan, di mana BP-AKR telah sepakat membeli dua kargo atau 200.000 barel base fuel, dengan indikasi akan menambah pesanan hingga 300.000 barel, sementara Shell dan Vivo masih dalam tahap negosiasi.
-2.  Kementerian Keuangan mengawal penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan yang ditargetkan meningkatkan kapasitas produksi bahan bakar minyak hingga 142.000 barel per hari, LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun, dengan nilai investasi mencapai US$7,4 miliar. PT Kilang Pertamina Internasional telah melakukan pengoperasian awal Unit Residual Fluid Catalytic Cracking Complex di RDMP Balikpapan pada 10 November 2025, yang berhasil meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari dan produksi LPG menjadi 43.000 ton per tahun. Sementara itu, keputusan investasi akhir atau Final Investment Decision (FID) proyek Kilang Tuban berkapasitas 300.000 barel per hari dengan Rosneft ditargetkan rampung pada awal Desember 2025.
-3.  Kementerian Energi dan Sumber Daya Mineral mendorong penerapan bensin campuran 10% etanol (E10) pada 2028, atau berpotensi dipercepat menjadi 2027, dengan kebutuhan etanol mencapai 1,4 juta hingga 4 juta kiloliter. Proyek ini menghadapi tantangan seperti ketersediaan bahan baku, keterbatasan insentif, dan infrastruktur distribusi yang belum memadai, serta usulan dari Asosiasi Produsen Spiritus dan Etanol Indonesia untuk membebaskan etanol dari kategori barang kena cukai sebesar Rp20.000 per liter agar tidak membebani harga bensin hijau bagi konsumen. Pemerintah juga mencari keterlibatan sektor swasta, dengan Toyota Indonesia menunjukkan minat untuk mengembangkan pabrik bioetanol.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>45982</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1.  Penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan senilai 7.4 miliar USD ditargetkan pada pertengahan Desember 2025. Proyek ini akan meningkatkan kapasitas kilang dari 260.000 barel per hari (bph) menjadi 360.000 bph, berpotensi mengurangi ketergantungan impor Bahan Bakar Minyak (BBM) hingga 15% dan memenuhi 22%-25% kebutuhan energi domestik. Unit Residual Fluid Catalytic Cracking (RFCC) Complex dengan kapasitas 90.000 bph telah mulai beroperasi pada 10 November 2025.
-2.  PT Pertamina Patra Niaga mencatat volume penjualan bensin dan solar sebesar 87 juta kiloliter (KL) per Oktober 2025, dengan 41% berasal dari produk non-subsidi. Penyaluran Solar bersubsidi terkendali 1.5% di bawah kuota 18.8 juta KL dan Pertalite 10% di bawah kuota 31.2 juta KL hingga Oktober 2025. Permintaan Pertamax Turbo (RON 98) melonjak 76%, sehingga Pertamina menambah pasokan melalui impor dan memastikan kesiapan distribusi untuk periode Natal dan Tahun Baru 2025-2026.
-3.  Dalam pengembangan biofuel, penjualan Pertamax Green 95 (E5) di 168 SPBU Pertamina mencatat pertumbuhan 80% dari 2024, dengan proyeksi kebutuhan bioetanol 4,800-5,000 KL per tahun untuk Pulau Jawa. Asosiasi Produsen Spiritus dan Etanol Indonesia (Aspendo) mengusulkan penghapusan cukai bioetanol fuel grade sebesar Rp20.000 per liter untuk menjaga harga kompetitif. Sementara itu, BP-AKR membeli 100.000 barel base fuel dari Pertamina Patra Niaga untuk mengatasi kekurangan stok, sedangkan Shell dan Vivo masih dalam negosiasi business-to-business untuk pengadaan base fuel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>45989</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1. PT Pertamina Patra Niaga memperkuat pasokan BBM untuk periode Natal 2025 dan Tahun Baru 2026. Ini mencakup penambahan 1,4 juta kiloliter Pertalite dari produksi kilang domestik dan impor baru, dengan target ketahanan stok 21-23 hari per 25 November 2025. Kilang Pertamina Internasional juga memulai operasi awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari di Kilang Balikpapan sejak 10 November 2025, yang akan meningkatkan produksi gasoline dan LPG serta mengurangi impor.
-2. Pasokan BBM di SPBU swasta mulai normal kembali setelah mencapai kesepakatan pembelian base fuel dari Pertamina Patra Niaga. Vivo Energy Indonesia telah menerima 100.000 barel Revvo 92 (RON 92) yang mulai tersedia bertahap sejak 23 November 2025. BP-AKR menambah pembelian base fuel menjadi total 230.000 barel dari Pertamina Patra Niaga per 27 November 2025. Shell Indonesia juga menyelesaikan kesepakatan pada 25 November 2025 untuk membeli 100.000 barel base fuel, dengan harapan stok pulih akhir November 2025.
-3. Distribusi energi menghadapi tantangan cuaca ekstrem dan diperkuat dengan langkah keamanan. Dua kapal pengangkut Pertalite dan Biosolar tidak dapat bersandar di Belawan, Sumatra Utara sejak 23 November 2025 karena cuaca ekstrem, menyebabkan penyesuaian pola suplai dari terminal alternatif. Untuk mengamankan infrastruktur energi nasional, pemerintah akan mengerahkan personel TNI untuk menjaga kilang minyak dan terminal BBM Pertamina yang memiliki kapasitas pengolahan 1 juta barel per hari dan 231 terminal migas, dimulai pada Desember 2025.</t>
+          <t>1.  The Federal Reserve (The Fed) memangkas suku bunga acuan sebesar 25 basis poin untuk ketiga kalinya pada 2025 ke kisaran 3,50%-3,75% pada FOMC Meeting 9-10 Desember. Keputusan ini diikuti oleh sinyal kehati-hatian The Fed mengenai pelonggaran lebih lanjut pada 2026, dengan proyeksi hanya satu kali pemangkasan 25 bps. Respons pasar global menunjukkan pelemahan nilai tukar dolar Amerika Serikat dan penguatan mayoritas mata uang Asia, termasuk rupiah, serta kenaikan harga emas dan perak yang mencapai rekor tertinggi, meskipun pasar aset kripto mengalami koreksi signifikan akibat aksi jual setelah berita.
+2.  Inflasi di Indonesia pada November 2025 tercatat relatif stabil di 2,72% secara tahunan, sesuai dengan target pemerintah 1,5-3,5%. Namun, tekanan inflasi masih didominasi oleh kelompok pangan bergejolak seperti cabai dan beras, yang harga ecerannya masih tinggi di beberapa daerah seperti Jawa Barat dan Semarang, di mana inflasi Semarang mencapai 2,92% YoY. Pemerintah daerah melalui Tim Pengendalian Inflasi Daerah (TPID) terus memperkuat ketahanan pangan dan efisiensi rantai pasok dengan berbagai program, seperti yang dilakukan Kabupaten Tanah Datar yang meraih TPID Award kelima kalinya.
+3.  Perekonomian Indonesia menunjukkan pertumbuhan yang solid sebesar 5,04% pada kuartal III/2025, dengan konsumsi rumah tangga menjadi pendorong utama. Proyeksi pertumbuhan ekonomi untuk 2026 dari Kadin, APINDO, dan Mandiri Sekuritas berkisar antara 5,0% hingga 5,4%, didukung oleh ekspektasi inflasi yang stabil (sekitar 2,5% ± 1%) dan penguatan investasi yang ditargetkan Rp2.175 triliun. Meskipun demikian, sektor keuangan menghadapi tantangan seperti perlambatan pertumbuhan kredit perbankan secara keseluruhan menjadi 7,36% per Oktober 2025, sementara sentimen konsumen menunjukkan kekhawatiran terhadap biaya hidup.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Bank Indonesia (BI) mempertahankan BI-Rate di level 4,75% pada Rapat Dewan Gubernur (RDG) 18-19 November 2025, dengan mayoritas ekonom memproyeksikan suku bunga acuan akan tetap pada level ini dalam RDG Desember 2025. Meskipun ruang pelonggaran moneter terbuka untuk tahun 2026, transmisi penurunan suku bunga kebijakan ke suku bunga deposito dan kredit perbankan masih berjalan lambat.
+2. Ekspektasi pasar global terhadap pemangkasan suku bunga The Federal Reserve (The Fed) sebesar 25 basis poin pada pertemuan 9-10 Desember 2025 sangat tinggi, mencapai probabilitas 80% hingga 90%. Prospek ini melemahkan dolar Amerika Serikat, mendorong penguatan rupiah menjadi Rp16.663 per dolar AS pada 1 Desember 2025, serta memicu kenaikan harga emas, perak, dan minyak dunia.
+3. Untuk mempercepat transmisi kebijakan moneter dan mendorong pertumbuhan kredit, BI mengguyur insentif kebijakan makroprudensial (KLM) mulai 1 Desember 2025, dengan potensi insentif mencapai 5,5% dari dana pihak ketiga (DPK). Sejalan dengan tren penurunan BI-Rate, emiten juga memanfaatkan momentum ini untuk menerbitkan obligasi guna pendanaan yang lebih murah, dan sektor properti memproyeksikan pertumbuhan positif pada 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. The Federal Reserve (The Fed) memangkas suku bunga acuan sebesar 25 basis poin menjadi kisaran 3,50%-3,75% pada pertemuan 9-10 Desember 2025. Ini merupakan pemangkasan ketiga kalinya pada tahun 2025, mencapai level terendah sejak Oktober 2022, dan keputusan diambil dengan voting 9-3 di Komite Pasar Terbuka Federal (FOMC) disertai sinyal kehati-hatian untuk pemangkasan lanjutan pada 2026.
+2. Keputusan The Fed tersebut berdampak pada pelemahan dolar AS di pasar global, mendorong penguatan harga komoditas. Harga emas mencapai level tertinggi dalam lebih dari sebulan di atas US$4.200 per troy ounce, sementara harga perak melonjak ke rekor tertinggi sepanjang masa di atas US$60 per troy ounce. Harga minyak dunia menunjukkan pergerakan yang lebih stabil di kisaran US$62-US$63 per barel.
+3. Pasar keuangan Indonesia merespons positif dengan lonjakan Indeks Harga Saham Gabungan (IHSG) yang mencapai rekor tertinggi baru di 8.710,69 dan membukukan kenaikan 21,76% sepanjang tahun berjalan. Aliran modal asing masuk secara signifikan, mencapai net buy Rp14,08 triliun di seluruh instrumen pada awal Desember 2025, dengan rupiah yang menunjukkan volatilitas namun cenderung menguat, didukung ekspektasi penurunan BI Rate lanjutan dan prospek pertumbuhan ekonomi domestik yang membaik.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Bank Indonesia (BI) mengumumkan penyesuaian operasional untuk sistem pembayaran dan penyelesaiannya menjelang Hari Raya Natal dan akhir tahun 2025, dengan operasi normal dijadwalkan kembali pada 2 Januari 2026. Penyesuaian ini mencakup perubahan jam operasional Sistem Kliring Nasional Bank Indonesia (SKNBI) untuk beberapa layanannya.
+2. Batas waktu transaksi antar Peserta (Nasabah/TSA) akan diperpanjang dari pukul 16.30 WIB menjadi 17.30 WIB pada periode 19-30 Desember 2025, dan selanjutnya menjadi 22.30 WIB pada 31 Desember 2025. Batas waktu cut-off sistem untuk BI-RTGS, BI-SSSS, dan BI-ETP juga akan diperpanjang secara signifikan, dengan cut-off Sistem BI-RTGS terakhir mencapai pukul 23.55 WIB pada 31 Desember 2025.
+3. Publikasi JIBOR, INDONIA, JISDOR, dan Kurs Acuan Non USD/IDR tidak mengalami perubahan jadwal dan akan terus dipublikasikan setiap hari. Publikasi JIBOR terakhir untuk tahun 2025 akan dilakukan pada 31 Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Menteri Keuangan Purbaya Yudhi Sadewa menyatakan ekonomi nasional menunjukkan perbaikan, didukung peningkatan aktivitas masyarakat termasuk penjualan ritel, dan kebijakan penempatan dana pemerintah ke perbankan. Indeks Keyakinan Konsumen (IKK) mencapai 133,2 pada Oktober 2025, Indeks Keyakinan Konsumen terhadap Kinerja Pemerintah (IKKP) mencapai 135,9 pada November 2025, dan penjualan motor tumbuh 8,4% pada Oktober 2025.
+2. Pemerintah mengumumkan kesiapan pemberian insentif fiskal untuk mendorong investor ritel di pasar saham, dengan syarat Otoritas Jasa Keuangan dan Bursa Efek Indonesia menindak praktik saham gorengan dalam enam bulan. OJK telah menerbitkan SEOJK No. 25/SEOJK.04/2025 per 27 November 2025, yang mengubah skema alokasi penawaran umum saham untuk ritel menjadi 1:1 dari 1:2, serta membatasi pemesanan maksimal 10% dari total nilai efek.
+3. Pasar modal Indonesia menunjukkan pergerakan beragam di awal Desember 2025, dengan Indeks Harga Saham Gabungan (IHSG) ditutup naik 0,27% ke level 8.635,23 pada 4 Desember 2025 setelah sempat melemah 0,06% ke 8.611,79 pada 3 Desember 2025. Pelaku pasar juga mencermati fenomena window dressing yang diperkirakan akan mendorong permintaan saham berfundamental solid oleh investor di bulan Desember.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. The Federal Reserve (The Fed) memangkas suku bunga acuan sebesar 25 basis poin menjadi 3.50-3.75% pada 10 Desember 2025, menjadikannya pemangkasan ketiga tahun ini. Keputusan ini diperkirakan mendorong aliran dana asing ke Indonesia, berpotensi menguatkan rupiah dan Indeks Harga Saham Gabungan (IHSG).
+2. Indeks Harga Saham Gabungan (IHSG) menunjukkan penguatan signifikan, mencapai level tertinggi sepanjang masa dan dibuka di 8.764,09 pada 11 Desember 2025. Proyeksi optimis memperkirakan IHSG dapat mencapai 9.000 pada akhir 2025, didukung oleh aktivitas investor ritel domestik yang kuat dan Indeks Keyakinan Konsumen (IKK) Indonesia yang meningkat menjadi 124 pada November 2025.
+3. Survei Bank Indonesia menunjukkan Indeks Penjualan Riil (IPR) nasional tumbuh 4.3% secara tahunan pada Oktober 2025, meskipun pemulihan belum merata di semua kelompok barang. Di tengah penguatan pasar saham dan data konsumsi domestik, nilai tukar Rupiah masih cukup tertekan imbas Dolar AS yang kuat.</t>
         </is>
       </c>
     </row>

--- a/src/results/(News)Sentiment.xlsx
+++ b/src/results/(News)Sentiment.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="13" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" tabRatio="600" firstSheet="13" activeTab="15" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)All" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,10 +21,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)PDB" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Biodiesel" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Bioetanol" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Minyak" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Minyak" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Produk Kilang" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Produk Kilang" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)RUPTL" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Minyak" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Minyak" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Harga Produk Kilang" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(Summary)Volume Produk Kilang" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -38,13 +39,18 @@
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -73,12 +79,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -136,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,6 +170,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -519,7 +543,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -1163,7 +1187,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1247,7 +1271,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1331,7 +1355,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1415,7 +1439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1499,7 +1523,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
@@ -1652,7 +1676,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="13.36328125" customWidth="1" min="1" max="1"/>
+    <col width="14.36328125" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1677,10 +1705,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -1695,10 +1723,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="1" t="n">
         <v>45998</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1715,10 +1743,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="1" t="n">
         <v>46005</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1745,151 +1773,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Tanggal awal</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Tanggal akhir</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Summary Data</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>45961</v>
+      <c r="A2" s="8" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>45991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>45968</v>
+      <c r="A3" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>45998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Harga minyak mentah global mengalami tekanan penurunan sepanjang minggu pertama November 2025 akibat kekhawatiran kelebihan pasokan dan lemahnya permintaan, khususnya dari Amerika Serikat. Harga Brent diperdagangkan di sekitar US$63-US$64 per barel, dan West Texas Intermediate (WTI) mendekati US$60 per barel, dengan WTI anjlok sekitar 16-17% secara tahun berjalan. Stok minyak mentah AS menunjukkan kenaikan signifikan, dengan laporan API sebesar 6.5 juta barel dan EIA sebesar 5.2 juta barel pada pekan lalu.
-2. OPEC+ memutuskan untuk menghentikan sementara rencana kenaikan produksi pada kuartal I 2026, setelah peningkatan moderat pada Desember, sebagai upaya menyeimbangkan pasar dan meredam volatilitas. Morgan Stanley menaikkan proyeksi harga Brent menjadi US$60 per barel untuk semester I 2026 dari US$57.50. Namun, proyeksi tekanan harga tetap ada, dengan Capital Economics memperkirakan Brent mencapai US$60 per barel pada akhir 2025 dan US$50 per barel pada akhir 2026.
-3. Sanksi AS terhadap produsen minyak utama Rusia (Rosneft PJSC dan Lukoil PJSC) mengakibatkan kilang-kilang di China menghentikan pembelian minyak mentah Rusia, mempengaruhi sekitar 400.000 barel per hari atau 45% dari total impor Rusia ke China. Kondisi pasar yang cukup pasokan ini mendorong Arab Saudi untuk memangkas harga jual minyak mentah utamanya untuk pembeli Asia pada Desember, termasuk Arab Light yang dipangkas US$1.20 per barel.</t>
-        </is>
-      </c>
+          <t>1. Pemerintah dan PT PLN (Persero) mempercepat pemulihan infrastruktur kelistrikan di wilayah Sumatra (Aceh, Sumatra Utara, dan Sumatra Barat) yang terdampak bencana banjir dan longsor, dengan target sebagian besar wilayah pulih pada 6-7 Desember 2025. Proses pemulihan melibatkan pengerahan personel, pengiriman material melalui berbagai moda transportasi termasuk udara, serta dukungan dari berbagai instansi. Relaksasi aturan pembelian BBM juga diberlakukan di daerah terdampak untuk menjamin pasokan.
+2. Diskusi dan kebijakan terkait transisi energi terus berjalan, meliputi pembatalan pensiun dini PLTU Cirebon-1 dengan alasan teknis dan pencarian PLTU alternatif yang lebih tua dan berdampak lingkungan lebih buruk. Sektor panas bumi aktif dengan rencana pembentukan usaha patungan antara PT Pertamina Geothermal Energy Tbk (PGEO) dan PT PLN Indonesia Power (PLN IP) untuk menggarap proyek berkapasitas besar. Sementara itu, pengembangan energi nuklir menjadi perhatian, dengan PLN menugaskan kajian teknologi PLTN dan rencana pembentukan Badan Pelaksana Program Energi Nuklir (NEPIO) yang ditargetkan beroperasi pada 2030.
+3. Kinerja sektor batubara menunjukkan penurunan ekspor dan harga yang cenderung melemah. Pemerintah tengah mempertimbangkan penerapan bea keluar batubara mulai 2026, serta rencana penyesuaian target produksi dan porsi domestic market obligation (DMO) batubara yang harganya stagnan sejak 2018. Hal ini memicu diskusi antara pemerintah dan pelaku usaha terkait dampaknya terhadap biaya produksi dan potensi beban pada tarif listrik nasional.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>45975</v>
+      <c r="A4" s="8" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>46005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Harga minyak global menunjukkan kenaikan, dengan Brent di atas USD64 per barel dan West Texas Intermediate di sekitar USD60 per barel, didukung oleh perkembangan positif di Amerika Serikat. Kenaikan ini terjadi setelah harga minyak mentah turun dalam lima dari enam pekan terakhir karena kekhawatiran kelebihan pasokan. Pasar sedang menantikan rilis data pasokan dan permintaan dari OPEC, IEA, dan EIA pekan ini, sementara OPEC dan sekutunya berencana menunda kenaikan produksi pada kuartal pertama tahun depan untuk mengelola pasokan.
-2. Produksi minyak mentah Rusia sedikit meningkat pada Oktober menjadi rata-rata 9.411 mb/d, 43.000 b/d lebih tinggi dari September, namun masih 70.000 b/d di bawah kuota OPEC+ yang mencakup pemotongan kompensasi. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena beberapa kilang di India, China, dan Turki enggan menerima pasokan yang terkena sanksi.
-3. India, sebagai importir minyak mentah terbesar ketiga di dunia, mengurangi pembelian minyak dari Rusia untuk pengiriman Desember sebagai dampak sanksi Barat dan negosiasi dagang dengan Amerika Serikat. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia India tahun ini, tidak mengajukan pesanan untuk bulan tersebut. Pergeseran ini mendorong India untuk mencari pasokan alternatif dari kawasan Amerika dan Timur Tengah, mengingat sekitar 36% dari total impor minyak mentah India tahun ini berasal dari Rusia.</t>
-        </is>
-      </c>
+          <t>1.  Upaya transisi energi Indonesia menghadapi tantangan dan perubahan kebijakan, ditandai dengan pembatalan pensiun dini Pembangkit Listrik Tenaga Uap (PLTU) Cirebon-1 yang kemudian pemerintah mencari alternatif pembangkit lain untuk disuntik mati. Selain itu, terdapat kekhawatiran terkait keterlambatan proyek Pembangkit Listrik Tenaga Air (PLTA) dan kritik terhadap target Pembangkit Listrik Tenaga Surya (PLTS) 100 gigawatt. Pemerintah juga menjajaki kerja sama pengembangan Pembangkit Listrik Tenaga Nuklir (PLTN), termasuk tawaran dari Rusia, dengan rencana lelang mitra.
+2.  Pemerintah berencana menerapkan kebijakan fiskal baru seperti bea keluar untuk ekspor batu bara (1%-5%) dan emas (7,5%-15%) mulai tahun 2026 guna mendorong hilirisasi dan meningkatkan penerimaan negara. Selain itu, pemerintah mengkaji pengalihan subsidi LPG untuk mendukung proyek hilirisasi batu bara menjadi Dimethyl Ether (DME) yang ditargetkan mulai konstruksi pada 2026. Kementerian Energi dan Sumber Daya Mineral (ESDM) juga menolak ekspor listrik energi baru terbarukan (EBT) mentah dan mendorong hilirisasi EBT di dalam negeri.
+3.  Sektor ketenagalistrikan di Aceh, Sumatra Utara, dan Sumatra Barat menghadapi kendala berat dalam pemulihan pasokan listrik pasca-bencana banjir dan longsor, yang juga menghambat pemulihan infrastruktur telekomunikasi. Di sisi lain, angkutan batu bara oleh PT Kereta Api Indonesia (Persero) mencatat peningkatan, menunjukkan peran bahan bakar tersebut dalam menopang kebutuhan Pembangkit Listrik Tenaga Uap (PLTU) di Jawa dan Bali.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>45982</v>
+      <c r="A5" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>46012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Indonesia sedang menyiapkan Peraturan Presiden yang memperbolehkan PT Pertamina (Persero) untuk mengimpor energi langsung dari perusahaan Amerika Serikat tanpa proses lelang. Kebijakan ini merupakan tindak lanjut dari kesepakatan tarif timbal balik antara AS dan Indonesia pada Juli 2025, dengan tujuan mengurangi defisit perdagangan AS dengan Indonesia yang sekitar US$18 miliar, dan mengakselerasi komitmen impor minyak Indonesia dari AS senilai US$15 miliar. PT Kilang Pertamina Internasional (KPI) mencari cara agar impor minyak mentah dari AS dapat lebih ekonomis, dan pemerintah berencana meningkatkan impor minyak mentah dari AS mulai Desember 2025.
-2. Harga minyak global terkoreksi di pekan ini, dengan harga berjangka Brent turun US$1,63 (2,5%) menjadi US$63,26 per barel dan West Texas Intermediate (WTI) melemah US$1,56 (2,6%) menjadi US$59,18 per barel pada 20 November 2025. Penurunan ini dipengaruhi oleh laporan upaya AS untuk mengakhiri perang Rusia-Ukraina, yang berpotensi meningkatkan pasokan minyak Rusia ke pasar. Bersamaan dengan itu, sanksi AS terhadap Rosneft dan Lukoil mulai berlaku pada 21 November 2025, berpotensi membuat hampir 48 juta barel minyak mentah Rusia terlantar di laut dan mendorong pembeli di Asia mencari pasokan alternatif.
-3. Harga minyak mentah Indonesia (ICP) untuk Oktober 2025 ditetapkan sebesar US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya. Penurunan ini disebabkan oleh beberapa faktor seperti peningkatan suplai minyak oleh OPEC+ sebesar 137.000 barel per hari untuk November 2025, berkurangnya ketegangan geopolitik di Timur Tengah, pengolahan minyak mentah global yang diperkirakan mencapai titik terendah musiman 81,6 juta barel per hari pada Oktober, penguatan nilai tukar dolar AS, serta pemotongan harga jual resmi minyak mentah Arab Saudi untuk pembeli di Asia di tengah melemahnya permintaan dan perlambatan ekonomi Tiongkok.</t>
-        </is>
-      </c>
+          <t>1.  Pemerintah dan PT PLN (Persero) terus berupaya memulihkan pasokan listrik di wilayah Sumatra, terutama Aceh, yang terdampak bencana banjir dan tanah longsor. Pemulihan menghadapi tantangan karena kerusakan infrastruktur yang parah dan area yang terisolasi. Meskipun listrik di Banda Aceh telah pulih, beberapa kabupaten masih mengalami kendala listrik bergilir akibat kerusakan infrastruktur tegangan rendah. Berbagai pihak terlibat dalam penyaluran bantuan dan perbaikan.
+2.  Ekosistem kendaraan listrik di Indonesia menunjukkan perkembangan, ditandai dengan peresmian pabrik baru, penambahan Stasiun Pengisian Kendaraan Listrik Umum (SPKLU) oleh PLN, dan pertumbuhan penjualan kendaraan listrik. Di sisi energi terbarukan, PLN Energi Primer Indonesia menargetkan peningkatan penggunaan biomassa untuk co-firing di PLTU dan mengkaji pengembangan Pembangkit Listrik Tenaga Surya (PLTS) Terapung Cirata. Investasi dalam energi surya semakin kompetitif karena penurunan biaya.
+3.  Pemerintah sedang menyusun kebijakan fiskal di sektor energi, termasuk rencana pengenaan bea keluar untuk ekspor batu bara dan emas mulai Januari 2026 guna menambah penerimaan negara dan menyeimbangkan pasar. Pembahasan mengenai pajak karbon dan kelayakan ekonomi proyek gasifikasi batu bara menjadi Dimethyl Ether (DME) sebagai pengganti LPG juga berlanjut, dengan pertimbangan besar tentang subsidi yang dibutuhkan. Selain itu, pemerintah berencana memperketat aturan pembelian LPG 3 kg.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>45989</v>
+      <c r="A6" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>46019</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.  Harga minyak menunjukkan tekanan turun selama minggu ini, dengan Brent diperdagangkan di kisaran USD 62-63 per barel dan WTI Crude di kisaran USD 58-59 per barel. Prediksi dari bank investasi seperti Goldman Sachs memperkirakan WTI Crude akan rata-rata USD 53 per barel pada 2026, sementara JP Morgan memproyeksikan Brent dapat turun ke kisaran USD 30-an per barel pada 2027 karena kekhawatiran pasokan berlebih sebesar 2 juta barel per hari. Harga bensin eceran di Amerika Serikat turun di bawah USD 3 per galon di banyak negara bagian, dengan beberapa lokasi mencapai USD 1.99 per galon.
-2.  Pasokan minyak global tetap kuat, didorong oleh produksi yang tangguh dari produsen non-OPEC seperti Amerika Serikat, Brasil, dan Guyana. Meskipun eksekutif shale AS melaporkan tantangan profitabilitas di bawah USD 60 per barel dan kenaikan biaya pengeboran sebesar 5 hingga 10 persen dari tahun lalu, produksi shale AS terus meningkat. OPEC+ diperkirakan akan mempertahankan tingkat produksi saat ini pada pertemuan tanggal 30 November, menunda peningkatan produksi yang direncanakan untuk kuartal I 2026 akibat kekhawatiran peningkatan persediaan global.
-3.  Pembicaraan damai yang diperbarui antara Rusia dan Ukraina memberikan tekanan signifikan pada harga minyak karena potensi pelonggaran sanksi yang dapat meningkatkan pasokan Rusia. Di sisi lain, konferensi energi di Timur Tengah menampilkan pandangan yang berbeda, dengan ADIPEC menyoroti permintaan energi jangka panjang yang kuat dan kebutuhan investasi besar USD 18.2 triliun untuk mencapai 123 juta barel per hari pada 2050, sementara Dii Desert Energy Summit berfokus pada percepatan pertumbuhan energi rendah karbon dan investasi yang melampaui bahan bakar fosil dengan rasio 2 berbanding 1. Cina terus mempercepat pembelian minyak mentah strategisnya, mengimpor sekitar 2.15 juta barel per hari dari Rusia dan menimbun lebih dari 1 juta barel per hari pada beberapa bulan di tahun 2025.</t>
-        </is>
-      </c>
+          <t>1. PLN dan mitra strategis terus mempercepat pengembangan energi baru terbarukan (EBT) sesuai Rencana Usaha Penyediaan Tenaga Listrik (RUPTL) 2025–2034, yang menargetkan 76% dari penambahan kapasitas pembangkit berasal dari EBT. Kolaborasi dengan Danantara Investment Management akan menjajaki investasi besar pada proyek-proyek EBT, dan kesepakatan tarif listrik telah dicapai untuk PLTP Ulubelu 30 MW. Selain itu, pemerintah memastikan keberlanjutan operasional PLTSa Benowo melalui alokasi anggaran Rp120 miliar dan Pertamina NRE meluncurkan PLTS di Batam.
+2. Pemerintah tidak akan melanjutkan insentif kendaraan listrik (EV) pada 2026, termasuk pembebasan PPN dan bea masuk impor CBU, yang dapat mempengaruhi pertumbuhan pasar EV. Meskipun demikian, produsen seperti BYD dan VinFast berencana menjaga harga dengan fokus pada produksi lokal. Guna mendukung ekosistem EV, PLN telah menyiagakan lebih dari 4.500 Stasiun Pengisian Kendaraan Listrik Umum (SPKLU) di berbagai wilayah untuk periode Natal dan Tahun Baru, serta PLN bekerja sama dengan KAI untuk elektrifikasi jalur KRL Cikampek.
+3. Mulai 2026, pemerintah akan menerapkan bea keluar pada ekspor batu bara dengan proyeksi penerimaan Rp25 triliun per tahun, sebagai respons terhadap tingginya restitusi Pajak Pertambahan Nilai (PPN) dari sektor batu bara. Sementara itu, PLN terus berupaya memulihkan dan meningkatkan keandalan pasokan listrik di wilayah Aceh, Sumatra Utara, dan Sumatra Barat yang terdampak bencana, termasuk mengoperasikan jalur transmisi kedua Arun–Bireuen dan Pembangkit Listrik Tenaga Gas (PLTG) Tanjung Selor 20 MW di Kalimantan Utara.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45990</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>45991</v>
+      <c r="A7" s="8" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>46020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>45998</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1. OPEC+ menegaskan kembali rencana untuk menahan kenaikan produksi minyak mentah sepanjang kuartal I 2026 di tengah ekspektasi pelemahan pasar musiman dan potensi surplus pasokan global. Badan Energi Internasional (IEA) memproyeksikan rekor kelebihan pasokan pada 2026, sementara harga Brent diperdagangkan mendekati USD63/bbl dan West Texas Intermediate (WTI) mendekati USD59/bbl pada awal Desember 2025.
-2. Ketegangan geopolitik, seperti retorika dan pengerahan pasukan Amerika Serikat di bawah Presiden Donald Trump terkait Venezuela, serta upaya perundingan damai antara Amerika Serikat dan Rusia mengenai konflik Ukraina, terus menopang harga minyak dengan menambah premi risiko. Potensi gencatan senjata di Ukraina dapat membuka peluang pelonggaran sanksi terhadap Rusia dan peningkatan ekspor minyak, yang berpotensi menekan harga lebih lanjut.
-3. Indikasi kelebihan pasokan global tetap menjadi perhatian, didorong oleh lonjakan pasokan dari Amerika dan kenaikan persediaan minyak mentah AS sekitar 574.000 barel pada pekan lalu. Di sisi domestik, PT Pertamina International Shipping (PIS) menyiagakan 332 armada kapal tanker ditambah 12 kapal cadangan untuk memastikan kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia di Indonesia selama periode Natal 2025 dan Tahun Baru 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46005</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1. Harga minyak global menunjukkan volatilitas dan tren bearish menjelang akhir pekan, berfluktuasi antara sekitar US$57–US$64 per barel. Penurunan suku bunga acuan Federal Reserve sebesar 25 basis poin sesuai ekspektasi pasar, namun kekhawatiran kelebihan pasokan global dan perkembangan negosiasi Rusia-Ukraina yang mengarah ke jalur perdamaian menekan harga minyak.
-2. Kekhawatiran kelebihan pasokan global menjadi sentimen dominan, dengan laporan International Energy Agency (IEA) mencatat pasokan minyak dunia mencapai 109 juta barel per hari pada November. IEA merevisi perkiraan surplus global untuk tahun 2026 menjadi 3.84 juta barel per hari, sedikit lebih rendah dari proyeksi sebelumnya, didorong oleh peningkatan proyeksi pertumbuhan permintaan.
-3. Tiongkok terus melakukan penimbunan minyak mentah strategis dan komersial dengan rata-rata sekitar 1 juta barel per hari pada tahun 2025, dan diproyeksikan sekitar 900.000 barel per hari pada tahun 2026, yang membantu meredam kelebihan pasokan di pasar global. Sementara itu, Kementerian Energi dan Sumber Daya Mineral Indonesia melaporkan kerugian devisa negara sebesar Rp523 triliun per tahun karena impor minyak yang mencapai 313 juta barel pada 2024.</t>
-        </is>
-      </c>
+          <t>1. Penggunaan kendaraan listrik di Indonesia menunjukkan peningkatan, tercermin dari lonjakan pengisian daya selama periode Natal dan Tahun Baru 2025/2026, didukung oleh penambahan infrastruktur Stasiun Pengisian Kendaraan Listrik Umum (SPKLU) oleh PLN.
+2. Pemerintah Indonesia sedang membahas insentif untuk mendorong industri kendaraan listrik, khususnya yang berkaitan dengan pemanfaatan sumber daya nikel domestik, meskipun terdapat perdebatan mengenai potensi distorsi teknologi akibat preferensi jenis baterai tertentu.
+3. Sektor energi Indonesia menghadapi tantangan operasional, seperti pemulihan kelistrikan pascabencana di Sumatra, serta dampak fluktuasi harga komoditas batu bara terhadap penerimaan negara.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1903,7 +1908,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -1949,9 +1954,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.  OPEC+ mengumumkan penghentian sementara kenaikan produksi pada kuartal I-2026 setelah kenaikan moderat pada Desember, sebagai upaya menyeimbangkan pasar di tengah tanda-tanda kelebihan pasokan. Morgan Stanley menaikkan proyeksi harga Brent menjadi USD60/bbl untuk semester I-2026, namun mencatat peningkatan produksi OPEC+ sebesar 500.000 bph dari Maret hingga Oktober jauh di bawah kenaikan kuota 2,6 mb/d.
-2.  Harga minyak mentah global melemah dan mencatat penurunan mingguan kedua, tertekan oleh peningkatan pasokan dari OPEC+ serta produsen non-anggota seperti Amerika Serikat dan Brasil. Brent turun menjadi sekitar USD63/bbl dan WTI di bawah USD60/bbl, dengan WTI anjlok sekitar 16% hingga 17% sepanjang tahun ini. Data American Petroleum Institute (API) menunjukkan stok minyak mentah Amerika Serikat naik 6,5 juta barel pada pekan lalu.
-3.  Kilang-kilang minyak di China, termasuk milik negara dan swasta, menghentikan pembelian minyak mentah asal Rusia setelah Amerika Serikat menjatuhkan sanksi terhadap produsen utama Moskow, memengaruhi sekitar 400.000 bpd atau hampir 45% dari total impor minyak Rusia ke China. Menanggapi pasar yang cukup mendapat pasokan dan lemahnya permintaan di Asia, Saudi Aramco memangkas harga minyak mentah unggulannya, Arab Light, untuk pasar Asia pada Desember sebesar USD1.20/bbl.</t>
+          <t>1. Harga minyak mentah global mengalami tekanan penurunan sepanjang minggu pertama November 2025 akibat kekhawatiran kelebihan pasokan dan lemahnya permintaan, khususnya dari Amerika Serikat. Harga Brent diperdagangkan di sekitar US$63-US$64 per barel, dan West Texas Intermediate (WTI) mendekati US$60 per barel, dengan WTI anjlok sekitar 16-17% secara tahun berjalan. Stok minyak mentah AS menunjukkan kenaikan signifikan, dengan laporan API sebesar 6.5 juta barel dan EIA sebesar 5.2 juta barel pada pekan lalu.
+2. OPEC+ memutuskan untuk menghentikan sementara rencana kenaikan produksi pada kuartal I 2026, setelah peningkatan moderat pada Desember, sebagai upaya menyeimbangkan pasar dan meredam volatilitas. Morgan Stanley menaikkan proyeksi harga Brent menjadi US$60 per barel untuk semester I 2026 dari US$57.50. Namun, proyeksi tekanan harga tetap ada, dengan Capital Economics memperkirakan Brent mencapai US$60 per barel pada akhir 2025 dan US$50 per barel pada akhir 2026.
+3. Sanksi AS terhadap produsen minyak utama Rusia (Rosneft PJSC dan Lukoil PJSC) mengakibatkan kilang-kilang di China menghentikan pembelian minyak mentah Rusia, mempengaruhi sekitar 400.000 barel per hari atau 45% dari total impor Rusia ke China. Kondisi pasar yang cukup pasokan ini mendorong Arab Saudi untuk memangkas harga jual minyak mentah utamanya untuk pembeli Asia pada Desember, termasuk Arab Light yang dipangkas US$1.20 per barel.</t>
         </is>
       </c>
     </row>
@@ -1964,9 +1969,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Produksi minyak mentah Rusia pada Oktober mencapai rata-rata 9.411 juta barel per hari, meningkat 43.000 barel per hari dari September. Angka ini 70.000 barel per hari di bawah kuota OPEC+ yang mencakup pemotongan kompensasi, dengan target yang dibutuhkan sebesar 9.481 juta barel per hari. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena keengganan beberapa kilang di India, China, dan Turki untuk menerima minyak yang terkena sanksi.
-2. Harga minyak global menunjukkan kenaikan, dengan Brent melewati US$64 per barel dan West Texas Intermediate (WTI) bergerak di kisaran US$60 per barel, didorong oleh upaya mengakhiri penutupan pemerintahan Amerika Serikat. Kekhawatiran akan kelebihan pasokan masih membebani pasar, menyebabkan harga minyak mentah turun dalam lima dari enam pekan terakhir. Organisasi Negara-Negara Pengekspor Minyak (OPEC) dan sekutunya mulai melonggarkan pembatasan produksi, namun berencana menunda kenaikan output pada kuartal pertama tahun depan, sementara produsen non-OPEC termasuk Amerika Serikat terus menambah pasokan.
-3. India, importir minyak terbesar ketiga di dunia, mengurangi pembelian minyak mentah dari Rusia untuk pengiriman Desember. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia tahun ini, belum mengajukan pesanan. Perubahan pola pembelian ini sebagian besar didorong oleh sanksi Barat terhadap produsen minyak Rusia dan negosiasi dagang dengan Amerika Serikat, di mana India berkomitmen membeli lebih banyak minyak mentah dari Amerika Serikat. Akibatnya, kilang-kilang di India mulai mencari alternatif pasokan dari kawasan Amerika dan Timur Tengah, dengan Indian Oil Corp. berupaya membeli hingga 24 juta barel dari Amerika untuk pengiriman Januari hingga Maret.</t>
+          <t>1. Harga minyak global menunjukkan kenaikan, dengan Brent di atas USD64 per barel dan West Texas Intermediate di sekitar USD60 per barel, didukung oleh perkembangan positif di Amerika Serikat. Kenaikan ini terjadi setelah harga minyak mentah turun dalam lima dari enam pekan terakhir karena kekhawatiran kelebihan pasokan. Pasar sedang menantikan rilis data pasokan dan permintaan dari OPEC, IEA, dan EIA pekan ini, sementara OPEC dan sekutunya berencana menunda kenaikan produksi pada kuartal pertama tahun depan untuk mengelola pasokan.
+2. Produksi minyak mentah Rusia sedikit meningkat pada Oktober menjadi rata-rata 9.411 mb/d, 43.000 b/d lebih tinggi dari September, namun masih 70.000 b/d di bawah kuota OPEC+ yang mencakup pemotongan kompensasi. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena beberapa kilang di India, China, dan Turki enggan menerima pasokan yang terkena sanksi.
+3. India, sebagai importir minyak mentah terbesar ketiga di dunia, mengurangi pembelian minyak dari Rusia untuk pengiriman Desember sebagai dampak sanksi Barat dan negosiasi dagang dengan Amerika Serikat. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia India tahun ini, tidak mengajukan pesanan untuk bulan tersebut. Pergeseran ini mendorong India untuk mencari pasokan alternatif dari kawasan Amerika dan Timur Tengah, mengingat sekitar 36% dari total impor minyak mentah India tahun ini berasal dari Rusia.</t>
         </is>
       </c>
     </row>
@@ -1979,9 +1984,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Indonesia berkomitmen untuk meningkatkan impor minyak mentah dari Amerika Serikat hingga US$15 miliar mulai Desember 2025, sebagai bagian dari kesepakatan tarif timbal balik. PT Pertamina (Persero) melalui anak usahanya PT Kilang Pertamina Internasional (KPI) berupaya mencari skema ekonomis untuk impor ini, dengan regulasi baru yang memungkinkan pembelian langsung tanpa lelang dari perusahaan AS.
-2. Harga minyak mentah global mengalami koreksi, dengan Brent turun 2,5% ke US$63,26 per barel dan WTI melemah 2,6% menjadi US$59,18 per barel pada 20 November 2025, dipicu laporan potensi berakhirnya perang Rusia-Ukraina dan peningkatan pasokan OPEC+ sebesar 137.000 barel per hari mulai November 2025. Harga Minyak Mentah Indonesia (ICP) Oktober 2025 ditetapkan US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya.
-3. Sanksi Amerika Serikat terhadap produsen minyak Rusia Rosneft PJSC dan Lukoil PJSC yang berlaku pada 21 November 2025 berpotensi menyebabkan hampir 48 juta barel minyak mentah Rusia terlantar di laut, memaksa pembeli di Asia mencari pasokan alternatif dan kapal tanker mencari tujuan baru di tengah tekanan untuk mematuhi sanksi.</t>
+          <t>1. Indonesia sedang menyiapkan Peraturan Presiden yang memperbolehkan PT Pertamina (Persero) untuk mengimpor energi langsung dari perusahaan Amerika Serikat tanpa proses lelang. Kebijakan ini merupakan tindak lanjut dari kesepakatan tarif timbal balik antara AS dan Indonesia pada Juli 2025, dengan tujuan mengurangi defisit perdagangan AS dengan Indonesia yang sekitar US$18 miliar, dan mengakselerasi komitmen impor minyak Indonesia dari AS senilai US$15 miliar. PT Kilang Pertamina Internasional (KPI) mencari cara agar impor minyak mentah dari AS dapat lebih ekonomis, dan pemerintah berencana meningkatkan impor minyak mentah dari AS mulai Desember 2025.
+2. Harga minyak global terkoreksi di pekan ini, dengan harga berjangka Brent turun US$1,63 (2,5%) menjadi US$63,26 per barel dan West Texas Intermediate (WTI) melemah US$1,56 (2,6%) menjadi US$59,18 per barel pada 20 November 2025. Penurunan ini dipengaruhi oleh laporan upaya AS untuk mengakhiri perang Rusia-Ukraina, yang berpotensi meningkatkan pasokan minyak Rusia ke pasar. Bersamaan dengan itu, sanksi AS terhadap Rosneft dan Lukoil mulai berlaku pada 21 November 2025, berpotensi membuat hampir 48 juta barel minyak mentah Rusia terlantar di laut dan mendorong pembeli di Asia mencari pasokan alternatif.
+3. Harga minyak mentah Indonesia (ICP) untuk Oktober 2025 ditetapkan sebesar US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya. Penurunan ini disebabkan oleh beberapa faktor seperti peningkatan suplai minyak oleh OPEC+ sebesar 137.000 barel per hari untuk November 2025, berkurangnya ketegangan geopolitik di Timur Tengah, pengolahan minyak mentah global yang diperkirakan mencapai titik terendah musiman 81,6 juta barel per hari pada Oktober, penguatan nilai tukar dolar AS, serta pemotongan harga jual resmi minyak mentah Arab Saudi untuk pembeli di Asia di tengah melemahnya permintaan dan perlambatan ekonomi Tiongkok.</t>
         </is>
       </c>
     </row>
@@ -1994,9 +1999,9 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.  Pada 27 November 2025, harga minyak Brent naik 0.2% menjadi USD 63.34 per barel dan West Texas Intermediate (WTI) menguat 0.8% menjadi USD 59.10 per barel. Kenaikan ini dipicu oleh harapan terobosan pembicaraan perdamaian antara Rusia dan Ukraina, yang menetralkan kekhawatiran pasokan akibat sanksi baru AS terhadap produsen Rusia.
-2.  Organisasi Negara-Negara Pengekspor Minyak dan sekutunya (OPEC+) diperkirakan akan mempertahankan tingkat produksi pada pertemuan mendatang. Selain itu, delapan negara anggota OPEC+ yang secara bertahap meningkatkan produksi pada tahun 2025 diproyeksikan untuk mempertahankan kebijakan jeda kenaikan produksi pada kuartal I 2026.
-3.  Ekspektasi pemangkasan suku bunga acuan oleh The Federal Reserve pada Desember 2025 turut mendorong harga minyak, mengingat penurunan suku bunga dapat mendukung pertumbuhan ekonomi global dan memperkuat permintaan minyak.</t>
+          <t>1.  Harga minyak menunjukkan tekanan turun selama minggu ini, dengan Brent diperdagangkan di kisaran USD 62-63 per barel dan WTI Crude di kisaran USD 58-59 per barel. Prediksi dari bank investasi seperti Goldman Sachs memperkirakan WTI Crude akan rata-rata USD 53 per barel pada 2026, sementara JP Morgan memproyeksikan Brent dapat turun ke kisaran USD 30-an per barel pada 2027 karena kekhawatiran pasokan berlebih sebesar 2 juta barel per hari. Harga bensin eceran di Amerika Serikat turun di bawah USD 3 per galon di banyak negara bagian, dengan beberapa lokasi mencapai USD 1.99 per galon.
+2.  Pasokan minyak global tetap kuat, didorong oleh produksi yang tangguh dari produsen non-OPEC seperti Amerika Serikat, Brasil, dan Guyana. Meskipun eksekutif shale AS melaporkan tantangan profitabilitas di bawah USD 60 per barel dan kenaikan biaya pengeboran sebesar 5 hingga 10 persen dari tahun lalu, produksi shale AS terus meningkat. OPEC+ diperkirakan akan mempertahankan tingkat produksi saat ini pada pertemuan tanggal 30 November, menunda peningkatan produksi yang direncanakan untuk kuartal I 2026 akibat kekhawatiran peningkatan persediaan global.
+3.  Pembicaraan damai yang diperbarui antara Rusia dan Ukraina memberikan tekanan signifikan pada harga minyak karena potensi pelonggaran sanksi yang dapat meningkatkan pasokan Rusia. Di sisi lain, konferensi energi di Timur Tengah menampilkan pandangan yang berbeda, dengan ADIPEC menyoroti permintaan energi jangka panjang yang kuat dan kebutuhan investasi besar USD 18.2 triliun untuk mencapai 123 juta barel per hari pada 2050, sementara Dii Desert Energy Summit berfokus pada percepatan pertumbuhan energi rendah karbon dan investasi yang melampaui bahan bakar fosil dengan rasio 2 berbanding 1. Cina terus mempercepat pembelian minyak mentah strategisnya, mengimpor sekitar 2.15 juta barel per hari dari Rusia dan menimbun lebih dari 1 juta barel per hari pada beberapa bulan di tahun 2025.</t>
         </is>
       </c>
     </row>
@@ -2027,9 +2032,9 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. PT Pertamina International Shipping (PIS) mengaktifkan Satuan Tugas Nataru 2025/2026 dan menyiagakan 332 kapal tanker utama ditambah 12 kapal cadangan serta 338 kapal pendukung pelabuhan mulai 1 Desember 2025 untuk menjamin kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia nasional.
-2. Harga minyak dunia menguat pada 1 Desember 2025, dengan Brent diperdagangkan pada US$63 per barel dan West Texas Intermediate (WTI) pada US$59.13 per barel, setelah OPEC+ menegaskan rencana menahan kenaikan produksi sepanjang kuartal I/2026 akibat pelemahan kondisi pasar musiman.
-3. Keputusan OPEC+ untuk mempertahankan jeda pasokan selama tiga bulan diambil di tengah proyeksi surplus pasokan global, dengan Badan Energi Internasional (IEA) memperkirakan rekor kelebihan pasokan pada tahun 2026 dan harga minyak telah merosot 15% sepanjang tahun hingga akhir November 2025.</t>
+          <t>1. OPEC+ menegaskan kembali rencana untuk menahan kenaikan produksi minyak mentah sepanjang kuartal I 2026 di tengah ekspektasi pelemahan pasar musiman dan potensi surplus pasokan global. Badan Energi Internasional (IEA) memproyeksikan rekor kelebihan pasokan pada 2026, sementara harga Brent diperdagangkan mendekati USD63/bbl dan West Texas Intermediate (WTI) mendekati USD59/bbl pada awal Desember 2025.
+2. Ketegangan geopolitik, seperti retorika dan pengerahan pasukan Amerika Serikat di bawah Presiden Donald Trump terkait Venezuela, serta upaya perundingan damai antara Amerika Serikat dan Rusia mengenai konflik Ukraina, terus menopang harga minyak dengan menambah premi risiko. Potensi gencatan senjata di Ukraina dapat membuka peluang pelonggaran sanksi terhadap Rusia dan peningkatan ekspor minyak, yang berpotensi menekan harga lebih lanjut.
+3. Indikasi kelebihan pasokan global tetap menjadi perhatian, didorong oleh lonjakan pasokan dari Amerika dan kenaikan persediaan minyak mentah AS sekitar 574.000 barel pada pekan lalu. Di sisi domestik, PT Pertamina International Shipping (PIS) menyiagakan 332 armada kapal tanker ditambah 12 kapal cadangan untuk memastikan kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia di Indonesia selama periode Natal 2025 dan Tahun Baru 2026.</t>
         </is>
       </c>
     </row>
@@ -2042,9 +2047,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.  Harga minyak global melemah sepanjang minggu dengan Brent diperdagangkan di bawah US$64/bbl dan kemudian turun menjadi US$61,94/bbl, sementara WTI mendekati US$60/bbl dan kemudian merosot ke US$58,25/bbl. Penurunan ini dipicu oleh pemulihan produksi 460.000 barel per hari di ladang minyak West Qurna 2 Irak dan kekhawatiran pasokan global berlebih dari OPEC+, Amerika Serikat, Brasil, dan Guyana. Stok minyak kargo di laut meningkat sekitar 2,5 juta barel per hari sejak pertengahan Agustus.
-2.  Medco Energi menargetkan produksi minyak dan gas bumi mencapai 160.000 barel setara minyak per hari (boepd) pada akhir 2025, meningkat dari 150.000 boepd pada kuartal III/2025, didukung oleh akuisisi 24% Participating Interest di Corridor PSC dan 45% PI di Sakakemang PSC. Perusahaan juga menandatangani perjanjian penjaminan untuk uang muka jual beli transaksi minyak mentah senilai maksimum US$80 juta. Pada semester I/2025, Medco mencatatkan laba bersih US$37,36 juta dari penjualan US$1,13 miliar.
-3.  Perkembangan geopolitik dan makroekonomi memengaruhi pasar minyak, termasuk negosiasi damai Rusia-Ukraina dan serangan terhadap infrastruktur energi Rusia. Negara-negara G7 dan Uni Eropa sedang mempertimbangkan larangan penuh layanan maritim untuk minyak Rusia. China melanjutkan penimbunan minyak mentah dengan perkiraan 800.000 hingga 900.000 barel per hari pada tahun 2026, meskipun pertumbuhan permintaan domestiknya diproyeksikan melambat menjadi 150.000 hingga 320.000 barel per hari pada tahun yang sama. Keputusan suku bunga Federal Reserve AS sebesar 25 basis poin juga dinantikan pasar.</t>
+          <t>1. Harga minyak global menunjukkan volatilitas dan tren bearish menjelang akhir pekan, berfluktuasi antara sekitar US$57–US$64 per barel. Penurunan suku bunga acuan Federal Reserve sebesar 25 basis poin sesuai ekspektasi pasar, namun kekhawatiran kelebihan pasokan global dan perkembangan negosiasi Rusia-Ukraina yang mengarah ke jalur perdamaian menekan harga minyak.
+2. Kekhawatiran kelebihan pasokan global menjadi sentimen dominan, dengan laporan International Energy Agency (IEA) mencatat pasokan minyak dunia mencapai 109 juta barel per hari pada November. IEA merevisi perkiraan surplus global untuk tahun 2026 menjadi 3.84 juta barel per hari, sedikit lebih rendah dari proyeksi sebelumnya, didorong oleh peningkatan proyeksi pertumbuhan permintaan.
+3. Tiongkok terus melakukan penimbunan minyak mentah strategis dan komersial dengan rata-rata sekitar 1 juta barel per hari pada tahun 2025, dan diproyeksikan sekitar 900.000 barel per hari pada tahun 2026, yang membantu meredam kelebihan pasokan di pasar global. Sementara itu, Kementerian Energi dan Sumber Daya Mineral Indonesia melaporkan kerugian devisa negara sebesar Rp523 triliun per tahun karena impor minyak yang mencapai 313 juta barel pada 2024.</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2065,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -2106,9 +2111,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Pada 1 November 2025, beberapa operator SPBU di Indonesia melakukan penyesuaian harga Bahan Bakar Minyak (BBM). PT Pertamina (Persero) menaikkan harga Dexlite dan Pertamina Dex masing-masing sebesar Rp200 per liter menjadi Rp13.900/liter dan Rp14.200/liter, sementara harga Pertamax, Pertamax Turbo, dan Pertamax Green tetap tidak berubah. SPBU Shell dan BP-AKR mayoritas menurunkan harga produk bensin mereka seperti Shell Super (turun Rp210 menjadi Rp12.680/liter) dan BP 92 (turun Rp210 menjadi Rp12.680/liter), namun menaikkan harga produk diesel mereka.
-2. PT Pertamina Patra Niaga telah menyalurkan 100.000 barel base fuel RON 92 kepada BP-AKR (PT Aneka Petroindo Raya) melalui mekanisme bisnis-ke-bisnis, yang memungkinkan ketersediaan kembali BBM BP 92 di jaringan SPBU BP-AKR. BP-AKR diperkirakan akan membeli tambahan 100.000 barel base fuel lagi yang dijadwalkan tiba pada pekan ketiga November 2025. Kementerian ESDM melaporkan PT Vivo Energy Indonesia juga hampir mencapai kesepakatan untuk pembelian sekitar 100.000 barel base fuel, sedangkan negosiasi dengan Shell Indonesia masih berlangsung.
-3. Menanggapi dugaan masalah kualitas BBM Pertalite yang menyebabkan keluhan kendaraan "brebet" di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM telah memeriksa hampir 300 SPBU dan hasil sementara menunjukkan tidak ada kontaminasi air atau etanol. Pertamina juga membuka posko pengaduan dan menyediakan 32 bengkel rekanan untuk perbaikan gratis bagi konsumen yang terdampak. Sementara itu, Kilang Pertamina Internasional (KPI) di Cilacap melanjutkan inisiatif energi hijau, meningkatkan produksi gasoline RON 92 menjadi 53.000 barel per hari dan memproduksi bahan bakar nabati (HVO serta PertaminaSAF).</t>
+          <t>1.  OPEC+ mengumumkan penghentian sementara kenaikan produksi pada kuartal I-2026 setelah kenaikan moderat pada Desember, sebagai upaya menyeimbangkan pasar di tengah tanda-tanda kelebihan pasokan. Morgan Stanley menaikkan proyeksi harga Brent menjadi USD60/bbl untuk semester I-2026, namun mencatat peningkatan produksi OPEC+ sebesar 500.000 bph dari Maret hingga Oktober jauh di bawah kenaikan kuota 2,6 mb/d.
+2.  Harga minyak mentah global melemah dan mencatat penurunan mingguan kedua, tertekan oleh peningkatan pasokan dari OPEC+ serta produsen non-anggota seperti Amerika Serikat dan Brasil. Brent turun menjadi sekitar USD63/bbl dan WTI di bawah USD60/bbl, dengan WTI anjlok sekitar 16% hingga 17% sepanjang tahun ini. Data American Petroleum Institute (API) menunjukkan stok minyak mentah Amerika Serikat naik 6,5 juta barel pada pekan lalu.
+3.  Kilang-kilang minyak di China, termasuk milik negara dan swasta, menghentikan pembelian minyak mentah asal Rusia setelah Amerika Serikat menjatuhkan sanksi terhadap produsen utama Moskow, memengaruhi sekitar 400.000 bpd atau hampir 45% dari total impor minyak Rusia ke China. Menanggapi pasar yang cukup mendapat pasokan dan lemahnya permintaan di Asia, Saudi Aramco memangkas harga minyak mentah unggulannya, Arab Light, untuk pasar Asia pada Desember sebesar USD1.20/bbl.</t>
         </is>
       </c>
     </row>
@@ -2121,9 +2126,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Pada 10 November 2025, PT Kilang Pertamina Internasional (KPI) memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) Complex hasil Proyek Refinery Development Master Plan (RDMP) Balikpapan. Proyek ini akan meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari, serta memproduksi bahan bakar standar Euro V, tambahan LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun. Di samping itu, PT Pertamina (Persero) menargetkan keputusan investasi akhir (FID) proyek Kilang Tuban senilai US$24 miliar, dengan kapasitas 300.000 barel per hari, dapat rampung pada awal Desember 2025.
-2. Sepanjang 9-12 November 2025, Kementerian ESDM mendorong pemerataan distribusi BBM dan mengatasi isu pasokan SPBU swasta yang kuota impornya telah habis. BP-AKR telah membeli 100.000 barel base fuel dari Pertamina Patra Niaga dan berencana menambah pembelian 200.000 barel, melalui skema business to business. Sementara itu, Shell dan Vivo masih dalam tahap negosiasi pembelian base fuel dari Pertamina.
-3. Pada 13 November 2025, Kementerian ESDM menyatakan akan mendorong penerapan bensin campuran 10% etanol (E10) pada tahun 2028, dengan kebutuhan etanol diperkirakan mencapai 1,4 juta kiloliter pada 2027. Implementasi E10 menghadapi tantangan seperti ketersediaan bahan baku dan infrastruktur produksi, serta usulan pembebasan etanol bahan bakar dari cukai sebesar Rp20.000 per liter oleh Asosiasi Produsen Spiritus dan Etanol Indonesia (Apsendo) untuk mencegah kenaikan harga produk.</t>
+          <t>1. Produksi minyak mentah Rusia pada Oktober mencapai rata-rata 9.411 juta barel per hari, meningkat 43.000 barel per hari dari September. Angka ini 70.000 barel per hari di bawah kuota OPEC+ yang mencakup pemotongan kompensasi, dengan target yang dibutuhkan sebesar 9.481 juta barel per hari. Sanksi terbaru Amerika Serikat terhadap sektor energi Rusia, termasuk Rosneft PJSC dan Lukoil PJSC, telah mengurangi ekspor minyak mentah karena keengganan beberapa kilang di India, China, dan Turki untuk menerima minyak yang terkena sanksi.
+2. Harga minyak global menunjukkan kenaikan, dengan Brent melewati US$64 per barel dan West Texas Intermediate (WTI) bergerak di kisaran US$60 per barel, didorong oleh upaya mengakhiri penutupan pemerintahan Amerika Serikat. Kekhawatiran akan kelebihan pasokan masih membebani pasar, menyebabkan harga minyak mentah turun dalam lima dari enam pekan terakhir. Organisasi Negara-Negara Pengekspor Minyak (OPEC) dan sekutunya mulai melonggarkan pembatasan produksi, namun berencana menunda kenaikan output pada kuartal pertama tahun depan, sementara produsen non-OPEC termasuk Amerika Serikat terus menambah pasokan.
+3. India, importir minyak terbesar ketiga di dunia, mengurangi pembelian minyak mentah dari Rusia untuk pengiriman Desember. Lima perusahaan kilang besar di India, yang menyumbang sekitar dua pertiga dari total impor minyak Rusia tahun ini, belum mengajukan pesanan. Perubahan pola pembelian ini sebagian besar didorong oleh sanksi Barat terhadap produsen minyak Rusia dan negosiasi dagang dengan Amerika Serikat, di mana India berkomitmen membeli lebih banyak minyak mentah dari Amerika Serikat. Akibatnya, kilang-kilang di India mulai mencari alternatif pasokan dari kawasan Amerika dan Timur Tengah, dengan Indian Oil Corp. berupaya membeli hingga 24 juta barel dari Amerika untuk pengiriman Januari hingga Maret.</t>
         </is>
       </c>
     </row>
@@ -2136,9 +2141,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Proyek Refinery Development Master Plan Balikpapan menunjukkan kemajuan signifikan dengan pengoperasian awal unit Residual Fluid Catalytic Cracking pada 10 November 2025, menargetkan peresmian pada pertengahan Desember 2025. Investasi sebesar US$7.4 miliar (Rp126 triliun) ini akan meningkatkan kapasitas produksi menjadi 360.000 barel per hari, memenuhi 22-25% kebutuhan energi nasional, dan memangkas ketergantungan impor bahan bakar minyak (BBM) sebesar 10-15% serta avtur mulai tahun 2026. Kilang ini juga akan menghasilkan produk berstandar Euro V dan petrokimia bernilai tinggi.
-2. Pertamina Patra Niaga mencatat peningkatan signifikan pada penjualan produk non-subsidi hingga Oktober 2025, dengan Pertamax Turbo naik 76% secara tahunan dan Pertamax Green 95 naik 80% dibandingkan 2024, yang menyebabkan Pertamina harus menambah pasokan Pertamax Turbo melalui produksi kilang dan impor. Sementara itu, penyaluran BBM bersubsidi seperti Pertalite dan Solar terkendali di bawah kuota masing-masing 10% dan 1.5% dari target 2025, menunjukkan pergeseran konsumen ke BBM beroktan lebih tinggi dan potensi penghematan kompensasi sebesar Rp12.61 triliun.
-3. Harga minyak mentah global mengalami penurunan dengan West Texas Intermediate (WTI) diperdagangkan di atas US$59 per barel dan Brent di bawah US$64 per barel, didorong oleh kenaikan persediaan bensin dan distillate di Amerika Serikat. Di sisi lain, sanksi Amerika Serikat terhadap produsen minyak Rusia dan Iran menghambat aliran minyak mentah ke China dan India, meskipun ketersediaan BBM nasional dipastikan aman dengan cadangan 18-19 hari. Untuk memenuhi permintaan domestik, operator SPBU BP-AKR juga mengandalkan pasokan base fuel dari Pertamina Patra Niaga.</t>
+          <t>1. Indonesia berkomitmen untuk meningkatkan impor minyak mentah dari Amerika Serikat hingga US$15 miliar mulai Desember 2025, sebagai bagian dari kesepakatan tarif timbal balik. PT Pertamina (Persero) melalui anak usahanya PT Kilang Pertamina Internasional (KPI) berupaya mencari skema ekonomis untuk impor ini, dengan regulasi baru yang memungkinkan pembelian langsung tanpa lelang dari perusahaan AS.
+2. Harga minyak mentah global mengalami koreksi, dengan Brent turun 2,5% ke US$63,26 per barel dan WTI melemah 2,6% menjadi US$59,18 per barel pada 20 November 2025, dipicu laporan potensi berakhirnya perang Rusia-Ukraina dan peningkatan pasokan OPEC+ sebesar 137.000 barel per hari mulai November 2025. Harga Minyak Mentah Indonesia (ICP) Oktober 2025 ditetapkan US$63,62 per barel, turun US$3,19 per barel dari bulan sebelumnya.
+3. Sanksi Amerika Serikat terhadap produsen minyak Rusia Rosneft PJSC dan Lukoil PJSC yang berlaku pada 21 November 2025 berpotensi menyebabkan hampir 48 juta barel minyak mentah Rusia terlantar di laut, memaksa pembeli di Asia mencari pasokan alternatif dan kapal tanker mencari tujuan baru di tengah tekanan untuk mematuhi sanksi.</t>
         </is>
       </c>
     </row>
@@ -2151,9 +2156,9 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. PT Pertamina (Persero) dan anak usahanya, PT Pertamina Patra Niaga (PPN), memperkuat pasokan dan distribusi bahan bakar minyak (BBM) serta LPG menjelang libur Natal 2025 dan Tahun Baru 2026 (Nataru), dengan proyeksi kenaikan konsumsi gasoline 2.3% dan LPG 3.3%. PPN menambah 1.4 juta kiloliter (kl) Pertalite dan memastikan ketahanan stok nasional BBM rata-rata 20.2 hari. Selain itu, stok BBM di SPBU swasta seperti Vivo, BP-AKR, dan Shell secara bertahap kembali tersedia mulai 23 November 2025, setelah membeli base fuel dari PPN. Vivo dan BP-AKR menyerap total 100.000 barel dan 230.000 barel base fuel, sementara Shell telah menyepakati pembelian 100.000 barel base fuel dari PPN.
-2. Pemerintah RI mulai menerapkan skema pembayaran dana kompensasi BBM bersubsidi secara bulanan (70% per bulan) kepada Pertamina efektif 19 November 2025, menggantikan pola kuartalan, yang diperkirakan akan memperkuat likuiditas Pertamina. BPH Migas merencanakan revisi Perpres Nomor 191 Tahun 2014 untuk mengatur tata kelola penjualan Pertalite agar lebih tepat sasaran. Pertamina Patra Niaga juga mempertimbangkan peluang impor Pertalite dari Amerika Serikat sebagai bagian dari strategi pengadaan, menunggu arahan pemerintah.
-3. PT Kilang Pertamina Internasional (KPI) Unit Balikpapan memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari pada 10 November 2025, bertujuan meningkatkan produksi produk bernilai tinggi dan mengurangi impor BBM. Selain itu, PT AGPA Refinery Complex (ARC) berkapasitas 500.000 ton per tahun di Balikpapan diresmikan pada 21 November 2025 sebagai fasilitas hilir sawit nasional baru, mendukung transformasi energi terbarukan berbasis kelapa sawit. Upaya menjaga operasional kilang Pertamina sebagai objek vital nasional diperkuat dengan pengerahan personel TNI dan BAIS mulai Desember 2025.</t>
+          <t>1.  Pada 27 November 2025, harga minyak Brent naik 0.2% menjadi USD 63.34 per barel dan West Texas Intermediate (WTI) menguat 0.8% menjadi USD 59.10 per barel. Kenaikan ini dipicu oleh harapan terobosan pembicaraan perdamaian antara Rusia dan Ukraina, yang menetralkan kekhawatiran pasokan akibat sanksi baru AS terhadap produsen Rusia.
+2.  Organisasi Negara-Negara Pengekspor Minyak dan sekutunya (OPEC+) diperkirakan akan mempertahankan tingkat produksi pada pertemuan mendatang. Selain itu, delapan negara anggota OPEC+ yang secara bertahap meningkatkan produksi pada tahun 2025 diproyeksikan untuk mempertahankan kebijakan jeda kenaikan produksi pada kuartal I 2026.
+3.  Ekspektasi pemangkasan suku bunga acuan oleh The Federal Reserve pada Desember 2025 turut mendorong harga minyak, mengingat penurunan suku bunga dapat mendukung pertumbuhan ekonomi global dan memperkuat permintaan minyak.</t>
         </is>
       </c>
     </row>
@@ -2184,9 +2189,9 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.  Pertamina Patra Niaga dan operator SPBU swasta seperti Shell, BP, serta Vivo menyesuaikan harga produk kilang nonsubsidi mereka per 1 Desember 2025, yang secara kompak mengalami kenaikan mengacu pada formula harga pemerintah dan tren harga minyak dunia. Namun, khusus tiga wilayah terdampak bencana di Aceh, Sumatra Utara, dan Sumatra Barat, harga BBM nonsubsidi relatif tidak mengalami penyesuaian signifikan. Terkait kinerja ekspor, Badan Pusat Statistik mencatat nilai ekspor Indonesia pada Oktober 2025 mencapai US$24,24 miliar, turun 2,31% dibanding tahun sebelumnya, terutama disebabkan oleh penurunan ekspor bahan bakar mineral sebesar 19,04% nilai dan 7,26% volume.
-2.  Pemerintah dan Pertamina Group mengintensifkan upaya penyaluran dan distribusi energi untuk wilayah Sumatra yang terdampak bencana banjir dan longsor di Aceh, Sumatra Utara, dan Sumatra Barat, serta dalam rangka persiapan periode Natal 2025 dan Tahun Baru 2026 (Nataru). Langkah-langkah yang diambil meliputi pengerahan armada tanker oleh PTPertamina International Shipping, penggunaan moda transportasi beragam seperti pesawat Hercules dan perintis untuk pengiriman BBM ke daerah terisolasi, serta peniadaan sementara sistem barcode MyPertamina untuk pembelian BBM subsidi di daerah bencana. Pertamina Patra Niaga juga berhasil menyuplai total 430.000 barel base fuel kepada SPBU swasta (Shell, BP-AKR, Vivo) untuk menormalisasi kembali ketersediaan BBM mereka.
-3.  Dalam pengembangan industri kilang, PT Kilang Pertamina Internasional (KPI) berkomitmen meningkatkan produksi petrokimia, dengan proyek Refinery Development Master Plan Balikpapan yang akan menghasilkan propilena sekitar 225.000 ton per tahun untuk mengurangi ketergantungan impor. Selain itu, pemerintah berencana merombak skema subsidi energi (BBM dan listrik) dalam dua tahun ke depan untuk meningkatkan efisiensi dan ketepatan sasaran. Pertamina Patra Niaga juga mempertimbangkan opsi impor Pertalite dari Amerika Serikat yang direncanakan mencapai 40% dari total pengadaan, sebagai bagian dari strategi ketahanan energi nasional.</t>
+          <t>1. PT Pertamina International Shipping (PIS) mengaktifkan Satuan Tugas Nataru 2025/2026 dan menyiagakan 332 kapal tanker utama ditambah 12 kapal cadangan serta 338 kapal pendukung pelabuhan mulai 1 Desember 2025 untuk menjamin kelancaran distribusi minyak mentah, BBM, LPG, dan petrokimia nasional.
+2. Harga minyak dunia menguat pada 1 Desember 2025, dengan Brent diperdagangkan pada US$63 per barel dan West Texas Intermediate (WTI) pada US$59.13 per barel, setelah OPEC+ menegaskan rencana menahan kenaikan produksi sepanjang kuartal I/2026 akibat pelemahan kondisi pasar musiman.
+3. Keputusan OPEC+ untuk mempertahankan jeda pasokan selama tiga bulan diambil di tengah proyeksi surplus pasokan global, dengan Badan Energi Internasional (IEA) memperkirakan rekor kelebihan pasokan pada tahun 2026 dan harga minyak telah merosot 15% sepanjang tahun hingga akhir November 2025.</t>
         </is>
       </c>
     </row>
@@ -2199,9 +2204,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Kementerian Energi dan Sumber Daya Mineral (ESDM) melaporkan devisa negara hilang Rp523 triliun per tahun akibat impor minyak dan Bahan Bakar Minyak (BBM), dengan produksi minyak Indonesia 221 juta barel pada 2024 berbanding impor 313 juta barel. Sebagai upaya penahanan laju impor, Pertamina Patra Niaga telah menyalurkan 430.000 barel base fuel kepada SPBU swasta, mengakhiri kekosongan stok sejak akhir Agustus 2025. Kementerian ESDM juga akan memutuskan kuota impor BBM untuk SPBU swasta pada tahun 2026.
-2. Pertamina Patra Niaga menaikkan harga BBM nonsubsidi per 1 Desember 2025, seperti Pertamax (RON 92) menjadi Rp12.750 per liter dari sebelumnya Rp12.200 per liter, sejalan dengan tren harga minyak global dan nilai tukar rupiah terhadap dolar Amerika Serikat. SPBU swasta juga melakukan penyesuaian harga serupa. Untuk periode Natal 2025 dan Tahun Baru 2026 (Nataru), Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan gasolin 5% dan avtur 1,6%, serta memberikan diskon avtur rata-rata 10% di 37 bandara strategis mulai 22 Desember 2025.
-3. Kilang Pertamina Internasional (KPI) mempercepat proyek Refinery Development Master Plan (RDMP) Balikpapan untuk meningkatkan kapasitas pengolahan minyak mentah dari 260.000 barel menjadi 360.000 barel per hari, dengan target operasi komersial pada 17 Desember 2025. Proyek ini bernilai US$7,4 miliar. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban, yang bernilai US$20,7 miliar hingga US$24 miliar, diharapkan diputuskan antara Pertamina dan Rosneft Singapore Pte Ltd pada pertengahan Desember 2025.</t>
+          <t>1.  Harga minyak global melemah sepanjang minggu dengan Brent diperdagangkan di bawah US$64/bbl dan kemudian turun menjadi US$61,94/bbl, sementara WTI mendekati US$60/bbl dan kemudian merosot ke US$58,25/bbl. Penurunan ini dipicu oleh pemulihan produksi 460.000 barel per hari di ladang minyak West Qurna 2 Irak dan kekhawatiran pasokan global berlebih dari OPEC+, Amerika Serikat, Brasil, dan Guyana. Stok minyak kargo di laut meningkat sekitar 2,5 juta barel per hari sejak pertengahan Agustus.
+2.  Medco Energi menargetkan produksi minyak dan gas bumi mencapai 160.000 barel setara minyak per hari (boepd) pada akhir 2025, meningkat dari 150.000 boepd pada kuartal III/2025, didukung oleh akuisisi 24% Participating Interest di Corridor PSC dan 45% PI di Sakakemang PSC. Perusahaan juga menandatangani perjanjian penjaminan untuk uang muka jual beli transaksi minyak mentah senilai maksimum US$80 juta. Pada semester I/2025, Medco mencatatkan laba bersih US$37,36 juta dari penjualan US$1,13 miliar.
+3.  Perkembangan geopolitik dan makroekonomi memengaruhi pasar minyak, termasuk negosiasi damai Rusia-Ukraina dan serangan terhadap infrastruktur energi Rusia. Negara-negara G7 dan Uni Eropa sedang mempertimbangkan larangan penuh layanan maritim untuk minyak Rusia. China melanjutkan penimbunan minyak mentah dengan perkiraan 800.000 hingga 900.000 barel per hari pada tahun 2026, meskipun pertumbuhan permintaan domestiknya diproyeksikan melambat menjadi 150.000 hingga 320.000 barel per hari pada tahun yang sama. Keputusan suku bunga Federal Reserve AS sebesar 25 basis poin juga dinantikan pasar.</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2222,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -2263,9 +2268,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. PT Pertamina Patra Niaga (PPN) menyalurkan 100.000 barel bahan bakar dasar impor kepada BP-AKR untuk menormalisasi pasokan BBM di SPBU swasta, dengan 100.000 barel tambahan diperkirakan tiba pada pekan ketiga November 2025. Badan usaha swasta lainnya, termasuk Vivo dan Shell, masih dalam tahap negosiasi untuk pembelian bahan bakar dasar dari Pertamina.
-2. Per 01 November 2025, Pertamina menaikkan harga Dexlite dan Pertamina Dex sebesar Rp200 per liter, menjadi Rp13.900 per liter dan Rp14.200 per liter. Pada periode yang sama, Shell dan BP-AKR juga menyesuaikan harga BBM, dengan mayoritas jenis bensin turun dan jenis diesel naik.
-3. Terkait dugaan masalah kualitas Pertalite di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM melakukan pengecekan di sekitar 300 SPBU. Hasil sementara menunjukkan bahwa Pertalite yang disalurkan "on specification" tanpa kontaminasi air atau etanol, dan Pertamina telah membuka 32 posko pengaduan serta bengkel rekanan untuk memberikan solusi dan kompensasi kepada masyarakat yang terdampak.</t>
+          <t>1. Pada 1 November 2025, beberapa operator SPBU di Indonesia melakukan penyesuaian harga Bahan Bakar Minyak (BBM). PT Pertamina (Persero) menaikkan harga Dexlite dan Pertamina Dex masing-masing sebesar Rp200 per liter menjadi Rp13.900/liter dan Rp14.200/liter, sementara harga Pertamax, Pertamax Turbo, dan Pertamax Green tetap tidak berubah. SPBU Shell dan BP-AKR mayoritas menurunkan harga produk bensin mereka seperti Shell Super (turun Rp210 menjadi Rp12.680/liter) dan BP 92 (turun Rp210 menjadi Rp12.680/liter), namun menaikkan harga produk diesel mereka.
+2. PT Pertamina Patra Niaga telah menyalurkan 100.000 barel base fuel RON 92 kepada BP-AKR (PT Aneka Petroindo Raya) melalui mekanisme bisnis-ke-bisnis, yang memungkinkan ketersediaan kembali BBM BP 92 di jaringan SPBU BP-AKR. BP-AKR diperkirakan akan membeli tambahan 100.000 barel base fuel lagi yang dijadwalkan tiba pada pekan ketiga November 2025. Kementerian ESDM melaporkan PT Vivo Energy Indonesia juga hampir mencapai kesepakatan untuk pembelian sekitar 100.000 barel base fuel, sedangkan negosiasi dengan Shell Indonesia masih berlangsung.
+3. Menanggapi dugaan masalah kualitas BBM Pertalite yang menyebabkan keluhan kendaraan "brebet" di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM telah memeriksa hampir 300 SPBU dan hasil sementara menunjukkan tidak ada kontaminasi air atau etanol. Pertamina juga membuka posko pengaduan dan menyediakan 32 bengkel rekanan untuk perbaikan gratis bagi konsumen yang terdampak. Sementara itu, Kilang Pertamina Internasional (KPI) di Cilacap melanjutkan inisiatif energi hijau, meningkatkan produksi gasoline RON 92 menjadi 53.000 barel per hari dan memproduksi bahan bakar nabati (HVO serta PertaminaSAF).</t>
         </is>
       </c>
     </row>
@@ -2278,9 +2283,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.  Pemerintah daerah Sumatra Barat dan Pertamina Patra Niaga telah mengambil langkah cepat untuk memulihkan kelangkaan bahan bakar minyak di wilayah tersebut pada November 2025, dengan Pertamina mempercepat pasokan melalui jalur darat dan mengoperasikan Integrated Terminal Teluk Kabung 24 jam sehari sejak 7 November 2025, yang meningkatkan kecepatan penyaluran sekitar 16%. Di sisi lain, Kementerian Energi dan Sumber Daya Mineral mendorong SPBU swasta untuk membeli base fuel dari Pertamina Patra Niaga untuk mengatasi ketimpangan pasokan, di mana BP-AKR telah sepakat membeli dua kargo atau 200.000 barel base fuel, dengan indikasi akan menambah pesanan hingga 300.000 barel, sementara Shell dan Vivo masih dalam tahap negosiasi.
-2.  Kementerian Keuangan mengawal penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan yang ditargetkan meningkatkan kapasitas produksi bahan bakar minyak hingga 142.000 barel per hari, LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun, dengan nilai investasi mencapai US$7,4 miliar. PT Kilang Pertamina Internasional telah melakukan pengoperasian awal Unit Residual Fluid Catalytic Cracking Complex di RDMP Balikpapan pada 10 November 2025, yang berhasil meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari dan produksi LPG menjadi 43.000 ton per tahun. Sementara itu, keputusan investasi akhir atau Final Investment Decision (FID) proyek Kilang Tuban berkapasitas 300.000 barel per hari dengan Rosneft ditargetkan rampung pada awal Desember 2025.
-3.  Kementerian Energi dan Sumber Daya Mineral mendorong penerapan bensin campuran 10% etanol (E10) pada 2028, atau berpotensi dipercepat menjadi 2027, dengan kebutuhan etanol mencapai 1,4 juta hingga 4 juta kiloliter. Proyek ini menghadapi tantangan seperti ketersediaan bahan baku, keterbatasan insentif, dan infrastruktur distribusi yang belum memadai, serta usulan dari Asosiasi Produsen Spiritus dan Etanol Indonesia untuk membebaskan etanol dari kategori barang kena cukai sebesar Rp20.000 per liter agar tidak membebani harga bensin hijau bagi konsumen. Pemerintah juga mencari keterlibatan sektor swasta, dengan Toyota Indonesia menunjukkan minat untuk mengembangkan pabrik bioetanol.</t>
+          <t>1. Pada 10 November 2025, PT Kilang Pertamina Internasional (KPI) memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) Complex hasil Proyek Refinery Development Master Plan (RDMP) Balikpapan. Proyek ini akan meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari, serta memproduksi bahan bakar standar Euro V, tambahan LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun. Di samping itu, PT Pertamina (Persero) menargetkan keputusan investasi akhir (FID) proyek Kilang Tuban senilai US$24 miliar, dengan kapasitas 300.000 barel per hari, dapat rampung pada awal Desember 2025.
+2. Sepanjang 9-12 November 2025, Kementerian ESDM mendorong pemerataan distribusi BBM dan mengatasi isu pasokan SPBU swasta yang kuota impornya telah habis. BP-AKR telah membeli 100.000 barel base fuel dari Pertamina Patra Niaga dan berencana menambah pembelian 200.000 barel, melalui skema business to business. Sementara itu, Shell dan Vivo masih dalam tahap negosiasi pembelian base fuel dari Pertamina.
+3. Pada 13 November 2025, Kementerian ESDM menyatakan akan mendorong penerapan bensin campuran 10% etanol (E10) pada tahun 2028, dengan kebutuhan etanol diperkirakan mencapai 1,4 juta kiloliter pada 2027. Implementasi E10 menghadapi tantangan seperti ketersediaan bahan baku dan infrastruktur produksi, serta usulan pembebasan etanol bahan bakar dari cukai sebesar Rp20.000 per liter oleh Asosiasi Produsen Spiritus dan Etanol Indonesia (Apsendo) untuk mencegah kenaikan harga produk.</t>
         </is>
       </c>
     </row>
@@ -2293,9 +2298,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.  Penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan senilai 7.4 miliar USD ditargetkan pada pertengahan Desember 2025. Proyek ini akan meningkatkan kapasitas kilang dari 260.000 barel per hari (bph) menjadi 360.000 bph, berpotensi mengurangi ketergantungan impor Bahan Bakar Minyak (BBM) hingga 15% dan memenuhi 22%-25% kebutuhan energi domestik. Unit Residual Fluid Catalytic Cracking (RFCC) Complex dengan kapasitas 90.000 bph telah mulai beroperasi pada 10 November 2025.
-2.  PT Pertamina Patra Niaga mencatat volume penjualan bensin dan solar sebesar 87 juta kiloliter (KL) per Oktober 2025, dengan 41% berasal dari produk non-subsidi. Penyaluran Solar bersubsidi terkendali 1.5% di bawah kuota 18.8 juta KL dan Pertalite 10% di bawah kuota 31.2 juta KL hingga Oktober 2025. Permintaan Pertamax Turbo (RON 98) melonjak 76%, sehingga Pertamina menambah pasokan melalui impor dan memastikan kesiapan distribusi untuk periode Natal dan Tahun Baru 2025-2026.
-3.  Dalam pengembangan biofuel, penjualan Pertamax Green 95 (E5) di 168 SPBU Pertamina mencatat pertumbuhan 80% dari 2024, dengan proyeksi kebutuhan bioetanol 4,800-5,000 KL per tahun untuk Pulau Jawa. Asosiasi Produsen Spiritus dan Etanol Indonesia (Aspendo) mengusulkan penghapusan cukai bioetanol fuel grade sebesar Rp20.000 per liter untuk menjaga harga kompetitif. Sementara itu, BP-AKR membeli 100.000 barel base fuel dari Pertamina Patra Niaga untuk mengatasi kekurangan stok, sedangkan Shell dan Vivo masih dalam negosiasi business-to-business untuk pengadaan base fuel.</t>
+          <t>1. Proyek Refinery Development Master Plan Balikpapan menunjukkan kemajuan signifikan dengan pengoperasian awal unit Residual Fluid Catalytic Cracking pada 10 November 2025, menargetkan peresmian pada pertengahan Desember 2025. Investasi sebesar US$7.4 miliar (Rp126 triliun) ini akan meningkatkan kapasitas produksi menjadi 360.000 barel per hari, memenuhi 22-25% kebutuhan energi nasional, dan memangkas ketergantungan impor bahan bakar minyak (BBM) sebesar 10-15% serta avtur mulai tahun 2026. Kilang ini juga akan menghasilkan produk berstandar Euro V dan petrokimia bernilai tinggi.
+2. Pertamina Patra Niaga mencatat peningkatan signifikan pada penjualan produk non-subsidi hingga Oktober 2025, dengan Pertamax Turbo naik 76% secara tahunan dan Pertamax Green 95 naik 80% dibandingkan 2024, yang menyebabkan Pertamina harus menambah pasokan Pertamax Turbo melalui produksi kilang dan impor. Sementara itu, penyaluran BBM bersubsidi seperti Pertalite dan Solar terkendali di bawah kuota masing-masing 10% dan 1.5% dari target 2025, menunjukkan pergeseran konsumen ke BBM beroktan lebih tinggi dan potensi penghematan kompensasi sebesar Rp12.61 triliun.
+3. Harga minyak mentah global mengalami penurunan dengan West Texas Intermediate (WTI) diperdagangkan di atas US$59 per barel dan Brent di bawah US$64 per barel, didorong oleh kenaikan persediaan bensin dan distillate di Amerika Serikat. Di sisi lain, sanksi Amerika Serikat terhadap produsen minyak Rusia dan Iran menghambat aliran minyak mentah ke China dan India, meskipun ketersediaan BBM nasional dipastikan aman dengan cadangan 18-19 hari. Untuk memenuhi permintaan domestik, operator SPBU BP-AKR juga mengandalkan pasokan base fuel dari Pertamina Patra Niaga.</t>
         </is>
       </c>
     </row>
@@ -2308,9 +2313,9 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. PT Pertamina Patra Niaga memperkuat pasokan BBM untuk periode Natal 2025 dan Tahun Baru 2026. Ini mencakup penambahan 1,4 juta kiloliter Pertalite dari produksi kilang domestik dan impor baru, dengan target ketahanan stok 21-23 hari per 25 November 2025. Kilang Pertamina Internasional juga memulai operasi awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari di Kilang Balikpapan sejak 10 November 2025, yang akan meningkatkan produksi gasoline dan LPG serta mengurangi impor.
-2. Pasokan BBM di SPBU swasta mulai normal kembali setelah mencapai kesepakatan pembelian base fuel dari Pertamina Patra Niaga. Vivo Energy Indonesia telah menerima 100.000 barel Revvo 92 (RON 92) yang mulai tersedia bertahap sejak 23 November 2025. BP-AKR menambah pembelian base fuel menjadi total 230.000 barel dari Pertamina Patra Niaga per 27 November 2025. Shell Indonesia juga menyelesaikan kesepakatan pada 25 November 2025 untuk membeli 100.000 barel base fuel, dengan harapan stok pulih akhir November 2025.
-3. Distribusi energi menghadapi tantangan cuaca ekstrem dan diperkuat dengan langkah keamanan. Dua kapal pengangkut Pertalite dan Biosolar tidak dapat bersandar di Belawan, Sumatra Utara sejak 23 November 2025 karena cuaca ekstrem, menyebabkan penyesuaian pola suplai dari terminal alternatif. Untuk mengamankan infrastruktur energi nasional, pemerintah akan mengerahkan personel TNI untuk menjaga kilang minyak dan terminal BBM Pertamina yang memiliki kapasitas pengolahan 1 juta barel per hari dan 231 terminal migas, dimulai pada Desember 2025.</t>
+          <t>1. PT Pertamina (Persero) dan anak usahanya, PT Pertamina Patra Niaga (PPN), memperkuat pasokan dan distribusi bahan bakar minyak (BBM) serta LPG menjelang libur Natal 2025 dan Tahun Baru 2026 (Nataru), dengan proyeksi kenaikan konsumsi gasoline 2.3% dan LPG 3.3%. PPN menambah 1.4 juta kiloliter (kl) Pertalite dan memastikan ketahanan stok nasional BBM rata-rata 20.2 hari. Selain itu, stok BBM di SPBU swasta seperti Vivo, BP-AKR, dan Shell secara bertahap kembali tersedia mulai 23 November 2025, setelah membeli base fuel dari PPN. Vivo dan BP-AKR menyerap total 100.000 barel dan 230.000 barel base fuel, sementara Shell telah menyepakati pembelian 100.000 barel base fuel dari PPN.
+2. Pemerintah RI mulai menerapkan skema pembayaran dana kompensasi BBM bersubsidi secara bulanan (70% per bulan) kepada Pertamina efektif 19 November 2025, menggantikan pola kuartalan, yang diperkirakan akan memperkuat likuiditas Pertamina. BPH Migas merencanakan revisi Perpres Nomor 191 Tahun 2014 untuk mengatur tata kelola penjualan Pertalite agar lebih tepat sasaran. Pertamina Patra Niaga juga mempertimbangkan peluang impor Pertalite dari Amerika Serikat sebagai bagian dari strategi pengadaan, menunggu arahan pemerintah.
+3. PT Kilang Pertamina Internasional (KPI) Unit Balikpapan memulai pengoperasian awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari pada 10 November 2025, bertujuan meningkatkan produksi produk bernilai tinggi dan mengurangi impor BBM. Selain itu, PT AGPA Refinery Complex (ARC) berkapasitas 500.000 ton per tahun di Balikpapan diresmikan pada 21 November 2025 sebagai fasilitas hilir sawit nasional baru, mendukung transformasi energi terbarukan berbasis kelapa sawit. Upaya menjaga operasional kilang Pertamina sebagai objek vital nasional diperkuat dengan pengerahan personel TNI dan BAIS mulai Desember 2025.</t>
         </is>
       </c>
     </row>
@@ -2341,9 +2346,9 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Kilang Pertamina Internasional (KPI) menargetkan produksi untuk November 2025 sebesar 8 juta barel gasoline, 10,7 juta barel gasoil, dan 2,2 juta barel avtur. Untuk Desember 2025, produksi gasoil seri ditingkatkan menjadi sekitar 11,5 juta barel, sementara volume gasoline dan avtur dipertahankan sesuai rencana November 2025 guna mendukung kelancaran pasokan BBM menjelang periode Natal dan Tahun Baru 2026.
-2. Badan Pusat Statistik (BPS) mencatat volume ekspor bahan bakar mineral (BBM) Indonesia turun sebesar 7,26% pada Oktober 2025 dibandingkan periode yang sama tahun lalu. Penurunan ini merupakan bagian dari total ekspor migas yang turun 33,60% secara tahunan menjadi US$0,89 miliar.
-3. PT Pertamina Patra Niaga (PPN) memasok total 430.000 barel base fuel kepada badan usaha SPBU swasta seperti Shell, Vivo, dan BP-AKR untuk memastikan ketersediaan BBM. PPN juga memproyeksikan peningkatan konsumsi gasoline sebesar 8,4% dan avtur sebesar 2,4% selama periode Nataru 2025/2026 di wilayah Jawa Timur, Bali, dan Nusa Tenggara.</t>
+          <t>1.  Pertamina Patra Niaga dan operator SPBU swasta seperti Shell, BP, serta Vivo menyesuaikan harga produk kilang nonsubsidi mereka per 1 Desember 2025, yang secara kompak mengalami kenaikan mengacu pada formula harga pemerintah dan tren harga minyak dunia. Namun, khusus tiga wilayah terdampak bencana di Aceh, Sumatra Utara, dan Sumatra Barat, harga BBM nonsubsidi relatif tidak mengalami penyesuaian signifikan. Terkait kinerja ekspor, Badan Pusat Statistik mencatat nilai ekspor Indonesia pada Oktober 2025 mencapai US$24,24 miliar, turun 2,31% dibanding tahun sebelumnya, terutama disebabkan oleh penurunan ekspor bahan bakar mineral sebesar 19,04% nilai dan 7,26% volume.
+2.  Pemerintah dan Pertamina Group mengintensifkan upaya penyaluran dan distribusi energi untuk wilayah Sumatra yang terdampak bencana banjir dan longsor di Aceh, Sumatra Utara, dan Sumatra Barat, serta dalam rangka persiapan periode Natal 2025 dan Tahun Baru 2026 (Nataru). Langkah-langkah yang diambil meliputi pengerahan armada tanker oleh PTPertamina International Shipping, penggunaan moda transportasi beragam seperti pesawat Hercules dan perintis untuk pengiriman BBM ke daerah terisolasi, serta peniadaan sementara sistem barcode MyPertamina untuk pembelian BBM subsidi di daerah bencana. Pertamina Patra Niaga juga berhasil menyuplai total 430.000 barel base fuel kepada SPBU swasta (Shell, BP-AKR, Vivo) untuk menormalisasi kembali ketersediaan BBM mereka.
+3.  Dalam pengembangan industri kilang, PT Kilang Pertamina Internasional (KPI) berkomitmen meningkatkan produksi petrokimia, dengan proyek Refinery Development Master Plan Balikpapan yang akan menghasilkan propilena sekitar 225.000 ton per tahun untuk mengurangi ketergantungan impor. Selain itu, pemerintah berencana merombak skema subsidi energi (BBM dan listrik) dalam dua tahun ke depan untuk meningkatkan efisiensi dan ketepatan sasaran. Pertamina Patra Niaga juga mempertimbangkan opsi impor Pertalite dari Amerika Serikat yang direncanakan mencapai 40% dari total pengadaan, sebagai bagian dari strategi ketahanan energi nasional.</t>
         </is>
       </c>
     </row>
@@ -2356,9 +2361,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.  Kementerian Energi dan Sumber Daya Mineral melaporkan Indonesia kehilangan devisa sebesar Rp523 triliun per tahun akibat impor minyak. Pada 2024, produksi minyak Indonesia mencapai 221 juta barel, sementara impor minyak nasional sebesar 313 juta barel yang mencakup 112 juta barel minyak mentah dan 201 juta barel Bahan Bakar Minyak (BBM), dengan konsumsi BBM nasional sebesar 532 juta barel. Pemerintah berupaya mengurangi ketergantungan impor melalui kebijakan seperti implementasi B50 pada 2026 dan campuran etanol 10% pada 2027, serta menolak permintaan tambahan kuota impor BBM dari SPBU swasta pada 2025 dengan mengarahkan pembelian base fuel dari PT Pertamina Patra Niaga.
-2.  Proyek Refinery Development Master Plan (RDMP) Balikpapan dijadwalkan beroperasi komersial pada 17 Desember 2025, dengan peningkatan kapasitas unit distilasi minyak mentah (CDU) dari 260.000 barel per hari (bph) menjadi 360.000 bph, yang akan meningkatkan total kapasitas CDU nasional dari 1.17 juta bph menjadi 1.26 juta bph pada akhir 2025. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban yang bernilai sekitar US$20.7 miliar hingga US$24 miliar, dengan PJSC Rosneft Oil Company sebagai mitra utama, ditargetkan rampung pada akhir Desember 2025. PT Pertamina Patra Niaga juga telah menyalurkan total 430.000 barel base fuel kepada SPBU swasta per Desember 2025 untuk mengatasi kekosongan stok sebelumnya.
-3.  Distribusi BBM dan LPG di Aceh, Sumatra Utara, dan Sumatra Barat menghadapi tantangan akibat bencana alam, mendorong PT Pertamina Patra Niaga untuk mengoptimalkan berbagai moda transportasi termasuk jalur udara menggunakan pesawat Air Tractor guna memastikan pasokan energi mencapai wilayah terisolir. Kementerian Energi dan Sumber Daya Mineral memperpanjang relaksasi pembelian BBM subsidi tanpa penggunaan QR code di wilayah terdampak bencana hingga akhir Desember 2025. Selain itu, harga BBM nonsubsidi dari Pertamina, Shell, BP-AKR, dan Vivo mengalami penyesuaian kenaikan per 1 Desember 2025. Menjelang Natal dan Tahun Baru 2026, Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan BBM jenis gasolin sebesar 5% dan avtur 1.6%, serta penurunan gasoil sebesar 4% di wilayah Jawa Tengah-DI Yogyakarta.</t>
+          <t>1. Kementerian Energi dan Sumber Daya Mineral (ESDM) melaporkan devisa negara hilang Rp523 triliun per tahun akibat impor minyak dan Bahan Bakar Minyak (BBM), dengan produksi minyak Indonesia 221 juta barel pada 2024 berbanding impor 313 juta barel. Sebagai upaya penahanan laju impor, Pertamina Patra Niaga telah menyalurkan 430.000 barel base fuel kepada SPBU swasta, mengakhiri kekosongan stok sejak akhir Agustus 2025. Kementerian ESDM juga akan memutuskan kuota impor BBM untuk SPBU swasta pada tahun 2026.
+2. Pertamina Patra Niaga menaikkan harga BBM nonsubsidi per 1 Desember 2025, seperti Pertamax (RON 92) menjadi Rp12.750 per liter dari sebelumnya Rp12.200 per liter, sejalan dengan tren harga minyak global dan nilai tukar rupiah terhadap dolar Amerika Serikat. SPBU swasta juga melakukan penyesuaian harga serupa. Untuk periode Natal 2025 dan Tahun Baru 2026 (Nataru), Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan gasolin 5% dan avtur 1,6%, serta memberikan diskon avtur rata-rata 10% di 37 bandara strategis mulai 22 Desember 2025.
+3. Kilang Pertamina Internasional (KPI) mempercepat proyek Refinery Development Master Plan (RDMP) Balikpapan untuk meningkatkan kapasitas pengolahan minyak mentah dari 260.000 barel menjadi 360.000 barel per hari, dengan target operasi komersial pada 17 Desember 2025. Proyek ini bernilai US$7,4 miliar. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban, yang bernilai US$20,7 miliar hingga US$24 miliar, diharapkan diputuskan antara Pertamina dan Rosneft Singapore Pte Ltd pada pertengahan Desember 2025.</t>
         </is>
       </c>
     </row>
@@ -2374,10 +2379,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="11.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.90625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.36328125" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2422,6 +2427,163 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal awal</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal akhir</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Summary Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina Patra Niaga (PPN) menyalurkan 100.000 barel bahan bakar dasar impor kepada BP-AKR untuk menormalisasi pasokan BBM di SPBU swasta, dengan 100.000 barel tambahan diperkirakan tiba pada pekan ketiga November 2025. Badan usaha swasta lainnya, termasuk Vivo dan Shell, masih dalam tahap negosiasi untuk pembelian bahan bakar dasar dari Pertamina.
+2. Per 01 November 2025, Pertamina menaikkan harga Dexlite dan Pertamina Dex sebesar Rp200 per liter, menjadi Rp13.900 per liter dan Rp14.200 per liter. Pada periode yang sama, Shell dan BP-AKR juga menyesuaikan harga BBM, dengan mayoritas jenis bensin turun dan jenis diesel naik.
+3. Terkait dugaan masalah kualitas Pertalite di Jawa Timur, Pertamina Patra Niaga bersama Lemigas Kementerian ESDM melakukan pengecekan di sekitar 300 SPBU. Hasil sementara menunjukkan bahwa Pertalite yang disalurkan "on specification" tanpa kontaminasi air atau etanol, dan Pertamina telah membuka 32 posko pengaduan serta bengkel rekanan untuk memberikan solusi dan kompensasi kepada masyarakat yang terdampak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.  Pemerintah daerah Sumatra Barat dan Pertamina Patra Niaga telah mengambil langkah cepat untuk memulihkan kelangkaan bahan bakar minyak di wilayah tersebut pada November 2025, dengan Pertamina mempercepat pasokan melalui jalur darat dan mengoperasikan Integrated Terminal Teluk Kabung 24 jam sehari sejak 7 November 2025, yang meningkatkan kecepatan penyaluran sekitar 16%. Di sisi lain, Kementerian Energi dan Sumber Daya Mineral mendorong SPBU swasta untuk membeli base fuel dari Pertamina Patra Niaga untuk mengatasi ketimpangan pasokan, di mana BP-AKR telah sepakat membeli dua kargo atau 200.000 barel base fuel, dengan indikasi akan menambah pesanan hingga 300.000 barel, sementara Shell dan Vivo masih dalam tahap negosiasi.
+2.  Kementerian Keuangan mengawal penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan yang ditargetkan meningkatkan kapasitas produksi bahan bakar minyak hingga 142.000 barel per hari, LPG 336.000 ton per tahun, dan propylene 300.000 ton per tahun, dengan nilai investasi mencapai US$7,4 miliar. PT Kilang Pertamina Internasional telah melakukan pengoperasian awal Unit Residual Fluid Catalytic Cracking Complex di RDMP Balikpapan pada 10 November 2025, yang berhasil meningkatkan kapasitas pengolahan minyak mentah dari 260.000 menjadi 360.000 barel per hari dan produksi LPG menjadi 43.000 ton per tahun. Sementara itu, keputusan investasi akhir atau Final Investment Decision (FID) proyek Kilang Tuban berkapasitas 300.000 barel per hari dengan Rosneft ditargetkan rampung pada awal Desember 2025.
+3.  Kementerian Energi dan Sumber Daya Mineral mendorong penerapan bensin campuran 10% etanol (E10) pada 2028, atau berpotensi dipercepat menjadi 2027, dengan kebutuhan etanol mencapai 1,4 juta hingga 4 juta kiloliter. Proyek ini menghadapi tantangan seperti ketersediaan bahan baku, keterbatasan insentif, dan infrastruktur distribusi yang belum memadai, serta usulan dari Asosiasi Produsen Spiritus dan Etanol Indonesia untuk membebaskan etanol dari kategori barang kena cukai sebesar Rp20.000 per liter agar tidak membebani harga bensin hijau bagi konsumen. Pemerintah juga mencari keterlibatan sektor swasta, dengan Toyota Indonesia menunjukkan minat untuk mengembangkan pabrik bioetanol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.  Penyelesaian Proyek Refinery Development Master Plan (RDMP) Balikpapan senilai 7.4 miliar USD ditargetkan pada pertengahan Desember 2025. Proyek ini akan meningkatkan kapasitas kilang dari 260.000 barel per hari (bph) menjadi 360.000 bph, berpotensi mengurangi ketergantungan impor Bahan Bakar Minyak (BBM) hingga 15% dan memenuhi 22%-25% kebutuhan energi domestik. Unit Residual Fluid Catalytic Cracking (RFCC) Complex dengan kapasitas 90.000 bph telah mulai beroperasi pada 10 November 2025.
+2.  PT Pertamina Patra Niaga mencatat volume penjualan bensin dan solar sebesar 87 juta kiloliter (KL) per Oktober 2025, dengan 41% berasal dari produk non-subsidi. Penyaluran Solar bersubsidi terkendali 1.5% di bawah kuota 18.8 juta KL dan Pertalite 10% di bawah kuota 31.2 juta KL hingga Oktober 2025. Permintaan Pertamax Turbo (RON 98) melonjak 76%, sehingga Pertamina menambah pasokan melalui impor dan memastikan kesiapan distribusi untuk periode Natal dan Tahun Baru 2025-2026.
+3.  Dalam pengembangan biofuel, penjualan Pertamax Green 95 (E5) di 168 SPBU Pertamina mencatat pertumbuhan 80% dari 2024, dengan proyeksi kebutuhan bioetanol 4,800-5,000 KL per tahun untuk Pulau Jawa. Asosiasi Produsen Spiritus dan Etanol Indonesia (Aspendo) mengusulkan penghapusan cukai bioetanol fuel grade sebesar Rp20.000 per liter untuk menjaga harga kompetitif. Sementara itu, BP-AKR membeli 100.000 barel base fuel dari Pertamina Patra Niaga untuk mengatasi kekurangan stok, sedangkan Shell dan Vivo masih dalam negosiasi business-to-business untuk pengadaan base fuel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1. PT Pertamina Patra Niaga memperkuat pasokan BBM untuk periode Natal 2025 dan Tahun Baru 2026. Ini mencakup penambahan 1,4 juta kiloliter Pertalite dari produksi kilang domestik dan impor baru, dengan target ketahanan stok 21-23 hari per 25 November 2025. Kilang Pertamina Internasional juga memulai operasi awal unit Residual Fluid Catalytic Cracking (RFCC) berkapasitas 90 ribu barel per hari di Kilang Balikpapan sejak 10 November 2025, yang akan meningkatkan produksi gasoline dan LPG serta mengurangi impor.
+2. Pasokan BBM di SPBU swasta mulai normal kembali setelah mencapai kesepakatan pembelian base fuel dari Pertamina Patra Niaga. Vivo Energy Indonesia telah menerima 100.000 barel Revvo 92 (RON 92) yang mulai tersedia bertahap sejak 23 November 2025. BP-AKR menambah pembelian base fuel menjadi total 230.000 barel dari Pertamina Patra Niaga per 27 November 2025. Shell Indonesia juga menyelesaikan kesepakatan pada 25 November 2025 untuk membeli 100.000 barel base fuel, dengan harapan stok pulih akhir November 2025.
+3. Distribusi energi menghadapi tantangan cuaca ekstrem dan diperkuat dengan langkah keamanan. Dua kapal pengangkut Pertalite dan Biosolar tidak dapat bersandar di Belawan, Sumatra Utara sejak 23 November 2025 karena cuaca ekstrem, menyebabkan penyesuaian pola suplai dari terminal alternatif. Untuk mengamankan infrastruktur energi nasional, pemerintah akan mengerahkan personel TNI untuk menjaga kilang minyak dan terminal BBM Pertamina yang memiliki kapasitas pengolahan 1 juta barel per hari dan 231 terminal migas, dimulai pada Desember 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Kilang Pertamina Internasional (KPI) menargetkan produksi untuk November 2025 sebesar 8 juta barel gasoline, 10,7 juta barel gasoil, dan 2,2 juta barel avtur. Untuk Desember 2025, produksi gasoil seri ditingkatkan menjadi sekitar 11,5 juta barel, sementara volume gasoline dan avtur dipertahankan sesuai rencana November 2025 guna mendukung kelancaran pasokan BBM menjelang periode Natal dan Tahun Baru 2026.
+2. Badan Pusat Statistik (BPS) mencatat volume ekspor bahan bakar mineral (BBM) Indonesia turun sebesar 7,26% pada Oktober 2025 dibandingkan periode yang sama tahun lalu. Penurunan ini merupakan bagian dari total ekspor migas yang turun 33,60% secara tahunan menjadi US$0,89 miliar.
+3. PT Pertamina Patra Niaga (PPN) memasok total 430.000 barel base fuel kepada badan usaha SPBU swasta seperti Shell, Vivo, dan BP-AKR untuk memastikan ketersediaan BBM. PPN juga memproyeksikan peningkatan konsumsi gasoline sebesar 8,4% dan avtur sebesar 2,4% selama periode Nataru 2025/2026 di wilayah Jawa Timur, Bali, dan Nusa Tenggara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.  Kementerian Energi dan Sumber Daya Mineral melaporkan Indonesia kehilangan devisa sebesar Rp523 triliun per tahun akibat impor minyak. Pada 2024, produksi minyak Indonesia mencapai 221 juta barel, sementara impor minyak nasional sebesar 313 juta barel yang mencakup 112 juta barel minyak mentah dan 201 juta barel Bahan Bakar Minyak (BBM), dengan konsumsi BBM nasional sebesar 532 juta barel. Pemerintah berupaya mengurangi ketergantungan impor melalui kebijakan seperti implementasi B50 pada 2026 dan campuran etanol 10% pada 2027, serta menolak permintaan tambahan kuota impor BBM dari SPBU swasta pada 2025 dengan mengarahkan pembelian base fuel dari PT Pertamina Patra Niaga.
+2.  Proyek Refinery Development Master Plan (RDMP) Balikpapan dijadwalkan beroperasi komersial pada 17 Desember 2025, dengan peningkatan kapasitas unit distilasi minyak mentah (CDU) dari 260.000 barel per hari (bph) menjadi 360.000 bph, yang akan meningkatkan total kapasitas CDU nasional dari 1.17 juta bph menjadi 1.26 juta bph pada akhir 2025. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban yang bernilai sekitar US$20.7 miliar hingga US$24 miliar, dengan PJSC Rosneft Oil Company sebagai mitra utama, ditargetkan rampung pada akhir Desember 2025. PT Pertamina Patra Niaga juga telah menyalurkan total 430.000 barel base fuel kepada SPBU swasta per Desember 2025 untuk mengatasi kekosongan stok sebelumnya.
+3.  Distribusi BBM dan LPG di Aceh, Sumatra Utara, dan Sumatra Barat menghadapi tantangan akibat bencana alam, mendorong PT Pertamina Patra Niaga untuk mengoptimalkan berbagai moda transportasi termasuk jalur udara menggunakan pesawat Air Tractor guna memastikan pasokan energi mencapai wilayah terisolir. Kementerian Energi dan Sumber Daya Mineral memperpanjang relaksasi pembelian BBM subsidi tanpa penggunaan QR code di wilayah terdampak bencana hingga akhir Desember 2025. Selain itu, harga BBM nonsubsidi dari Pertamina, Shell, BP-AKR, dan Vivo mengalami penyesuaian kenaikan per 1 Desember 2025. Menjelang Natal dan Tahun Baru 2026, Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan BBM jenis gasolin sebesar 5% dan avtur 1.6%, serta penurunan gasoil sebesar 4% di wilayah Jawa Tengah-DI Yogyakarta.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2432,7 +2594,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
@@ -2486,7 +2648,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -2765,7 +2927,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -3029,7 +3191,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -3113,7 +3275,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -3197,7 +3359,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -3266,7 +3428,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">

--- a/src/results/(News)Sentiment.xlsx
+++ b/src/results/(News)Sentiment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pekerjaan\Dashboard-Pertamina-VeloCT\src\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446701BF-A547-4AF7-ADB1-01BD041413ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EE85EA-4FAE-4C58-9105-03C28E5259E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(Summary)All" sheetId="1" r:id="rId1"/>
@@ -28,18 +28,19 @@
     <sheet name="(Summary)PDB" sheetId="13" r:id="rId13"/>
     <sheet name="(Summary)Biodiesel" sheetId="14" r:id="rId14"/>
     <sheet name="(Summary)Bioetanol" sheetId="15" r:id="rId15"/>
-    <sheet name="(Summary)RUPTL" sheetId="16" r:id="rId16"/>
-    <sheet name="(Summary)Harga Minyak" sheetId="17" r:id="rId17"/>
-    <sheet name="(Summary)Volume Minyak" sheetId="18" r:id="rId18"/>
-    <sheet name="(Summary)Harga Produk Kilang" sheetId="19" r:id="rId19"/>
-    <sheet name="(Summary)Volume Produk Kilang" sheetId="20" r:id="rId20"/>
+    <sheet name="(Summary)SAF" sheetId="21" r:id="rId16"/>
+    <sheet name="(Summary)RUPTL" sheetId="16" r:id="rId17"/>
+    <sheet name="(Summary)Harga Minyak" sheetId="17" r:id="rId18"/>
+    <sheet name="(Summary)Volume Minyak" sheetId="18" r:id="rId19"/>
+    <sheet name="(Summary)Harga Produk Kilang" sheetId="19" r:id="rId20"/>
+    <sheet name="(Summary)Volume Produk Kilang" sheetId="20" r:id="rId21"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
   <si>
     <t>date</t>
   </si>
@@ -703,6 +704,46 @@
     <t>1.  Kementerian Energi dan Sumber Daya Mineral melaporkan Indonesia kehilangan devisa sebesar Rp523 triliun per tahun akibat impor minyak. Pada 2024, produksi minyak Indonesia mencapai 221 juta barel, sementara impor minyak nasional sebesar 313 juta barel yang mencakup 112 juta barel minyak mentah dan 201 juta barel Bahan Bakar Minyak (BBM), dengan konsumsi BBM nasional sebesar 532 juta barel. Pemerintah berupaya mengurangi ketergantungan impor melalui kebijakan seperti implementasi B50 pada 2026 dan campuran etanol 10% pada 2027, serta menolak permintaan tambahan kuota impor BBM dari SPBU swasta pada 2025 dengan mengarahkan pembelian base fuel dari PT Pertamina Patra Niaga.
 2.  Proyek Refinery Development Master Plan (RDMP) Balikpapan dijadwalkan beroperasi komersial pada 17 Desember 2025, dengan peningkatan kapasitas unit distilasi minyak mentah (CDU) dari 260.000 barel per hari (bph) menjadi 360.000 bph, yang akan meningkatkan total kapasitas CDU nasional dari 1.17 juta bph menjadi 1.26 juta bph pada akhir 2025. Sementara itu, keputusan investasi akhir (FID) untuk proyek Grass Root Refinery (GRR) Kilang Tuban yang bernilai sekitar US$20.7 miliar hingga US$24 miliar, dengan PJSC Rosneft Oil Company sebagai mitra utama, ditargetkan rampung pada akhir Desember 2025. PT Pertamina Patra Niaga juga telah menyalurkan total 430.000 barel base fuel kepada SPBU swasta per Desember 2025 untuk mengatasi kekosongan stok sebelumnya.
 3.  Distribusi BBM dan LPG di Aceh, Sumatra Utara, dan Sumatra Barat menghadapi tantangan akibat bencana alam, mendorong PT Pertamina Patra Niaga untuk mengoptimalkan berbagai moda transportasi termasuk jalur udara menggunakan pesawat Air Tractor guna memastikan pasokan energi mencapai wilayah terisolir. Kementerian Energi dan Sumber Daya Mineral memperpanjang relaksasi pembelian BBM subsidi tanpa penggunaan QR code di wilayah terdampak bencana hingga akhir Desember 2025. Selain itu, harga BBM nonsubsidi dari Pertamina, Shell, BP-AKR, dan Vivo mengalami penyesuaian kenaikan per 1 Desember 2025. Menjelang Natal dan Tahun Baru 2026, Pertamina Patra Niaga memproyeksikan kenaikan kebutuhan BBM jenis gasolin sebesar 5% dan avtur 1.6%, serta penurunan gasoil sebesar 4% di wilayah Jawa Tengah-DI Yogyakarta.</t>
+  </si>
+  <si>
+    <t>Pada periode 2025-12-01 sampai 2025-12-07, rata-rata SAF tercatat 2472.10 dan rata-rata UCO 1066.60. Secara periodik, SAF mengalami penurunan 4.11% dan UCO mengalami penurunan 0.49% dibanding periode sebelumnya.</t>
+  </si>
+  <si>
+    <t>Pada periode 2025-12-08 sampai 2025-12-14, rata-rata SAF tercatat 2278.40 dan rata-rata UCO 1060.00. Secara periodik, SAF mengalami penurunan 7.84% dan UCO mengalami penurunan 0.62% dibanding periode sebelumnya.</t>
+  </si>
+  <si>
+    <t>Pada periode 2025-12-15 sampai 2025-12-21, rata-rata SAF tercatat 2227.85 dan rata-rata UCO 1058.00. Secara periodik, SAF mengalami penurunan 2.22% dan UCO mengalami penurunan 0.19% dibanding periode sebelumnya.</t>
+  </si>
+  <si>
+    <t>Pada periode 2025-12-22 sampai 2025-12-28, rata-rata SAF tercatat 2246.50 dan rata-rata UCO 1055.00. Secara periodik, SAF mengalami kenaikan 0.84% dan UCO mengalami penurunan 0.28% dibanding periode sebelumnya.</t>
+  </si>
+  <si>
+    <t>Pada periode 2025-12-29 sampai 2026-01-04, rata-rata SAF tercatat 2231.31 dan rata-rata UCO 1055.00. Secara periodik, SAF mengalami penurunan 0.68% dan UCO mengalami kenaikan 0.00% dibanding periode sebelumnya.</t>
+  </si>
+  <si>
+    <t>"1) Harga Sustainable Aviation Fuel (SAF) di AS, Eropa, dan Asia umumnya menurun atau stabil karena volume kepatuhan tahun 2025 sebagian besar telah terpenuhi, sementara harga bahan baku minyak jelantah (UCO) menunjukkan tren bearish akibat permintaan yang lesu dan pemeliharaan pabrik.
+2) Banyak perusahaan secara global, termasuk Petrobras, Shell, dan XCF Global, berinvestasi dalam fasilitas produksi Sustainable Aviation Fuel (SAF) baru atau memperluas kapasitas yang ada, seringkali menggunakan bahan baku limbah atau mengembangkan teknologi e-SAF.
+3) Pemerintah di Inggris, Malaysia, dan Korea Selatan menerapkan atau memajukan mandat pencampuran SAF serta mekanisme dukungan untuk mempercepat adopsi, meskipun penundaan regulasi dan biaya produksi yang tinggi masih menjadi tantangan."</t>
+  </si>
+  <si>
+    <t>"1) Organisasi Penerbangan Sipil Internasional (ICAO) secara resmi menyetujui limbah cair kelapa sawit (POME) sebagai bahan baku bahan bakar penerbangan berkelanjutan (SAF), yang menempatkan Indonesia pada posisi untuk menjadi produsen utama dengan kapasitas besar dan mandat domestik pada tahun 2030.
+2) Produksi SAF global diproyeksikan tumbuh, tetapi harga premium yang tinggi dan masalah implementasi kebijakan, terutama di Eropa, meningkatkan biaya kepatuhan bagi maskapai penerbangan dan memengaruhi keputusan investasi, sementara Amerika Serikat berupaya memulihkan insentif pajak.
+3) Pasar bahan baku Asia, khususnya untuk minyak jelantah (UCO), mengalami pelemahan harga dan permintaan rendah, dipengaruhi oleh dinamika pasokan regional dan perubahan regulasi Eropa, terutama undang-undang RED III baru Jerman yang akan mengubah mekanisme kredit biofuel mulai tahun 2026."</t>
+  </si>
+  <si>
+    <t>"1) Indonesia akan memulai groundbreaking proyek kilang bioavtur di Cilacap senilai $1,1 miliar dan proyek bioetanol di Banyuwangi pada awal Januari 2026.
+2) Kapasitas produksi Sustainable Aviation Fuel (SAF) di Asia diperkirakan meningkat, namun sebagian besar outputnya akan diekspor ke Eropa karena regulasi mandatori yang lebih ketat di sana.
+3) Pasar SAF dan bahan baku seperti Used Cooking Oil (UCO) menunjukkan tren harga yang stabil atau melemah di berbagai wilayah, dipengaruhi oleh permintaan akhir tahun yang lambat dan perubahan kebijakan energi terbarukan di Eropa."</t>
+  </si>
+  <si>
+    <t>"1) Indonesia berencana menghentikan impor bahan bakar secara bertahap dalam empat tahun ke depan, dimulai dengan program B50 pada tahun 2026 untuk mengeliminasi impor diesel, serta mengembangkan kapasitas produksi SAF di kilang Cilacap, Dumai, dan Balongan.
+2) Pasar Sustainable Aviation Fuel (SAF) global menunjukkan peningkatan kapasitas produksi dari bahan baku limbah, bersamaan dengan penerapan mandat pencampuran SAF oleh beberapa negara, namun menghadapi tantangan harga yang tinggi dan perdebatan tentang penggunaan bahan baku nabati.
+3) Harga bahan baku minyak jelantah (UCO) di Asia melemah akibat permintaan yang lambat dan aktivitas pasar yang lesu, sementara Malaysia sedang mempertimbangkan pembatasan ekspor UCO dan residu minyak sawit untuk mengamankan pasokan domestik bagi sektor SAF."</t>
+  </si>
+  <si>
+    <t>"1) Volume produksi Sustainable Aviation Fuel (SAF) domestik di AS mencapai rekor tertinggi pada Desember 2025, sementara harga SAF di Asia dan Eropa menurun karena permintaan yang lesu dan ketidakjelasan kebijakan.
+2) Beberapa negara seperti Inggris, Uni Eropa, AS, dan Korea Selatan sedang menerapkan atau merencanakan mandat pencampuran SAF yang lebih tinggi, mendorong kebutuhan akan diversifikasi bahan baku dan peningkatan kapasitas produksi.
+3) Pasar bahan baku bioenergi seperti minyak jelantah (UCO) domestik di China menunjukkan kenaikan harga di beberapa wilayah karena minat beli yang meningkat, namun pasar global secara umum stabil dengan aktivitas perdagangan yang terbatas akibat liburan."</t>
   </si>
 </sst>
 </file>
@@ -712,7 +753,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,6 +785,19 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -841,7 +895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -858,6 +912,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1162,9 +1225,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45965</v>
       </c>
@@ -1186,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45965</v>
       </c>
@@ -1197,7 +1260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45965</v>
       </c>
@@ -1208,7 +1271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45965</v>
       </c>
@@ -1219,7 +1282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45965</v>
       </c>
@@ -1230,7 +1293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45965</v>
       </c>
@@ -1241,7 +1304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45965</v>
       </c>
@@ -1252,7 +1315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45965</v>
       </c>
@@ -1263,7 +1326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45965</v>
       </c>
@@ -1274,7 +1337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45965</v>
       </c>
@@ -1285,7 +1348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45965</v>
       </c>
@@ -1296,7 +1359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45958</v>
       </c>
@@ -1307,7 +1370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45958</v>
       </c>
@@ -1318,7 +1381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -1329,7 +1392,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45958</v>
       </c>
@@ -1340,7 +1403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45958</v>
       </c>
@@ -1351,7 +1414,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45958</v>
       </c>
@@ -1362,7 +1425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45958</v>
       </c>
@@ -1373,7 +1436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45958</v>
       </c>
@@ -1384,7 +1447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45958</v>
       </c>
@@ -1395,7 +1458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45958</v>
       </c>
@@ -1406,7 +1469,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45958</v>
       </c>
@@ -1417,7 +1480,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45958</v>
       </c>
@@ -1428,7 +1491,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45959</v>
       </c>
@@ -1439,7 +1502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45959</v>
       </c>
@@ -1450,7 +1513,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45959</v>
       </c>
@@ -1461,7 +1524,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45959</v>
       </c>
@@ -1472,7 +1535,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45959</v>
       </c>
@@ -1483,7 +1546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45959</v>
       </c>
@@ -1494,7 +1557,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45959</v>
       </c>
@@ -1505,7 +1568,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45959</v>
       </c>
@@ -1516,7 +1579,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45959</v>
       </c>
@@ -1527,7 +1590,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45959</v>
       </c>
@@ -1538,7 +1601,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45959</v>
       </c>
@@ -1549,7 +1612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45959</v>
       </c>
@@ -1568,9 +1631,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -1584,7 +1647,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -1598,7 +1661,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -1609,7 +1672,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -1628,9 +1691,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -1644,7 +1707,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -1658,7 +1721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -1669,7 +1732,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -1688,9 +1751,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -1704,7 +1767,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -1718,7 +1781,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -1729,7 +1792,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -1748,9 +1811,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -1764,7 +1827,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -1778,7 +1841,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -1789,7 +1852,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -1808,9 +1871,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>50</v>
       </c>
@@ -1824,7 +1887,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45950</v>
       </c>
@@ -1838,7 +1901,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45962</v>
       </c>
@@ -1852,7 +1915,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45969</v>
       </c>
@@ -1866,7 +1929,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45976</v>
       </c>
@@ -1880,7 +1943,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45983</v>
       </c>
@@ -1894,7 +1957,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45990</v>
       </c>
@@ -1916,13 +1979,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>50</v>
       </c>
@@ -1936,7 +1999,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -1950,7 +2013,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -1964,7 +2027,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -1984,206 +2047,199 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF5B289-DB7C-4659-B01A-C21D26B533A5}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>45990</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>45985</v>
+      </c>
+      <c r="B2" s="8">
         <v>45991</v>
       </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="C2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>45992</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="8">
         <v>45998</v>
       </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="C3" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
         <v>45999</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="8">
         <v>46005</v>
       </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>46006</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="8">
         <v>46012</v>
       </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="C5" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
         <v>46013</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="8">
         <v>46019</v>
       </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="C6" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46020</v>
       </c>
-      <c r="B7" s="1">
-        <v>46020</v>
-      </c>
-      <c r="C7" t="s">
-        <v>114</v>
+      <c r="B7" s="10">
+        <v>46026</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>45950</v>
+        <v>45990</v>
       </c>
       <c r="B2" s="1">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B3" s="1">
-        <v>45968</v>
+        <v>45998</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>45969</v>
+        <v>45999</v>
       </c>
       <c r="B4" s="1">
-        <v>45975</v>
+        <v>46005</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="B5" s="1">
-        <v>45982</v>
+        <v>46012</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>45983</v>
+        <v>46013</v>
       </c>
       <c r="B6" s="1">
-        <v>45989</v>
+        <v>46019</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>45990</v>
+        <v>46020</v>
       </c>
       <c r="B7" s="1">
-        <v>45991</v>
+        <v>46020</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>45992</v>
-      </c>
-      <c r="B8" s="1">
-        <v>45998</v>
-      </c>
-      <c r="C8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>45999</v>
-      </c>
-      <c r="B9" s="1">
-        <v>46005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2192,11 +2248,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2210,7 +2266,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45950</v>
       </c>
@@ -2221,7 +2277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45962</v>
       </c>
@@ -2229,10 +2285,10 @@
         <v>45968</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45969</v>
       </c>
@@ -2240,10 +2296,10 @@
         <v>45975</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45976</v>
       </c>
@@ -2251,10 +2307,10 @@
         <v>45982</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45983</v>
       </c>
@@ -2262,10 +2318,10 @@
         <v>45989</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45990</v>
       </c>
@@ -2279,7 +2335,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45992</v>
       </c>
@@ -2287,10 +2343,10 @@
         <v>45998</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45999</v>
       </c>
@@ -2298,7 +2354,7 @@
         <v>46005</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2307,11 +2363,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2325,7 +2381,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45950</v>
       </c>
@@ -2336,7 +2392,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45962</v>
       </c>
@@ -2344,10 +2400,10 @@
         <v>45968</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45969</v>
       </c>
@@ -2355,10 +2411,10 @@
         <v>45975</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45976</v>
       </c>
@@ -2366,10 +2422,10 @@
         <v>45982</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45983</v>
       </c>
@@ -2377,10 +2433,10 @@
         <v>45989</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45990</v>
       </c>
@@ -2394,7 +2450,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45992</v>
       </c>
@@ -2402,10 +2458,10 @@
         <v>45998</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45999</v>
       </c>
@@ -2413,7 +2469,7 @@
         <v>46005</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2424,13 +2480,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>50</v>
       </c>
@@ -2444,7 +2500,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -2464,11 +2520,126 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45950</v>
+      </c>
+      <c r="B2" s="1">
+        <v>45961</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45968</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45969</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45975</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45982</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45989</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45998</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2482,7 +2653,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45950</v>
       </c>
@@ -2493,7 +2664,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45962</v>
       </c>
@@ -2504,7 +2675,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45969</v>
       </c>
@@ -2515,7 +2686,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45976</v>
       </c>
@@ -2526,7 +2697,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45983</v>
       </c>
@@ -2537,7 +2708,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45990</v>
       </c>
@@ -2551,7 +2722,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45992</v>
       </c>
@@ -2562,7 +2733,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45999</v>
       </c>
@@ -2581,9 +2752,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>50</v>
       </c>
@@ -2597,7 +2768,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -2619,9 +2790,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2635,7 +2806,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -2649,7 +2820,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -2660,7 +2831,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45993</v>
       </c>
@@ -2671,7 +2842,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45994</v>
       </c>
@@ -2682,7 +2853,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45995</v>
       </c>
@@ -2693,7 +2864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45996</v>
       </c>
@@ -2704,7 +2875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45997</v>
       </c>
@@ -2715,7 +2886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46000</v>
       </c>
@@ -2726,7 +2897,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46001</v>
       </c>
@@ -2737,7 +2908,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46002</v>
       </c>
@@ -2748,7 +2919,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46003</v>
       </c>
@@ -2759,7 +2930,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46004</v>
       </c>
@@ -2770,7 +2941,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46005</v>
       </c>
@@ -2781,7 +2952,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46006</v>
       </c>
@@ -2792,7 +2963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46007</v>
       </c>
@@ -2803,7 +2974,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46008</v>
       </c>
@@ -2822,9 +2993,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2838,7 +3009,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -2852,7 +3023,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -2863,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45993</v>
       </c>
@@ -2874,7 +3045,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45994</v>
       </c>
@@ -2885,7 +3056,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45995</v>
       </c>
@@ -2896,7 +3067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45996</v>
       </c>
@@ -2907,7 +3078,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45997</v>
       </c>
@@ -2918,7 +3089,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46000</v>
       </c>
@@ -2929,7 +3100,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46001</v>
       </c>
@@ -2940,7 +3111,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46002</v>
       </c>
@@ -2951,7 +3122,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46003</v>
       </c>
@@ -2962,7 +3133,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46004</v>
       </c>
@@ -2973,7 +3144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46005</v>
       </c>
@@ -2984,7 +3155,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46007</v>
       </c>
@@ -2995,7 +3166,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46008</v>
       </c>
@@ -3014,9 +3185,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -3030,7 +3201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -3044,7 +3215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -3055,7 +3226,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -3074,9 +3245,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -3090,7 +3261,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -3104,7 +3275,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -3115,7 +3286,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
@@ -3134,9 +3305,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -3150,7 +3321,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -3164,7 +3335,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -3183,9 +3354,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -3199,7 +3370,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45990</v>
       </c>
@@ -3213,7 +3384,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45992</v>
       </c>
@@ -3224,7 +3395,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45999</v>
       </c>
